--- a/store_wise_monthly_costs.xlsx
+++ b/store_wise_monthly_costs.xlsx
@@ -5894,10 +5894,10 @@
         <v>11.1</v>
       </c>
       <c r="H156" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I156" t="n">
-        <v>143149.07</v>
+        <v>44354.55</v>
       </c>
     </row>
     <row r="157">
@@ -5929,10 +5929,10 @@
         <v>4.94</v>
       </c>
       <c r="H157" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I157" t="n">
-        <v>63738.35</v>
+        <v>19749.25</v>
       </c>
     </row>
     <row r="158">
@@ -5964,10 +5964,10 @@
         <v>8.1</v>
       </c>
       <c r="H158" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I158" t="n">
-        <v>104462.34</v>
+        <v>32367.52</v>
       </c>
     </row>
     <row r="159">
@@ -5999,10 +5999,10 @@
         <v>3.6</v>
       </c>
       <c r="H159" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I159" t="n">
-        <v>46361.68</v>
+        <v>14365.11</v>
       </c>
     </row>
     <row r="160">
@@ -6034,10 +6034,10 @@
         <v>7.37</v>
       </c>
       <c r="H160" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I160" t="n">
-        <v>95030.50999999999</v>
+        <v>29445.08</v>
       </c>
     </row>
     <row r="161">
@@ -6069,10 +6069,10 @@
         <v>6.08</v>
       </c>
       <c r="H161" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I161" t="n">
-        <v>78438.47</v>
+        <v>24304.06</v>
       </c>
     </row>
     <row r="162">
@@ -6104,10 +6104,10 @@
         <v>2.79</v>
       </c>
       <c r="H162" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I162" t="n">
-        <v>36010.45</v>
+        <v>11157.79</v>
       </c>
     </row>
     <row r="163">
@@ -6139,10 +6139,10 @@
         <v>1.31</v>
       </c>
       <c r="H163" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I163" t="n">
-        <v>16876.93</v>
+        <v>5229.29</v>
       </c>
     </row>
     <row r="164">
@@ -6174,10 +6174,10 @@
         <v>11.92</v>
       </c>
       <c r="H164" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I164" t="n">
-        <v>153664.31</v>
+        <v>47612.69</v>
       </c>
     </row>
     <row r="165">
@@ -6209,10 +6209,10 @@
         <v>12.32</v>
       </c>
       <c r="H165" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I165" t="n">
-        <v>158938.06</v>
+        <v>49246.75</v>
       </c>
     </row>
     <row r="166">
@@ -6244,10 +6244,10 @@
         <v>10.17</v>
       </c>
       <c r="H166" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I166" t="n">
-        <v>131159.78</v>
+        <v>40639.69</v>
       </c>
     </row>
     <row r="167">
@@ -6279,10 +6279,10 @@
         <v>6.07</v>
       </c>
       <c r="H167" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I167" t="n">
-        <v>78238.91</v>
+        <v>24242.22</v>
       </c>
     </row>
     <row r="168">
@@ -6314,10 +6314,10 @@
         <v>13.43</v>
       </c>
       <c r="H168" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
       <c r="I168" t="n">
-        <v>173216.89</v>
+        <v>53671.03</v>
       </c>
     </row>
     <row r="169">
@@ -6349,10 +6349,10 @@
         <v>5.52</v>
       </c>
       <c r="H169" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I169" t="n">
-        <v>74044.89999999999</v>
+        <v>24900.89</v>
       </c>
     </row>
     <row r="170">
@@ -6384,10 +6384,10 @@
         <v>12.15</v>
       </c>
       <c r="H170" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I170" t="n">
-        <v>162887.74</v>
+        <v>54778.25</v>
       </c>
     </row>
     <row r="171">
@@ -6419,10 +6419,10 @@
         <v>12.68</v>
       </c>
       <c r="H171" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I171" t="n">
-        <v>170012.4</v>
+        <v>57174.23</v>
       </c>
     </row>
     <row r="172">
@@ -6454,10 +6454,10 @@
         <v>5.79</v>
       </c>
       <c r="H172" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I172" t="n">
-        <v>77683.99000000001</v>
+        <v>26124.7</v>
       </c>
     </row>
     <row r="173">
@@ -6489,10 +6489,10 @@
         <v>15.94</v>
       </c>
       <c r="H173" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I173" t="n">
-        <v>213777.72</v>
+        <v>71892.25999999999</v>
       </c>
     </row>
     <row r="174">
@@ -6524,10 +6524,10 @@
         <v>15.03</v>
       </c>
       <c r="H174" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I174" t="n">
-        <v>201611.03</v>
+        <v>67800.67</v>
       </c>
     </row>
     <row r="175">
@@ -6559,10 +6559,10 @@
         <v>8.1</v>
       </c>
       <c r="H175" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I175" t="n">
-        <v>108680.71</v>
+        <v>36548.72</v>
       </c>
     </row>
     <row r="176">
@@ -6594,10 +6594,10 @@
         <v>13.59</v>
       </c>
       <c r="H176" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I176" t="n">
-        <v>182197.79</v>
+        <v>61272.11</v>
       </c>
     </row>
     <row r="177">
@@ -6629,10 +6629,10 @@
         <v>11.2</v>
       </c>
       <c r="H177" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
       <c r="I177" t="n">
-        <v>150246.11</v>
+        <v>50526.93</v>
       </c>
     </row>
     <row r="178">
@@ -6664,10 +6664,10 @@
         <v>8.5</v>
       </c>
       <c r="H178" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I178" t="n">
-        <v>112965.96</v>
+        <v>37306.54</v>
       </c>
     </row>
     <row r="179">
@@ -6699,10 +6699,10 @@
         <v>12.87</v>
       </c>
       <c r="H179" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I179" t="n">
-        <v>170989.88</v>
+        <v>56468.7</v>
       </c>
     </row>
     <row r="180">
@@ -6734,10 +6734,10 @@
         <v>13.44</v>
       </c>
       <c r="H180" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I180" t="n">
-        <v>178611.86</v>
+        <v>58985.83</v>
       </c>
     </row>
     <row r="181">
@@ -6769,10 +6769,10 @@
         <v>8.65</v>
       </c>
       <c r="H181" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I181" t="n">
-        <v>114918.27</v>
+        <v>37951.29</v>
       </c>
     </row>
     <row r="182">
@@ -6804,10 +6804,10 @@
         <v>20.44</v>
       </c>
       <c r="H182" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I182" t="n">
-        <v>271639.83</v>
+        <v>89707.92999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6839,10 +6839,10 @@
         <v>14.21</v>
       </c>
       <c r="H183" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I183" t="n">
-        <v>188895.82</v>
+        <v>62382.07</v>
       </c>
     </row>
     <row r="184">
@@ -6874,10 +6874,10 @@
         <v>7.93</v>
       </c>
       <c r="H184" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I184" t="n">
-        <v>105340.66</v>
+        <v>34788.32</v>
       </c>
     </row>
     <row r="185">
@@ -6909,10 +6909,10 @@
         <v>7.67</v>
       </c>
       <c r="H185" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I185" t="n">
-        <v>101963.52</v>
+        <v>33673.03</v>
       </c>
     </row>
     <row r="186">
@@ -6944,10 +6944,10 @@
         <v>4.77</v>
       </c>
       <c r="H186" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
       <c r="I186" t="n">
-        <v>63366.92</v>
+        <v>20926.67</v>
       </c>
     </row>
     <row r="187">
@@ -6979,10 +6979,10 @@
         <v>5.01</v>
       </c>
       <c r="H187" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I187" t="n">
-        <v>71544.95</v>
+        <v>26987.47</v>
       </c>
     </row>
     <row r="188">
@@ -7014,10 +7014,10 @@
         <v>9.960000000000001</v>
       </c>
       <c r="H188" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I188" t="n">
-        <v>142369.73</v>
+        <v>53703.28</v>
       </c>
     </row>
     <row r="189">
@@ -7049,10 +7049,10 @@
         <v>13.4</v>
       </c>
       <c r="H189" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I189" t="n">
-        <v>191447.53</v>
+        <v>72215.91</v>
       </c>
     </row>
     <row r="190">
@@ -7084,10 +7084,10 @@
         <v>14.51</v>
       </c>
       <c r="H190" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I190" t="n">
-        <v>207413.43</v>
+        <v>78238.41</v>
       </c>
     </row>
     <row r="191">
@@ -7119,10 +7119,10 @@
         <v>2.7</v>
       </c>
       <c r="H191" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I191" t="n">
-        <v>38566.91</v>
+        <v>14547.82</v>
       </c>
     </row>
     <row r="192">
@@ -7154,10 +7154,10 @@
         <v>15.95</v>
       </c>
       <c r="H192" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I192" t="n">
-        <v>227872.03</v>
+        <v>85955.60000000001</v>
       </c>
     </row>
     <row r="193">
@@ -7189,10 +7189,10 @@
         <v>16.52</v>
       </c>
       <c r="H193" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I193" t="n">
-        <v>236020.19</v>
+        <v>89029.17</v>
       </c>
     </row>
     <row r="194">
@@ -7224,10 +7224,10 @@
         <v>6.72</v>
       </c>
       <c r="H194" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I194" t="n">
-        <v>96020.02</v>
+        <v>36219.71</v>
       </c>
     </row>
     <row r="195">
@@ -7259,10 +7259,10 @@
         <v>13.92</v>
       </c>
       <c r="H195" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
       <c r="I195" t="n">
-        <v>198860.26</v>
+        <v>75012.07000000001</v>
       </c>
     </row>
     <row r="196">
@@ -7294,10 +7294,10 @@
         <v>8</v>
       </c>
       <c r="H196" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I196" t="n">
-        <v>104867.02</v>
+        <v>33707.47</v>
       </c>
     </row>
     <row r="197">
@@ -7329,10 +7329,10 @@
         <v>21.94</v>
       </c>
       <c r="H197" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I197" t="n">
-        <v>287767.11</v>
+        <v>92497.14999999999</v>
       </c>
     </row>
     <row r="198">
@@ -7364,10 +7364,10 @@
         <v>10.99</v>
       </c>
       <c r="H198" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I198" t="n">
-        <v>144134.51</v>
+        <v>46329.24</v>
       </c>
     </row>
     <row r="199">
@@ -7399,10 +7399,10 @@
         <v>11.66</v>
       </c>
       <c r="H199" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I199" t="n">
-        <v>152918.91</v>
+        <v>49152.81</v>
       </c>
     </row>
     <row r="200">
@@ -7434,10 +7434,10 @@
         <v>5.48</v>
       </c>
       <c r="H200" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I200" t="n">
-        <v>71936.69</v>
+        <v>23122.65</v>
       </c>
     </row>
     <row r="201">
@@ -7469,10 +7469,10 @@
         <v>10.35</v>
       </c>
       <c r="H201" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I201" t="n">
-        <v>135803.95</v>
+        <v>43651.54</v>
       </c>
     </row>
     <row r="202">
@@ -7504,10 +7504,10 @@
         <v>8.789999999999999</v>
       </c>
       <c r="H202" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I202" t="n">
-        <v>115259.77</v>
+        <v>37048.01</v>
       </c>
     </row>
     <row r="203">
@@ -7539,10 +7539,10 @@
         <v>8.75</v>
       </c>
       <c r="H203" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I203" t="n">
-        <v>114729.5</v>
+        <v>36877.57</v>
       </c>
     </row>
     <row r="204">
@@ -7574,10 +7574,10 @@
         <v>13.96</v>
       </c>
       <c r="H204" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
       <c r="I204" t="n">
-        <v>183038.21</v>
+        <v>58834.08</v>
       </c>
     </row>
     <row r="205">
@@ -7609,10 +7609,10 @@
         <v>6.58</v>
       </c>
       <c r="H205" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I205" t="n">
-        <v>95242.36</v>
+        <v>36701.33</v>
       </c>
     </row>
     <row r="206">
@@ -7644,10 +7644,10 @@
         <v>20.46</v>
       </c>
       <c r="H206" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I206" t="n">
-        <v>296195.92</v>
+        <v>114138.12</v>
       </c>
     </row>
     <row r="207">
@@ -7679,10 +7679,10 @@
         <v>19.04</v>
       </c>
       <c r="H207" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I207" t="n">
-        <v>275725.66</v>
+        <v>106249.97</v>
       </c>
     </row>
     <row r="208">
@@ -7714,10 +7714,10 @@
         <v>3.91</v>
       </c>
       <c r="H208" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I208" t="n">
-        <v>56555.29</v>
+        <v>21793.39</v>
       </c>
     </row>
     <row r="209">
@@ -7749,10 +7749,10 @@
         <v>12.1</v>
       </c>
       <c r="H209" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I209" t="n">
-        <v>175263.36</v>
+        <v>67537.16</v>
       </c>
     </row>
     <row r="210">
@@ -7784,10 +7784,10 @@
         <v>5.85</v>
       </c>
       <c r="H210" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I210" t="n">
-        <v>84688</v>
+        <v>32634.24</v>
       </c>
     </row>
     <row r="211">
@@ -7819,10 +7819,10 @@
         <v>5.5</v>
       </c>
       <c r="H211" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I211" t="n">
-        <v>79630.61</v>
+        <v>30685.39</v>
       </c>
     </row>
     <row r="212">
@@ -7854,10 +7854,10 @@
         <v>10.68</v>
       </c>
       <c r="H212" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
       <c r="I212" t="n">
-        <v>154686.9</v>
+        <v>59608.09</v>
       </c>
     </row>
     <row r="213">
@@ -7889,10 +7889,10 @@
         <v>19.67</v>
       </c>
       <c r="H213" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I213" t="n">
-        <v>263288.77</v>
+        <v>88207.48</v>
       </c>
     </row>
     <row r="214">
@@ -7924,10 +7924,10 @@
         <v>10.45</v>
       </c>
       <c r="H214" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I214" t="n">
-        <v>139872.69</v>
+        <v>46860.4</v>
       </c>
     </row>
     <row r="215">
@@ -7959,10 +7959,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="H215" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I215" t="n">
-        <v>127795.25</v>
+        <v>42814.2</v>
       </c>
     </row>
     <row r="216">
@@ -7994,10 +7994,10 @@
         <v>6.16</v>
       </c>
       <c r="H216" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I216" t="n">
-        <v>82426.64</v>
+        <v>27614.72</v>
       </c>
     </row>
     <row r="217">
@@ -8029,10 +8029,10 @@
         <v>5.72</v>
       </c>
       <c r="H217" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I217" t="n">
-        <v>76598.05</v>
+        <v>25662.02</v>
       </c>
     </row>
     <row r="218">
@@ -8064,10 +8064,10 @@
         <v>8.59</v>
       </c>
       <c r="H218" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I218" t="n">
-        <v>114981.81</v>
+        <v>38521.42</v>
       </c>
     </row>
     <row r="219">
@@ -8099,10 +8099,10 @@
         <v>11.79</v>
       </c>
       <c r="H219" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I219" t="n">
-        <v>157847.42</v>
+        <v>52882.33</v>
       </c>
     </row>
     <row r="220">
@@ -8134,10 +8134,10 @@
         <v>8.539999999999999</v>
       </c>
       <c r="H220" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I220" t="n">
-        <v>114336.23</v>
+        <v>38305.13</v>
       </c>
     </row>
     <row r="221">
@@ -8169,10 +8169,10 @@
         <v>9.33</v>
       </c>
       <c r="H221" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I221" t="n">
-        <v>124908.06</v>
+        <v>41846.93</v>
       </c>
     </row>
     <row r="222">
@@ -8204,10 +8204,10 @@
         <v>7.71</v>
       </c>
       <c r="H222" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
       <c r="I222" t="n">
-        <v>103181.63</v>
+        <v>34568.1</v>
       </c>
     </row>
     <row r="223">
@@ -8239,10 +8239,10 @@
         <v>8.029999999999999</v>
       </c>
       <c r="H223" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I223" t="n">
-        <v>93398.3</v>
+        <v>21895.45</v>
       </c>
     </row>
     <row r="224">
@@ -8274,10 +8274,10 @@
         <v>19.49</v>
       </c>
       <c r="H224" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I224" t="n">
-        <v>226631.52</v>
+        <v>53129.44</v>
       </c>
     </row>
     <row r="225">
@@ -8309,10 +8309,10 @@
         <v>12.94</v>
       </c>
       <c r="H225" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I225" t="n">
-        <v>150490.39</v>
+        <v>35279.6</v>
       </c>
     </row>
     <row r="226">
@@ -8344,10 +8344,10 @@
         <v>9.93</v>
       </c>
       <c r="H226" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I226" t="n">
-        <v>115458.92</v>
+        <v>27067.14</v>
       </c>
     </row>
     <row r="227">
@@ -8379,10 +8379,10 @@
         <v>7.46</v>
       </c>
       <c r="H227" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I227" t="n">
-        <v>86694.44</v>
+        <v>20323.86</v>
       </c>
     </row>
     <row r="228">
@@ -8414,10 +8414,10 @@
         <v>10.01</v>
       </c>
       <c r="H228" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I228" t="n">
-        <v>116317.81</v>
+        <v>27268.49</v>
       </c>
     </row>
     <row r="229">
@@ -8449,10 +8449,10 @@
         <v>8.130000000000001</v>
       </c>
       <c r="H229" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I229" t="n">
-        <v>94550.84</v>
+        <v>22165.64</v>
       </c>
     </row>
     <row r="230">
@@ -8484,10 +8484,10 @@
         <v>12.37</v>
       </c>
       <c r="H230" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I230" t="n">
-        <v>143783.67</v>
+        <v>33707.34</v>
       </c>
     </row>
     <row r="231">
@@ -8519,10 +8519,10 @@
         <v>9.27</v>
       </c>
       <c r="H231" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
       <c r="I231" t="n">
-        <v>107756.99</v>
+        <v>25261.57</v>
       </c>
     </row>
     <row r="232">
@@ -8554,10 +8554,10 @@
         <v>18.65</v>
       </c>
       <c r="H232" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I232" t="n">
-        <v>244221.65</v>
+        <v>78206.03999999999</v>
       </c>
     </row>
     <row r="233">
@@ -8589,10 +8589,10 @@
         <v>10.04</v>
       </c>
       <c r="H233" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I233" t="n">
-        <v>131482.43</v>
+        <v>42104.05</v>
       </c>
     </row>
     <row r="234">
@@ -8624,10 +8624,10 @@
         <v>3.93</v>
       </c>
       <c r="H234" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I234" t="n">
-        <v>51507.5</v>
+        <v>16494.02</v>
       </c>
     </row>
     <row r="235">
@@ -8659,10 +8659,10 @@
         <v>19.12</v>
       </c>
       <c r="H235" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I235" t="n">
-        <v>250384.04</v>
+        <v>80179.39</v>
       </c>
     </row>
     <row r="236">
@@ -8694,10 +8694,10 @@
         <v>16.91</v>
       </c>
       <c r="H236" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I236" t="n">
-        <v>221387.01</v>
+        <v>70893.8</v>
       </c>
     </row>
     <row r="237">
@@ -8729,10 +8729,10 @@
         <v>16.03</v>
       </c>
       <c r="H237" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I237" t="n">
-        <v>209874.12</v>
+        <v>67207.08</v>
       </c>
     </row>
     <row r="238">
@@ -8764,10 +8764,10 @@
         <v>8.44</v>
       </c>
       <c r="H238" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I238" t="n">
-        <v>110522.09</v>
+        <v>35392.01</v>
       </c>
     </row>
     <row r="239">
@@ -8799,10 +8799,10 @@
         <v>5.75</v>
       </c>
       <c r="H239" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
       <c r="I239" t="n">
-        <v>75240.75</v>
+        <v>24094.02</v>
       </c>
     </row>
     <row r="240">
@@ -8834,10 +8834,10 @@
         <v>8.869999999999999</v>
       </c>
       <c r="H240" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I240" t="n">
-        <v>114444.38</v>
+        <v>35511.67</v>
       </c>
     </row>
     <row r="241">
@@ -8869,10 +8869,10 @@
         <v>11.36</v>
       </c>
       <c r="H241" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I241" t="n">
-        <v>146538.17</v>
+        <v>45470.26</v>
       </c>
     </row>
     <row r="242">
@@ -8904,10 +8904,10 @@
         <v>12.87</v>
       </c>
       <c r="H242" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I242" t="n">
-        <v>166056.78</v>
+        <v>51526.82</v>
       </c>
     </row>
     <row r="243">
@@ -8939,10 +8939,10 @@
         <v>7.21</v>
       </c>
       <c r="H243" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I243" t="n">
-        <v>93071.34</v>
+        <v>28879.7</v>
       </c>
     </row>
     <row r="244">
@@ -8974,10 +8974,10 @@
         <v>11.74</v>
       </c>
       <c r="H244" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I244" t="n">
-        <v>151470.22</v>
+        <v>47000.66</v>
       </c>
     </row>
     <row r="245">
@@ -9009,10 +9009,10 @@
         <v>11.71</v>
       </c>
       <c r="H245" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I245" t="n">
-        <v>151118.2</v>
+        <v>46891.43</v>
       </c>
     </row>
     <row r="246">
@@ -9044,10 +9044,10 @@
         <v>12.85</v>
       </c>
       <c r="H246" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I246" t="n">
-        <v>165835.98</v>
+        <v>51458.3</v>
       </c>
     </row>
     <row r="247">
@@ -9079,10 +9079,10 @@
         <v>9.08</v>
       </c>
       <c r="H247" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I247" t="n">
-        <v>117154.62</v>
+        <v>36352.65</v>
       </c>
     </row>
     <row r="248">
@@ -9114,10 +9114,10 @@
         <v>12.33</v>
       </c>
       <c r="H248" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
       <c r="I248" t="n">
-        <v>159113.66</v>
+        <v>49372.39</v>
       </c>
     </row>
     <row r="249">
@@ -9149,10 +9149,10 @@
         <v>13.3</v>
       </c>
       <c r="H249" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I249" t="n">
-        <v>158237.53</v>
+        <v>39894.66</v>
       </c>
     </row>
     <row r="250">
@@ -9184,10 +9184,10 @@
         <v>5.36</v>
       </c>
       <c r="H250" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I250" t="n">
-        <v>63818.48</v>
+        <v>16089.84</v>
       </c>
     </row>
     <row r="251">
@@ -9219,10 +9219,10 @@
         <v>10.15</v>
       </c>
       <c r="H251" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I251" t="n">
-        <v>120835.31</v>
+        <v>30464.86</v>
       </c>
     </row>
     <row r="252">
@@ -9254,10 +9254,10 @@
         <v>6.5</v>
       </c>
       <c r="H252" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I252" t="n">
-        <v>77348.75999999999</v>
+        <v>19501.08</v>
       </c>
     </row>
     <row r="253">
@@ -9289,10 +9289,10 @@
         <v>13.04</v>
       </c>
       <c r="H253" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I253" t="n">
-        <v>155146.41</v>
+        <v>39115.33</v>
       </c>
     </row>
     <row r="254">
@@ -9324,10 +9324,10 @@
         <v>12.95</v>
       </c>
       <c r="H254" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I254" t="n">
-        <v>154100.57</v>
+        <v>38851.66</v>
       </c>
     </row>
     <row r="255">
@@ -9359,10 +9359,10 @@
         <v>22.6</v>
       </c>
       <c r="H255" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I255" t="n">
-        <v>268966.75</v>
+        <v>67811.59</v>
       </c>
     </row>
     <row r="256">
@@ -9394,10 +9394,10 @@
         <v>7.66</v>
       </c>
       <c r="H256" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I256" t="n">
-        <v>91107.67</v>
+        <v>22969.96</v>
       </c>
     </row>
     <row r="257">
@@ -9429,10 +9429,10 @@
         <v>6.5</v>
       </c>
       <c r="H257" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
       <c r="I257" t="n">
-        <v>77307.89999999999</v>
+        <v>19490.78</v>
       </c>
     </row>
     <row r="258">
@@ -9464,10 +9464,10 @@
         <v>6.13</v>
       </c>
       <c r="H258" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I258" t="n">
-        <v>83043.00999999999</v>
+        <v>28466.76</v>
       </c>
     </row>
     <row r="259">
@@ -9499,10 +9499,10 @@
         <v>13.27</v>
       </c>
       <c r="H259" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I259" t="n">
-        <v>179654.75</v>
+        <v>61584.83</v>
       </c>
     </row>
     <row r="260">
@@ -9534,10 +9534,10 @@
         <v>12.74</v>
       </c>
       <c r="H260" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I260" t="n">
-        <v>172492.47</v>
+        <v>59129.63</v>
       </c>
     </row>
     <row r="261">
@@ -9569,10 +9569,10 @@
         <v>12.82</v>
       </c>
       <c r="H261" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I261" t="n">
-        <v>173582.2</v>
+        <v>59503.18</v>
       </c>
     </row>
     <row r="262">
@@ -9604,10 +9604,10 @@
         <v>9.880000000000001</v>
       </c>
       <c r="H262" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I262" t="n">
-        <v>133795.43</v>
+        <v>45864.46</v>
       </c>
     </row>
     <row r="263">
@@ -9639,10 +9639,10 @@
         <v>11.06</v>
       </c>
       <c r="H263" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I263" t="n">
-        <v>149759.74</v>
+        <v>51336.95</v>
       </c>
     </row>
     <row r="264">
@@ -9674,10 +9674,10 @@
         <v>13.47</v>
       </c>
       <c r="H264" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I264" t="n">
-        <v>182359.69</v>
+        <v>62512.07</v>
       </c>
     </row>
     <row r="265">
@@ -9709,10 +9709,10 @@
         <v>7.8</v>
       </c>
       <c r="H265" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I265" t="n">
-        <v>105565.72</v>
+        <v>36187.45</v>
       </c>
     </row>
     <row r="266">
@@ -9744,10 +9744,10 @@
         <v>7</v>
       </c>
       <c r="H266" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I266" t="n">
-        <v>94753.38</v>
+        <v>32481.03</v>
       </c>
     </row>
     <row r="267">
@@ -9779,10 +9779,10 @@
         <v>4.33</v>
       </c>
       <c r="H267" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
       <c r="I267" t="n">
-        <v>58676.58</v>
+        <v>20114.06</v>
       </c>
     </row>
     <row r="268">
@@ -14838,26 +14838,26 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>DPI64273</t>
+          <t>DPI63822</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>135.21</v>
+        <v>164.81</v>
       </c>
       <c r="E412" t="n">
         <v>980</v>
       </c>
       <c r="F412" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G412" t="n">
-        <v>13.8</v>
+        <v>16.82</v>
       </c>
       <c r="H412" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I412" t="n">
-        <v>163774.07</v>
+        <v>197890.86</v>
       </c>
     </row>
     <row r="413">
@@ -14873,26 +14873,26 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>DPI64665</t>
+          <t>DPI64378</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>69.66</v>
+        <v>105.69</v>
       </c>
       <c r="E413" t="n">
         <v>980</v>
       </c>
       <c r="F413" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G413" t="n">
-        <v>7.11</v>
+        <v>10.78</v>
       </c>
       <c r="H413" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I413" t="n">
-        <v>84381.37</v>
+        <v>126900.15</v>
       </c>
     </row>
     <row r="414">
@@ -14908,26 +14908,26 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>DPI66263</t>
+          <t>DPI64255</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>123.87</v>
+        <v>119.39</v>
       </c>
       <c r="E414" t="n">
         <v>980</v>
       </c>
       <c r="F414" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G414" t="n">
-        <v>12.64</v>
+        <v>12.18</v>
       </c>
       <c r="H414" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I414" t="n">
-        <v>150042.81</v>
+        <v>143355.4</v>
       </c>
     </row>
     <row r="415">
@@ -14943,26 +14943,26 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>DPI64502</t>
+          <t>DPI63920</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>96.36</v>
+        <v>105.6</v>
       </c>
       <c r="E415" t="n">
         <v>980</v>
       </c>
       <c r="F415" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G415" t="n">
-        <v>9.83</v>
+        <v>10.78</v>
       </c>
       <c r="H415" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I415" t="n">
-        <v>116717.06</v>
+        <v>126795.13</v>
       </c>
     </row>
     <row r="416">
@@ -14978,26 +14978,26 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>DPI70120</t>
+          <t>DPI66659</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>93.91</v>
+        <v>133.62</v>
       </c>
       <c r="E416" t="n">
         <v>980</v>
       </c>
       <c r="F416" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G416" t="n">
-        <v>9.58</v>
+        <v>13.63</v>
       </c>
       <c r="H416" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I416" t="n">
-        <v>113744.63</v>
+        <v>160432.92</v>
       </c>
     </row>
     <row r="417">
@@ -15013,26 +15013,26 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>DPI64647</t>
+          <t>DPI64476</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>103.29</v>
+        <v>105.61</v>
       </c>
       <c r="E417" t="n">
         <v>980</v>
       </c>
       <c r="F417" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G417" t="n">
-        <v>10.54</v>
+        <v>10.78</v>
       </c>
       <c r="H417" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I417" t="n">
-        <v>125115.6</v>
+        <v>126811.62</v>
       </c>
     </row>
     <row r="418">
@@ -15048,26 +15048,26 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>DPI64032</t>
+          <t>DPI66175</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>85.3</v>
+        <v>174.81</v>
       </c>
       <c r="E418" t="n">
         <v>980</v>
       </c>
       <c r="F418" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G418" t="n">
-        <v>8.699999999999999</v>
+        <v>17.84</v>
       </c>
       <c r="H418" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I418" t="n">
-        <v>103325.88</v>
+        <v>209898.82</v>
       </c>
     </row>
     <row r="419">
@@ -15083,26 +15083,26 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>DPI66402</t>
+          <t>DPI70317</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>148.74</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="E419" t="n">
         <v>980</v>
       </c>
       <c r="F419" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G419" t="n">
-        <v>15.18</v>
+        <v>7.08</v>
       </c>
       <c r="H419" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I419" t="n">
-        <v>180161.1</v>
+        <v>83268.33</v>
       </c>
     </row>
     <row r="420">
@@ -15113,31 +15113,31 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>DPI64758</t>
+          <t>DPI64696</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>99.53</v>
+        <v>137.67</v>
       </c>
       <c r="E420" t="n">
         <v>980</v>
       </c>
       <c r="F420" t="n">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="G420" t="n">
-        <v>10.16</v>
+        <v>14.05</v>
       </c>
       <c r="H420" t="n">
-        <v>1187034.55</v>
+        <v>1194686.49</v>
       </c>
       <c r="I420" t="n">
-        <v>120559.42</v>
+        <v>167834.86</v>
       </c>
     </row>
     <row r="421">
@@ -15153,11 +15153,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>DPI70302</t>
+          <t>DPI64179</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>51.33</v>
+        <v>138.73</v>
       </c>
       <c r="E421" t="n">
         <v>980</v>
@@ -15166,13 +15166,13 @@
         <v>968</v>
       </c>
       <c r="G421" t="n">
-        <v>5.24</v>
+        <v>14.16</v>
       </c>
       <c r="H421" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I421" t="n">
-        <v>62576.63</v>
+        <v>169126.93</v>
       </c>
     </row>
     <row r="422">
@@ -15188,11 +15188,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>DPI66262</t>
+          <t>DPI64651</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>130.59</v>
+        <v>129.73</v>
       </c>
       <c r="E422" t="n">
         <v>980</v>
@@ -15201,13 +15201,13 @@
         <v>968</v>
       </c>
       <c r="G422" t="n">
-        <v>13.33</v>
+        <v>13.24</v>
       </c>
       <c r="H422" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I422" t="n">
-        <v>159213.32</v>
+        <v>158143.67</v>
       </c>
     </row>
     <row r="423">
@@ -15223,11 +15223,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DPI70273</t>
+          <t>DPI70179</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>39.41</v>
+        <v>97.11</v>
       </c>
       <c r="E423" t="n">
         <v>980</v>
@@ -15236,13 +15236,13 @@
         <v>968</v>
       </c>
       <c r="G423" t="n">
-        <v>4.02</v>
+        <v>9.91</v>
       </c>
       <c r="H423" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I423" t="n">
-        <v>48041.12</v>
+        <v>118384.85</v>
       </c>
     </row>
     <row r="424">
@@ -15258,11 +15258,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>DPI70179</t>
+          <t>DPI70273</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>97.11</v>
+        <v>39.41</v>
       </c>
       <c r="E424" t="n">
         <v>980</v>
@@ -15271,13 +15271,13 @@
         <v>968</v>
       </c>
       <c r="G424" t="n">
-        <v>9.91</v>
+        <v>4.02</v>
       </c>
       <c r="H424" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I424" t="n">
-        <v>118392.75</v>
+        <v>48037.92</v>
       </c>
     </row>
     <row r="425">
@@ -15293,11 +15293,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>DPI64651</t>
+          <t>DPI66144</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>129.73</v>
+        <v>99.38</v>
       </c>
       <c r="E425" t="n">
         <v>980</v>
@@ -15306,13 +15306,13 @@
         <v>968</v>
       </c>
       <c r="G425" t="n">
-        <v>13.24</v>
+        <v>10.14</v>
       </c>
       <c r="H425" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I425" t="n">
-        <v>158154.22</v>
+        <v>121145.84</v>
       </c>
     </row>
     <row r="426">
@@ -15328,11 +15328,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>DPI66144</t>
+          <t>DPI63847</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>99.38</v>
+        <v>144.26</v>
       </c>
       <c r="E426" t="n">
         <v>980</v>
@@ -15341,13 +15341,13 @@
         <v>968</v>
       </c>
       <c r="G426" t="n">
-        <v>10.14</v>
+        <v>14.72</v>
       </c>
       <c r="H426" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I426" t="n">
-        <v>121153.92</v>
+        <v>175868.54</v>
       </c>
     </row>
     <row r="427">
@@ -15363,11 +15363,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>DPI63847</t>
+          <t>DPI66262</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>144.26</v>
+        <v>130.59</v>
       </c>
       <c r="E427" t="n">
         <v>980</v>
@@ -15376,13 +15376,13 @@
         <v>968</v>
       </c>
       <c r="G427" t="n">
-        <v>14.72</v>
+        <v>13.33</v>
       </c>
       <c r="H427" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I427" t="n">
-        <v>175880.27</v>
+        <v>159202.7</v>
       </c>
     </row>
     <row r="428">
@@ -15398,11 +15398,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>DPI64179</t>
+          <t>DPI70302</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>138.73</v>
+        <v>51.33</v>
       </c>
       <c r="E428" t="n">
         <v>980</v>
@@ -15411,13 +15411,13 @@
         <v>968</v>
       </c>
       <c r="G428" t="n">
-        <v>14.16</v>
+        <v>5.24</v>
       </c>
       <c r="H428" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I428" t="n">
-        <v>169138.21</v>
+        <v>62572.46</v>
       </c>
     </row>
     <row r="429">
@@ -15428,31 +15428,31 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>DPI64696</t>
+          <t>DPI66263</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>137.67</v>
+        <v>123.87</v>
       </c>
       <c r="E429" t="n">
         <v>980</v>
       </c>
       <c r="F429" t="n">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="G429" t="n">
-        <v>14.05</v>
+        <v>12.64</v>
       </c>
       <c r="H429" t="n">
-        <v>1194766.18</v>
+        <v>1208267.36</v>
       </c>
       <c r="I429" t="n">
-        <v>167846.06</v>
+        <v>152726.67</v>
       </c>
     </row>
     <row r="430">
@@ -15468,26 +15468,26 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>DPI64255</t>
+          <t>DPI64665</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>119.39</v>
+        <v>69.66</v>
       </c>
       <c r="E430" t="n">
         <v>980</v>
       </c>
       <c r="F430" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G430" t="n">
-        <v>12.18</v>
+        <v>7.11</v>
       </c>
       <c r="H430" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I430" t="n">
-        <v>143682.63</v>
+        <v>85890.72</v>
       </c>
     </row>
     <row r="431">
@@ -15503,26 +15503,26 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>DPI63822</t>
+          <t>DPI64502</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>164.81</v>
+        <v>96.36</v>
       </c>
       <c r="E431" t="n">
         <v>980</v>
       </c>
       <c r="F431" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G431" t="n">
-        <v>16.82</v>
+        <v>9.83</v>
       </c>
       <c r="H431" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I431" t="n">
-        <v>198342.57</v>
+        <v>118804.81</v>
       </c>
     </row>
     <row r="432">
@@ -15538,26 +15538,26 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>DPI64378</t>
+          <t>DPI70120</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>105.69</v>
+        <v>93.91</v>
       </c>
       <c r="E432" t="n">
         <v>980</v>
       </c>
       <c r="F432" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G432" t="n">
-        <v>10.78</v>
+        <v>9.58</v>
       </c>
       <c r="H432" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I432" t="n">
-        <v>127189.81</v>
+        <v>115779.21</v>
       </c>
     </row>
     <row r="433">
@@ -15573,26 +15573,26 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>DPI63920</t>
+          <t>DPI64647</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>105.6</v>
+        <v>103.29</v>
       </c>
       <c r="E433" t="n">
         <v>980</v>
       </c>
       <c r="F433" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G433" t="n">
-        <v>10.78</v>
+        <v>10.54</v>
       </c>
       <c r="H433" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I433" t="n">
-        <v>127084.56</v>
+        <v>127353.57</v>
       </c>
     </row>
     <row r="434">
@@ -15608,26 +15608,26 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>DPI66659</t>
+          <t>DPI64032</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>133.62</v>
+        <v>85.3</v>
       </c>
       <c r="E434" t="n">
         <v>980</v>
       </c>
       <c r="F434" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G434" t="n">
-        <v>13.63</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H434" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I434" t="n">
-        <v>160799.13</v>
+        <v>105174.1</v>
       </c>
     </row>
     <row r="435">
@@ -15643,26 +15643,26 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>DPI64476</t>
+          <t>DPI66402</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>105.61</v>
+        <v>148.74</v>
       </c>
       <c r="E435" t="n">
         <v>980</v>
       </c>
       <c r="F435" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G435" t="n">
-        <v>10.78</v>
+        <v>15.18</v>
       </c>
       <c r="H435" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I435" t="n">
-        <v>127101.09</v>
+        <v>183383.69</v>
       </c>
     </row>
     <row r="436">
@@ -15678,26 +15678,26 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>DPI66175</t>
+          <t>DPI64409</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>174.81</v>
+        <v>92.92</v>
       </c>
       <c r="E436" t="n">
         <v>980</v>
       </c>
       <c r="F436" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G436" t="n">
-        <v>17.84</v>
+        <v>9.48</v>
       </c>
       <c r="H436" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I436" t="n">
-        <v>210377.95</v>
+        <v>114564.53</v>
       </c>
     </row>
     <row r="437">
@@ -15713,26 +15713,26 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>DPI70317</t>
+          <t>DPI64273</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>69.34999999999999</v>
+        <v>135.21</v>
       </c>
       <c r="E437" t="n">
         <v>980</v>
       </c>
       <c r="F437" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G437" t="n">
-        <v>7.08</v>
+        <v>13.8</v>
       </c>
       <c r="H437" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
       <c r="I437" t="n">
-        <v>83458.39999999999</v>
+        <v>166703.54</v>
       </c>
     </row>
     <row r="438">
@@ -16098,26 +16098,26 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>DPI66264</t>
+          <t>DPI66684</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>147.75</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E448" t="n">
         <v>980</v>
       </c>
       <c r="F448" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G448" t="n">
-        <v>15.08</v>
+        <v>9.41</v>
       </c>
       <c r="H448" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I448" t="n">
-        <v>194402.2</v>
+        <v>134521.01</v>
       </c>
     </row>
     <row r="449">
@@ -16133,26 +16133,26 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>DPI66684</t>
+          <t>DPI64236</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>92.23999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E449" t="n">
         <v>980</v>
       </c>
       <c r="F449" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G449" t="n">
-        <v>9.41</v>
+        <v>7.12</v>
       </c>
       <c r="H449" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I449" t="n">
-        <v>121363.42</v>
+        <v>101706.43</v>
       </c>
     </row>
     <row r="450">
@@ -16168,26 +16168,26 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>DPI67031</t>
+          <t>DPI66734</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>136.7</v>
+        <v>111.78</v>
       </c>
       <c r="E450" t="n">
         <v>980</v>
       </c>
       <c r="F450" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G450" t="n">
-        <v>13.95</v>
+        <v>11.41</v>
       </c>
       <c r="H450" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I450" t="n">
-        <v>179870.94</v>
+        <v>163025.91</v>
       </c>
     </row>
     <row r="451">
@@ -16203,26 +16203,26 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>DPI64352</t>
+          <t>DPI70073</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>100.22</v>
+        <v>53.01</v>
       </c>
       <c r="E451" t="n">
         <v>980</v>
       </c>
       <c r="F451" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G451" t="n">
-        <v>10.23</v>
+        <v>5.41</v>
       </c>
       <c r="H451" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I451" t="n">
-        <v>131867.64</v>
+        <v>77306.64999999999</v>
       </c>
     </row>
     <row r="452">
@@ -16238,26 +16238,26 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>DPI64288</t>
+          <t>DPI70038</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>116.14</v>
+        <v>100.52</v>
       </c>
       <c r="E452" t="n">
         <v>980</v>
       </c>
       <c r="F452" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G452" t="n">
-        <v>11.85</v>
+        <v>10.26</v>
       </c>
       <c r="H452" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I452" t="n">
-        <v>152813.09</v>
+        <v>146597.34</v>
       </c>
     </row>
     <row r="453">
@@ -16273,26 +16273,26 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>DPI67024</t>
+          <t>DPI64149</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>96.65000000000001</v>
+        <v>43.53</v>
       </c>
       <c r="E453" t="n">
         <v>980</v>
       </c>
       <c r="F453" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G453" t="n">
-        <v>9.859999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="H453" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I453" t="n">
-        <v>127168.01</v>
+        <v>63479.22</v>
       </c>
     </row>
     <row r="454">
@@ -16308,26 +16308,26 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>DPI70041</t>
+          <t>DPI66572</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>72.68000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="E454" t="n">
         <v>980</v>
       </c>
       <c r="F454" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G454" t="n">
-        <v>7.42</v>
+        <v>8.23</v>
       </c>
       <c r="H454" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I454" t="n">
-        <v>95632.84</v>
+        <v>117675.91</v>
       </c>
     </row>
     <row r="455">
@@ -16343,26 +16343,26 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>DPI66646</t>
+          <t>DPI64234</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>154.63</v>
+        <v>68.98</v>
       </c>
       <c r="E455" t="n">
         <v>980</v>
       </c>
       <c r="F455" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G455" t="n">
-        <v>15.78</v>
+        <v>7.04</v>
       </c>
       <c r="H455" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I455" t="n">
-        <v>203456.53</v>
+        <v>100598.82</v>
       </c>
     </row>
     <row r="456">
@@ -16373,31 +16373,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>DPI64104</t>
+          <t>DPI64176</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>105.14</v>
+        <v>51.79</v>
       </c>
       <c r="E456" t="n">
         <v>980</v>
       </c>
       <c r="F456" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G456" t="n">
-        <v>10.73</v>
+        <v>5.29</v>
       </c>
       <c r="H456" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I456" t="n">
-        <v>153461.79</v>
+        <v>75536.19</v>
       </c>
     </row>
     <row r="457">
@@ -16408,31 +16408,31 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>DPI64236</t>
+          <t>DPI66460</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>69.73999999999999</v>
+        <v>71.19</v>
       </c>
       <c r="E457" t="n">
         <v>980</v>
       </c>
       <c r="F457" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G457" t="n">
-        <v>7.12</v>
+        <v>7.26</v>
       </c>
       <c r="H457" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I457" t="n">
-        <v>101791.56</v>
+        <v>103824.89</v>
       </c>
     </row>
     <row r="458">
@@ -16443,31 +16443,31 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>DPI66734</t>
+          <t>DPI63993</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>111.78</v>
+        <v>56.56</v>
       </c>
       <c r="E458" t="n">
         <v>980</v>
       </c>
       <c r="F458" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G458" t="n">
-        <v>11.41</v>
+        <v>5.77</v>
       </c>
       <c r="H458" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I458" t="n">
-        <v>163162.37</v>
+        <v>82486.36</v>
       </c>
     </row>
     <row r="459">
@@ -16478,31 +16478,31 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>DPI70073</t>
+          <t>DPI64044</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>53.01</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E459" t="n">
         <v>980</v>
       </c>
       <c r="F459" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G459" t="n">
-        <v>5.41</v>
+        <v>6.73</v>
       </c>
       <c r="H459" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I459" t="n">
-        <v>77371.36</v>
+        <v>96240.39999999999</v>
       </c>
     </row>
     <row r="460">
@@ -16513,31 +16513,31 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>DPI70038</t>
+          <t>DPI64639</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>100.52</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="E460" t="n">
         <v>980</v>
       </c>
       <c r="F460" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G460" t="n">
-        <v>10.26</v>
+        <v>7.84</v>
       </c>
       <c r="H460" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I460" t="n">
-        <v>146720.05</v>
+        <v>111994.48</v>
       </c>
     </row>
     <row r="461">
@@ -16553,26 +16553,26 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>DPI64149</t>
+          <t>DPI64758</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>43.53</v>
+        <v>99.53</v>
       </c>
       <c r="E461" t="n">
         <v>980</v>
       </c>
       <c r="F461" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G461" t="n">
-        <v>4.44</v>
+        <v>10.16</v>
       </c>
       <c r="H461" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I461" t="n">
-        <v>63532.36</v>
+        <v>116509.13</v>
       </c>
     </row>
     <row r="462">
@@ -16588,26 +16588,26 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>DPI66572</t>
+          <t>DPI66421</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>80.69</v>
+        <v>273.07</v>
       </c>
       <c r="E462" t="n">
         <v>980</v>
       </c>
       <c r="F462" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G462" t="n">
-        <v>8.23</v>
+        <v>27.86</v>
       </c>
       <c r="H462" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I462" t="n">
-        <v>117774.41</v>
+        <v>319641.14</v>
       </c>
     </row>
     <row r="463">
@@ -16623,26 +16623,26 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>DPI64234</t>
+          <t>DPI67128</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>68.98</v>
+        <v>107.28</v>
       </c>
       <c r="E463" t="n">
         <v>980</v>
       </c>
       <c r="F463" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G463" t="n">
-        <v>7.04</v>
+        <v>10.95</v>
       </c>
       <c r="H463" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I463" t="n">
-        <v>100683.02</v>
+        <v>125577.67</v>
       </c>
     </row>
     <row r="464">
@@ -16658,26 +16658,26 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>DPI64176</t>
+          <t>DPI70100</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>51.79</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E464" t="n">
         <v>980</v>
       </c>
       <c r="F464" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G464" t="n">
-        <v>5.29</v>
+        <v>6.67</v>
       </c>
       <c r="H464" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I464" t="n">
-        <v>75599.41</v>
+        <v>76551.61</v>
       </c>
     </row>
     <row r="465">
@@ -16693,26 +16693,26 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>DPI66460</t>
+          <t>DPI64303</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>71.19</v>
+        <v>103.22</v>
       </c>
       <c r="E465" t="n">
         <v>980</v>
       </c>
       <c r="F465" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G465" t="n">
-        <v>7.26</v>
+        <v>10.53</v>
       </c>
       <c r="H465" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I465" t="n">
-        <v>103911.8</v>
+        <v>120828.79</v>
       </c>
     </row>
     <row r="466">
@@ -16728,26 +16728,26 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>DPI63993</t>
+          <t>DPI66528</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>56.56</v>
+        <v>108.07</v>
       </c>
       <c r="E466" t="n">
         <v>980</v>
       </c>
       <c r="F466" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G466" t="n">
-        <v>5.77</v>
+        <v>11.03</v>
       </c>
       <c r="H466" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I466" t="n">
-        <v>82555.39999999999</v>
+        <v>126504.97</v>
       </c>
     </row>
     <row r="467">
@@ -16763,26 +16763,26 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DPI64044</t>
+          <t>DPI64692</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>65.98999999999999</v>
+        <v>133.08</v>
       </c>
       <c r="E467" t="n">
         <v>980</v>
       </c>
       <c r="F467" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G467" t="n">
-        <v>6.73</v>
+        <v>13.58</v>
       </c>
       <c r="H467" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I467" t="n">
-        <v>96320.95</v>
+        <v>155778.71</v>
       </c>
     </row>
     <row r="468">
@@ -16798,26 +16798,26 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>DPI64639</t>
+          <t>DPI67198</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>76.79000000000001</v>
+        <v>90.89</v>
       </c>
       <c r="E468" t="n">
         <v>980</v>
       </c>
       <c r="F468" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G468" t="n">
-        <v>7.84</v>
+        <v>9.27</v>
       </c>
       <c r="H468" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I468" t="n">
-        <v>112088.22</v>
+        <v>106392.84</v>
       </c>
     </row>
     <row r="469">
@@ -16833,26 +16833,26 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>DPI64409</t>
+          <t>DPI64104</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>92.92</v>
+        <v>105.14</v>
       </c>
       <c r="E469" t="n">
         <v>980</v>
       </c>
       <c r="F469" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G469" t="n">
-        <v>9.48</v>
+        <v>10.73</v>
       </c>
       <c r="H469" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I469" t="n">
-        <v>108820.44</v>
+        <v>138497.76</v>
       </c>
     </row>
     <row r="470">
@@ -16868,26 +16868,26 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>DPI66421</t>
+          <t>DPI66646</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>273.07</v>
+        <v>154.63</v>
       </c>
       <c r="E470" t="n">
         <v>980</v>
       </c>
       <c r="F470" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G470" t="n">
-        <v>27.86</v>
+        <v>15.78</v>
       </c>
       <c r="H470" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I470" t="n">
-        <v>319789.24</v>
+        <v>203694.74</v>
       </c>
     </row>
     <row r="471">
@@ -16903,26 +16903,26 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>DPI67128</t>
+          <t>DPI70041</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>107.28</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="E471" t="n">
         <v>980</v>
       </c>
       <c r="F471" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G471" t="n">
-        <v>10.95</v>
+        <v>7.42</v>
       </c>
       <c r="H471" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I471" t="n">
-        <v>125635.86</v>
+        <v>95744.8</v>
       </c>
     </row>
     <row r="472">
@@ -16938,26 +16938,26 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>DPI70100</t>
+          <t>DPI67024</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>65.40000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="E472" t="n">
         <v>980</v>
       </c>
       <c r="F472" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G472" t="n">
-        <v>6.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H472" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I472" t="n">
-        <v>76587.08</v>
+        <v>127316.9</v>
       </c>
     </row>
     <row r="473">
@@ -16973,26 +16973,26 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>DPI64303</t>
+          <t>DPI64288</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>103.22</v>
+        <v>116.14</v>
       </c>
       <c r="E473" t="n">
         <v>980</v>
       </c>
       <c r="F473" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G473" t="n">
-        <v>10.53</v>
+        <v>11.85</v>
       </c>
       <c r="H473" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I473" t="n">
-        <v>120884.77</v>
+        <v>152992</v>
       </c>
     </row>
     <row r="474">
@@ -17008,26 +17008,26 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>DPI66528</t>
+          <t>DPI64352</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>108.07</v>
+        <v>100.22</v>
       </c>
       <c r="E474" t="n">
         <v>980</v>
       </c>
       <c r="F474" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G474" t="n">
-        <v>11.03</v>
+        <v>10.23</v>
       </c>
       <c r="H474" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I474" t="n">
-        <v>126563.59</v>
+        <v>132022.03</v>
       </c>
     </row>
     <row r="475">
@@ -17043,26 +17043,26 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>DPI64692</t>
+          <t>DPI67031</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>133.08</v>
+        <v>136.7</v>
       </c>
       <c r="E475" t="n">
         <v>980</v>
       </c>
       <c r="F475" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G475" t="n">
-        <v>13.58</v>
+        <v>13.95</v>
       </c>
       <c r="H475" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I475" t="n">
-        <v>155850.89</v>
+        <v>180081.53</v>
       </c>
     </row>
     <row r="476">
@@ -17078,26 +17078,26 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>DPI67198</t>
+          <t>DPI66264</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>90.89</v>
+        <v>147.75</v>
       </c>
       <c r="E476" t="n">
         <v>980</v>
       </c>
       <c r="F476" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G476" t="n">
-        <v>9.27</v>
+        <v>15.08</v>
       </c>
       <c r="H476" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I476" t="n">
-        <v>106442.13</v>
+        <v>194629.81</v>
       </c>
     </row>
     <row r="477">

--- a/store_wise_monthly_costs.xlsx
+++ b/store_wise_monthly_costs.xlsx
@@ -5878,11 +5878,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DPI66387</t>
+          <t>DPI66339</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>108.78</v>
+        <v>131.28</v>
       </c>
       <c r="E156" t="n">
         <v>980</v>
@@ -5891,13 +5891,13 @@
         <v>972</v>
       </c>
       <c r="G156" t="n">
-        <v>11.1</v>
+        <v>13.4</v>
       </c>
       <c r="H156" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I156" t="n">
-        <v>44354.55</v>
+        <v>53130.91</v>
       </c>
     </row>
     <row r="157">
@@ -5913,11 +5913,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DPI70316</t>
+          <t>DFT80044</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>48.44</v>
+        <v>26.45</v>
       </c>
       <c r="E157" t="n">
         <v>980</v>
@@ -5926,13 +5926,13 @@
         <v>972</v>
       </c>
       <c r="G157" t="n">
-        <v>4.94</v>
+        <v>2.7</v>
       </c>
       <c r="H157" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I157" t="n">
-        <v>19749.25</v>
+        <v>10703.17</v>
       </c>
     </row>
     <row r="158">
@@ -5964,10 +5964,10 @@
         <v>8.1</v>
       </c>
       <c r="H158" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I158" t="n">
-        <v>32367.52</v>
+        <v>32126.24</v>
       </c>
     </row>
     <row r="159">
@@ -5999,10 +5999,10 @@
         <v>3.6</v>
       </c>
       <c r="H159" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I159" t="n">
-        <v>14365.11</v>
+        <v>14258.02</v>
       </c>
     </row>
     <row r="160">
@@ -6034,10 +6034,10 @@
         <v>7.37</v>
       </c>
       <c r="H160" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I160" t="n">
-        <v>29445.08</v>
+        <v>29225.58</v>
       </c>
     </row>
     <row r="161">
@@ -6069,10 +6069,10 @@
         <v>6.08</v>
       </c>
       <c r="H161" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I161" t="n">
-        <v>24304.06</v>
+        <v>24122.88</v>
       </c>
     </row>
     <row r="162">
@@ -6104,10 +6104,10 @@
         <v>2.79</v>
       </c>
       <c r="H162" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I162" t="n">
-        <v>11157.79</v>
+        <v>11074.62</v>
       </c>
     </row>
     <row r="163">
@@ -6139,10 +6139,10 @@
         <v>1.31</v>
       </c>
       <c r="H163" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I163" t="n">
-        <v>5229.29</v>
+        <v>5190.31</v>
       </c>
     </row>
     <row r="164">
@@ -6174,10 +6174,10 @@
         <v>11.92</v>
       </c>
       <c r="H164" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I164" t="n">
-        <v>47612.69</v>
+        <v>47257.76</v>
       </c>
     </row>
     <row r="165">
@@ -6209,10 +6209,10 @@
         <v>12.32</v>
       </c>
       <c r="H165" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I165" t="n">
-        <v>49246.75</v>
+        <v>48879.65</v>
       </c>
     </row>
     <row r="166">
@@ -6244,10 +6244,10 @@
         <v>10.17</v>
       </c>
       <c r="H166" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I166" t="n">
-        <v>40639.69</v>
+        <v>40336.74</v>
       </c>
     </row>
     <row r="167">
@@ -6279,10 +6279,10 @@
         <v>6.07</v>
       </c>
       <c r="H167" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I167" t="n">
-        <v>24242.22</v>
+        <v>24061.51</v>
       </c>
     </row>
     <row r="168">
@@ -6314,10 +6314,10 @@
         <v>13.43</v>
       </c>
       <c r="H168" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
       <c r="I168" t="n">
-        <v>53671.03</v>
+        <v>53270.94</v>
       </c>
     </row>
     <row r="169">
@@ -6333,26 +6333,26 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DPI70081</t>
+          <t>DPI64052</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>54.11</v>
+        <v>192.78</v>
       </c>
       <c r="E169" t="n">
         <v>980</v>
       </c>
       <c r="F169" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G169" t="n">
-        <v>5.52</v>
+        <v>19.67</v>
       </c>
       <c r="H169" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I169" t="n">
-        <v>24900.89</v>
+        <v>90724.53999999999</v>
       </c>
     </row>
     <row r="170">
@@ -6368,26 +6368,26 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DPI64624</t>
+          <t>DPI67187</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>119.04</v>
+        <v>102.41</v>
       </c>
       <c r="E170" t="n">
         <v>980</v>
       </c>
       <c r="F170" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G170" t="n">
-        <v>12.15</v>
+        <v>10.45</v>
       </c>
       <c r="H170" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I170" t="n">
-        <v>54778.25</v>
+        <v>48197.59</v>
       </c>
     </row>
     <row r="171">
@@ -6403,26 +6403,26 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DPI66102</t>
+          <t>DFT80077</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>124.24</v>
+        <v>46.73</v>
       </c>
       <c r="E171" t="n">
         <v>980</v>
       </c>
       <c r="F171" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G171" t="n">
-        <v>12.68</v>
+        <v>4.77</v>
       </c>
       <c r="H171" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I171" t="n">
-        <v>57174.23</v>
+        <v>21991.92</v>
       </c>
     </row>
     <row r="172">
@@ -6438,26 +6438,26 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DPI64166</t>
+          <t>DPI64666</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>56.77</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="E172" t="n">
         <v>980</v>
       </c>
       <c r="F172" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G172" t="n">
-        <v>5.79</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H172" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I172" t="n">
-        <v>26124.7</v>
+        <v>44035.93</v>
       </c>
     </row>
     <row r="173">
@@ -6473,26 +6473,26 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>DPI66384</t>
+          <t>DPI70190</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>156.23</v>
+        <v>60.35</v>
       </c>
       <c r="E173" t="n">
         <v>980</v>
       </c>
       <c r="F173" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G173" t="n">
-        <v>15.94</v>
+        <v>6.16</v>
       </c>
       <c r="H173" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I173" t="n">
-        <v>71892.25999999999</v>
+        <v>28402.73</v>
       </c>
     </row>
     <row r="174">
@@ -6508,26 +6508,26 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DPI66408</t>
+          <t>DPI70253</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>147.34</v>
+        <v>56.09</v>
       </c>
       <c r="E174" t="n">
         <v>980</v>
       </c>
       <c r="F174" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G174" t="n">
-        <v>15.03</v>
+        <v>5.72</v>
       </c>
       <c r="H174" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I174" t="n">
-        <v>67800.67</v>
+        <v>26394.3</v>
       </c>
     </row>
     <row r="175">
@@ -6543,26 +6543,26 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DPI64392</t>
+          <t>DPI64056</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>79.42</v>
+        <v>84.19</v>
       </c>
       <c r="E175" t="n">
         <v>980</v>
       </c>
       <c r="F175" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G175" t="n">
-        <v>8.1</v>
+        <v>8.59</v>
       </c>
       <c r="H175" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I175" t="n">
-        <v>36548.72</v>
+        <v>39620.65</v>
       </c>
     </row>
     <row r="176">
@@ -6578,26 +6578,26 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>DPI66618</t>
+          <t>DPI67074</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>133.15</v>
+        <v>115.58</v>
       </c>
       <c r="E176" t="n">
         <v>980</v>
       </c>
       <c r="F176" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G176" t="n">
-        <v>13.59</v>
+        <v>11.79</v>
       </c>
       <c r="H176" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I176" t="n">
-        <v>61272.11</v>
+        <v>54391.36</v>
       </c>
     </row>
     <row r="177">
@@ -6613,26 +6613,26 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>DPI66653</t>
+          <t>DPI64628</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>109.8</v>
+        <v>83.72</v>
       </c>
       <c r="E177" t="n">
         <v>980</v>
       </c>
       <c r="F177" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G177" t="n">
-        <v>11.2</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H177" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
       <c r="I177" t="n">
-        <v>50526.93</v>
+        <v>39398.19</v>
       </c>
     </row>
     <row r="178">
@@ -6643,31 +6643,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>DPI67178</t>
+          <t>DPI64119</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>83.31</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="E178" t="n">
         <v>980</v>
       </c>
       <c r="F178" t="n">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="G178" t="n">
-        <v>8.5</v>
+        <v>9.33</v>
       </c>
       <c r="H178" t="n">
-        <v>438859.68</v>
+        <v>461199.37</v>
       </c>
       <c r="I178" t="n">
-        <v>37306.54</v>
+        <v>43041.05</v>
       </c>
     </row>
     <row r="179">
@@ -6678,31 +6678,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>DPI64297</t>
+          <t>DFT80078</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>126.1</v>
+        <v>42.46</v>
       </c>
       <c r="E179" t="n">
         <v>980</v>
       </c>
       <c r="F179" t="n">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="G179" t="n">
-        <v>12.87</v>
+        <v>4.33</v>
       </c>
       <c r="H179" t="n">
-        <v>438859.68</v>
+        <v>461199.37</v>
       </c>
       <c r="I179" t="n">
-        <v>56468.7</v>
+        <v>19982.53</v>
       </c>
     </row>
     <row r="180">
@@ -6718,26 +6718,26 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>DPI63915</t>
+          <t>DPI64450</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>131.72</v>
+        <v>49.06</v>
       </c>
       <c r="E180" t="n">
         <v>980</v>
       </c>
       <c r="F180" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G180" t="n">
-        <v>13.44</v>
+        <v>5.01</v>
       </c>
       <c r="H180" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
       <c r="I180" t="n">
-        <v>58985.83</v>
+        <v>27026.52</v>
       </c>
     </row>
     <row r="181">
@@ -6753,26 +6753,26 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DPI64724</t>
+          <t>DPI66387</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>84.75</v>
+        <v>108.78</v>
       </c>
       <c r="E181" t="n">
         <v>980</v>
       </c>
       <c r="F181" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G181" t="n">
-        <v>8.65</v>
+        <v>11.1</v>
       </c>
       <c r="H181" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
       <c r="I181" t="n">
-        <v>37951.29</v>
+        <v>59924.2</v>
       </c>
     </row>
     <row r="182">
@@ -6788,26 +6788,26 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>DPI66742</t>
+          <t>DPI64301</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>200.32</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="E182" t="n">
         <v>980</v>
       </c>
       <c r="F182" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G182" t="n">
-        <v>20.44</v>
+        <v>10.15</v>
       </c>
       <c r="H182" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
       <c r="I182" t="n">
-        <v>89707.92999999999</v>
+        <v>54814.55</v>
       </c>
     </row>
     <row r="183">
@@ -6823,26 +6823,26 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>DPI66067</t>
+          <t>DPI66590</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>139.3</v>
+        <v>142.23</v>
       </c>
       <c r="E183" t="n">
         <v>980</v>
       </c>
       <c r="F183" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G183" t="n">
-        <v>14.21</v>
+        <v>14.51</v>
       </c>
       <c r="H183" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
       <c r="I183" t="n">
-        <v>62382.07</v>
+        <v>78351.61</v>
       </c>
     </row>
     <row r="184">
@@ -6858,26 +6858,26 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>DPI70213</t>
+          <t>DPI70316</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>77.68000000000001</v>
+        <v>48.44</v>
       </c>
       <c r="E184" t="n">
         <v>980</v>
       </c>
       <c r="F184" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G184" t="n">
-        <v>7.93</v>
+        <v>4.94</v>
       </c>
       <c r="H184" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
       <c r="I184" t="n">
-        <v>34788.32</v>
+        <v>26681.77</v>
       </c>
     </row>
     <row r="185">
@@ -6893,26 +6893,26 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>DPI70105</t>
+          <t>DPI66096</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>75.19</v>
+        <v>156.26</v>
       </c>
       <c r="E185" t="n">
         <v>980</v>
       </c>
       <c r="F185" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G185" t="n">
-        <v>7.67</v>
+        <v>15.95</v>
       </c>
       <c r="H185" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
       <c r="I185" t="n">
-        <v>33673.03</v>
+        <v>86079.97</v>
       </c>
     </row>
     <row r="186">
@@ -6928,26 +6928,26 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>DFT80077</t>
+          <t>DPI64018</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>46.73</v>
+        <v>161.85</v>
       </c>
       <c r="E186" t="n">
         <v>980</v>
       </c>
       <c r="F186" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G186" t="n">
-        <v>4.77</v>
+        <v>16.52</v>
       </c>
       <c r="H186" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
       <c r="I186" t="n">
-        <v>20926.67</v>
+        <v>89157.98</v>
       </c>
     </row>
     <row r="187">
@@ -6958,31 +6958,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>DPI64450</t>
+          <t>DPI66736</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>49.06</v>
+        <v>136.37</v>
       </c>
       <c r="E187" t="n">
         <v>980</v>
       </c>
       <c r="F187" t="n">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="G187" t="n">
-        <v>5.01</v>
+        <v>13.92</v>
       </c>
       <c r="H187" t="n">
-        <v>539070.01</v>
+        <v>539849.98</v>
       </c>
       <c r="I187" t="n">
-        <v>26987.47</v>
+        <v>75120.60000000001</v>
       </c>
     </row>
     <row r="188">
@@ -6993,31 +6993,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>DPI64686</t>
+          <t>DPI70229</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>97.63</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E188" t="n">
         <v>980</v>
       </c>
       <c r="F188" t="n">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="G188" t="n">
-        <v>9.960000000000001</v>
+        <v>6.72</v>
       </c>
       <c r="H188" t="n">
-        <v>539070.01</v>
+        <v>539849.98</v>
       </c>
       <c r="I188" t="n">
-        <v>53703.28</v>
+        <v>36272.11</v>
       </c>
     </row>
     <row r="189">
@@ -7033,26 +7033,26 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DPI66339</t>
+          <t>DPI66653</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>131.28</v>
+        <v>109.8</v>
       </c>
       <c r="E189" t="n">
         <v>980</v>
       </c>
       <c r="F189" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="G189" t="n">
-        <v>13.4</v>
+        <v>11.2</v>
       </c>
       <c r="H189" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
       <c r="I189" t="n">
-        <v>72215.91</v>
+        <v>50418.44</v>
       </c>
     </row>
     <row r="190">
@@ -7068,26 +7068,26 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>DPI66590</t>
+          <t>DPI64624</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>142.23</v>
+        <v>119.04</v>
       </c>
       <c r="E190" t="n">
         <v>980</v>
       </c>
       <c r="F190" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="G190" t="n">
-        <v>14.51</v>
+        <v>12.15</v>
       </c>
       <c r="H190" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
       <c r="I190" t="n">
-        <v>78238.41</v>
+        <v>54660.63</v>
       </c>
     </row>
     <row r="191">
@@ -7103,26 +7103,26 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>DFT80044</t>
+          <t>DPI66102</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>26.45</v>
+        <v>124.24</v>
       </c>
       <c r="E191" t="n">
         <v>980</v>
       </c>
       <c r="F191" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="G191" t="n">
-        <v>2.7</v>
+        <v>12.68</v>
       </c>
       <c r="H191" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
       <c r="I191" t="n">
-        <v>14547.82</v>
+        <v>57051.47</v>
       </c>
     </row>
     <row r="192">
@@ -7138,26 +7138,26 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DPI66096</t>
+          <t>DPI64166</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>156.26</v>
+        <v>56.77</v>
       </c>
       <c r="E192" t="n">
         <v>980</v>
       </c>
       <c r="F192" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="G192" t="n">
-        <v>15.95</v>
+        <v>5.79</v>
       </c>
       <c r="H192" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
       <c r="I192" t="n">
-        <v>85955.60000000001</v>
+        <v>26068.6</v>
       </c>
     </row>
     <row r="193">
@@ -7173,26 +7173,26 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DPI64018</t>
+          <t>DPI66384</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>161.85</v>
+        <v>156.23</v>
       </c>
       <c r="E193" t="n">
         <v>980</v>
       </c>
       <c r="F193" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="G193" t="n">
-        <v>16.52</v>
+        <v>15.94</v>
       </c>
       <c r="H193" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
       <c r="I193" t="n">
-        <v>89029.17</v>
+        <v>71737.89999999999</v>
       </c>
     </row>
     <row r="194">
@@ -7208,26 +7208,26 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DPI70229</t>
+          <t>DPI64392</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>65.84999999999999</v>
+        <v>79.42</v>
       </c>
       <c r="E194" t="n">
         <v>980</v>
       </c>
       <c r="F194" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72</v>
+        <v>8.1</v>
       </c>
       <c r="H194" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
       <c r="I194" t="n">
-        <v>36219.71</v>
+        <v>36470.24</v>
       </c>
     </row>
     <row r="195">
@@ -7243,26 +7243,26 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DPI66736</t>
+          <t>DPI66408</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>136.37</v>
+        <v>147.34</v>
       </c>
       <c r="E195" t="n">
         <v>980</v>
       </c>
       <c r="F195" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="G195" t="n">
-        <v>13.92</v>
+        <v>15.03</v>
       </c>
       <c r="H195" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
       <c r="I195" t="n">
-        <v>75012.07000000001</v>
+        <v>67655.09</v>
       </c>
     </row>
     <row r="196">
@@ -7273,31 +7273,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DPI66658</t>
+          <t>DPI66618</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>78.34999999999999</v>
+        <v>133.15</v>
       </c>
       <c r="E196" t="n">
         <v>980</v>
       </c>
       <c r="F196" t="n">
-        <v>979</v>
+        <v>925</v>
       </c>
       <c r="G196" t="n">
-        <v>8</v>
+        <v>13.59</v>
       </c>
       <c r="H196" t="n">
-        <v>421596.09</v>
+        <v>450001.99</v>
       </c>
       <c r="I196" t="n">
-        <v>33707.47</v>
+        <v>61140.54</v>
       </c>
     </row>
     <row r="197">
@@ -7323,16 +7323,16 @@
         <v>980</v>
       </c>
       <c r="F197" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G197" t="n">
         <v>21.94</v>
       </c>
       <c r="H197" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I197" t="n">
-        <v>92497.14999999999</v>
+        <v>92668.75</v>
       </c>
     </row>
     <row r="198">
@@ -7358,16 +7358,16 @@
         <v>980</v>
       </c>
       <c r="F198" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G198" t="n">
         <v>10.99</v>
       </c>
       <c r="H198" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I198" t="n">
-        <v>46329.24</v>
+        <v>46415.19</v>
       </c>
     </row>
     <row r="199">
@@ -7393,16 +7393,16 @@
         <v>980</v>
       </c>
       <c r="F199" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G199" t="n">
         <v>11.66</v>
       </c>
       <c r="H199" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I199" t="n">
-        <v>49152.81</v>
+        <v>49244</v>
       </c>
     </row>
     <row r="200">
@@ -7428,16 +7428,16 @@
         <v>980</v>
       </c>
       <c r="F200" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G200" t="n">
         <v>5.48</v>
       </c>
       <c r="H200" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I200" t="n">
-        <v>23122.65</v>
+        <v>23165.55</v>
       </c>
     </row>
     <row r="201">
@@ -7463,16 +7463,16 @@
         <v>980</v>
       </c>
       <c r="F201" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G201" t="n">
         <v>10.35</v>
       </c>
       <c r="H201" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I201" t="n">
-        <v>43651.54</v>
+        <v>43732.52</v>
       </c>
     </row>
     <row r="202">
@@ -7498,16 +7498,16 @@
         <v>980</v>
       </c>
       <c r="F202" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G202" t="n">
         <v>8.789999999999999</v>
       </c>
       <c r="H202" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I202" t="n">
-        <v>37048.01</v>
+        <v>37116.74</v>
       </c>
     </row>
     <row r="203">
@@ -7533,16 +7533,16 @@
         <v>980</v>
       </c>
       <c r="F203" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G203" t="n">
         <v>8.75</v>
       </c>
       <c r="H203" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I203" t="n">
-        <v>36877.57</v>
+        <v>36945.98</v>
       </c>
     </row>
     <row r="204">
@@ -7568,16 +7568,16 @@
         <v>980</v>
       </c>
       <c r="F204" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G204" t="n">
         <v>13.96</v>
       </c>
       <c r="H204" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
       <c r="I204" t="n">
-        <v>58834.08</v>
+        <v>58943.23</v>
       </c>
     </row>
     <row r="205">
@@ -7588,31 +7588,31 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DPI70109</t>
+          <t>DPI66636</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>64.45999999999999</v>
+        <v>75.55</v>
       </c>
       <c r="E205" t="n">
         <v>980</v>
       </c>
       <c r="F205" t="n">
-        <v>824</v>
+        <v>977</v>
       </c>
       <c r="G205" t="n">
-        <v>6.58</v>
+        <v>7.71</v>
       </c>
       <c r="H205" t="n">
-        <v>557988.3</v>
+        <v>422378.22</v>
       </c>
       <c r="I205" t="n">
-        <v>36701.33</v>
+        <v>32561.74</v>
       </c>
     </row>
     <row r="206">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DPI66129</t>
+          <t>DPI70109</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>200.46</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="E206" t="n">
         <v>980</v>
@@ -7641,13 +7641,13 @@
         <v>824</v>
       </c>
       <c r="G206" t="n">
-        <v>20.46</v>
+        <v>6.58</v>
       </c>
       <c r="H206" t="n">
         <v>557988.3</v>
       </c>
       <c r="I206" t="n">
-        <v>114138.12</v>
+        <v>36701.33</v>
       </c>
     </row>
     <row r="207">
@@ -7663,11 +7663,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DPI64495</t>
+          <t>DPI66129</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>186.61</v>
+        <v>200.46</v>
       </c>
       <c r="E207" t="n">
         <v>980</v>
@@ -7676,13 +7676,13 @@
         <v>824</v>
       </c>
       <c r="G207" t="n">
-        <v>19.04</v>
+        <v>20.46</v>
       </c>
       <c r="H207" t="n">
         <v>557988.3</v>
       </c>
       <c r="I207" t="n">
-        <v>106249.97</v>
+        <v>114138.12</v>
       </c>
     </row>
     <row r="208">
@@ -7698,11 +7698,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DFT80080</t>
+          <t>DPI64495</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>38.28</v>
+        <v>186.61</v>
       </c>
       <c r="E208" t="n">
         <v>980</v>
@@ -7711,13 +7711,13 @@
         <v>824</v>
       </c>
       <c r="G208" t="n">
-        <v>3.91</v>
+        <v>19.04</v>
       </c>
       <c r="H208" t="n">
         <v>557988.3</v>
       </c>
       <c r="I208" t="n">
-        <v>21793.39</v>
+        <v>106249.97</v>
       </c>
     </row>
     <row r="209">
@@ -7733,11 +7733,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DPI64548</t>
+          <t>DFT80080</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>118.62</v>
+        <v>38.28</v>
       </c>
       <c r="E209" t="n">
         <v>980</v>
@@ -7746,13 +7746,13 @@
         <v>824</v>
       </c>
       <c r="G209" t="n">
-        <v>12.1</v>
+        <v>3.91</v>
       </c>
       <c r="H209" t="n">
         <v>557988.3</v>
       </c>
       <c r="I209" t="n">
-        <v>67537.16</v>
+        <v>21793.39</v>
       </c>
     </row>
     <row r="210">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DPI70107</t>
+          <t>DPI64548</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>57.32</v>
+        <v>118.62</v>
       </c>
       <c r="E210" t="n">
         <v>980</v>
@@ -7781,13 +7781,13 @@
         <v>824</v>
       </c>
       <c r="G210" t="n">
-        <v>5.85</v>
+        <v>12.1</v>
       </c>
       <c r="H210" t="n">
         <v>557988.3</v>
       </c>
       <c r="I210" t="n">
-        <v>32634.24</v>
+        <v>67537.16</v>
       </c>
     </row>
     <row r="211">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>DPI70214</t>
+          <t>DPI70107</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>53.89</v>
+        <v>57.32</v>
       </c>
       <c r="E211" t="n">
         <v>980</v>
@@ -7816,13 +7816,13 @@
         <v>824</v>
       </c>
       <c r="G211" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="H211" t="n">
         <v>557988.3</v>
       </c>
       <c r="I211" t="n">
-        <v>30685.39</v>
+        <v>32634.24</v>
       </c>
     </row>
     <row r="212">
@@ -7838,11 +7838,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>DPI66634</t>
+          <t>DPI70214</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>104.69</v>
+        <v>53.89</v>
       </c>
       <c r="E212" t="n">
         <v>980</v>
@@ -7851,13 +7851,13 @@
         <v>824</v>
       </c>
       <c r="G212" t="n">
-        <v>10.68</v>
+        <v>5.5</v>
       </c>
       <c r="H212" t="n">
         <v>557988.3</v>
       </c>
       <c r="I212" t="n">
-        <v>59608.09</v>
+        <v>30685.39</v>
       </c>
     </row>
     <row r="213">
@@ -7868,31 +7868,31 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DPI64052</t>
+          <t>DPI66634</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>192.78</v>
+        <v>104.69</v>
       </c>
       <c r="E213" t="n">
         <v>980</v>
       </c>
       <c r="F213" t="n">
-        <v>956</v>
+        <v>824</v>
       </c>
       <c r="G213" t="n">
-        <v>19.67</v>
+        <v>10.68</v>
       </c>
       <c r="H213" t="n">
-        <v>448403.88</v>
+        <v>557988.3</v>
       </c>
       <c r="I213" t="n">
-        <v>88207.48</v>
+        <v>59608.09</v>
       </c>
     </row>
     <row r="214">
@@ -7908,26 +7908,26 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DPI67187</t>
+          <t>DPI70142</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>102.41</v>
+        <v>63.66</v>
       </c>
       <c r="E214" t="n">
         <v>980</v>
       </c>
       <c r="F214" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G214" t="n">
-        <v>10.45</v>
+        <v>6.5</v>
       </c>
       <c r="H214" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I214" t="n">
-        <v>46860.4</v>
+        <v>19458.58</v>
       </c>
     </row>
     <row r="215">
@@ -7943,26 +7943,26 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DPI64666</t>
+          <t>DPI66069</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>93.56999999999999</v>
+        <v>182.8</v>
       </c>
       <c r="E215" t="n">
         <v>980</v>
       </c>
       <c r="F215" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G215" t="n">
-        <v>9.550000000000001</v>
+        <v>18.65</v>
       </c>
       <c r="H215" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I215" t="n">
-        <v>42814.2</v>
+        <v>55873.19</v>
       </c>
     </row>
     <row r="216">
@@ -7978,26 +7978,26 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DPI70190</t>
+          <t>DPI64686</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>60.35</v>
+        <v>97.63</v>
       </c>
       <c r="E216" t="n">
         <v>980</v>
       </c>
       <c r="F216" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G216" t="n">
-        <v>6.16</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H216" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I216" t="n">
-        <v>27614.72</v>
+        <v>29841.03</v>
       </c>
     </row>
     <row r="217">
@@ -8013,26 +8013,26 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DPI70253</t>
+          <t>DPI70255</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>56.09</v>
+        <v>63.7</v>
       </c>
       <c r="E217" t="n">
         <v>980</v>
       </c>
       <c r="F217" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G217" t="n">
-        <v>5.72</v>
+        <v>6.5</v>
       </c>
       <c r="H217" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I217" t="n">
-        <v>25662.02</v>
+        <v>19468.86</v>
       </c>
     </row>
     <row r="218">
@@ -8048,26 +8048,26 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DPI64056</t>
+          <t>DPI66645</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>84.19</v>
+        <v>127.76</v>
       </c>
       <c r="E218" t="n">
         <v>980</v>
       </c>
       <c r="F218" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G218" t="n">
-        <v>8.59</v>
+        <v>13.04</v>
       </c>
       <c r="H218" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I218" t="n">
-        <v>38521.42</v>
+        <v>39050.71</v>
       </c>
     </row>
     <row r="219">
@@ -8083,26 +8083,26 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>DPI67074</t>
+          <t>DPI64244</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>115.58</v>
+        <v>126.9</v>
       </c>
       <c r="E219" t="n">
         <v>980</v>
       </c>
       <c r="F219" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G219" t="n">
-        <v>11.79</v>
+        <v>12.95</v>
       </c>
       <c r="H219" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I219" t="n">
-        <v>52882.33</v>
+        <v>38787.46</v>
       </c>
     </row>
     <row r="220">
@@ -8118,26 +8118,26 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>DPI64628</t>
+          <t>DPI66128</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>83.72</v>
+        <v>221.49</v>
       </c>
       <c r="E220" t="n">
         <v>980</v>
       </c>
       <c r="F220" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G220" t="n">
-        <v>8.539999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="H220" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I220" t="n">
-        <v>38305.13</v>
+        <v>67699.53999999999</v>
       </c>
     </row>
     <row r="221">
@@ -8153,26 +8153,26 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>DPI64119</t>
+          <t>DPI64094</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>91.45999999999999</v>
+        <v>75.03</v>
       </c>
       <c r="E221" t="n">
         <v>980</v>
       </c>
       <c r="F221" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G221" t="n">
-        <v>9.33</v>
+        <v>7.66</v>
       </c>
       <c r="H221" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
       <c r="I221" t="n">
-        <v>41846.93</v>
+        <v>22932.01</v>
       </c>
     </row>
     <row r="222">
@@ -8183,31 +8183,31 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DPI66636</t>
+          <t>DPI66597</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>75.55</v>
+        <v>90.83</v>
       </c>
       <c r="E222" t="n">
         <v>980</v>
       </c>
       <c r="F222" t="n">
-        <v>956</v>
+        <v>975</v>
       </c>
       <c r="G222" t="n">
-        <v>7.71</v>
+        <v>9.27</v>
       </c>
       <c r="H222" t="n">
-        <v>448403.88</v>
+        <v>248412.78</v>
       </c>
       <c r="I222" t="n">
-        <v>34568.1</v>
+        <v>23025.02</v>
       </c>
     </row>
     <row r="223">
@@ -8223,26 +8223,26 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DPI64431</t>
+          <t>DPI66373</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>78.73</v>
+        <v>98.05</v>
       </c>
       <c r="E223" t="n">
         <v>980</v>
       </c>
       <c r="F223" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G223" t="n">
-        <v>8.029999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="H223" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I223" t="n">
-        <v>21895.45</v>
+        <v>24854.26</v>
       </c>
     </row>
     <row r="224">
@@ -8258,26 +8258,26 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DPI66449</t>
+          <t>DPI66154</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>191.04</v>
+        <v>73.08</v>
       </c>
       <c r="E224" t="n">
         <v>980</v>
       </c>
       <c r="F224" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G224" t="n">
-        <v>19.49</v>
+        <v>7.46</v>
       </c>
       <c r="H224" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I224" t="n">
-        <v>53129.44</v>
+        <v>18524.47</v>
       </c>
     </row>
     <row r="225">
@@ -8293,26 +8293,26 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DPI67072</t>
+          <t>DPI64592</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>126.86</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="E225" t="n">
         <v>980</v>
       </c>
       <c r="F225" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G225" t="n">
-        <v>12.94</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H225" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I225" t="n">
-        <v>35279.6</v>
+        <v>24542.12</v>
       </c>
     </row>
     <row r="226">
@@ -8328,26 +8328,26 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DPI66153</t>
+          <t>DPI66449</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>97.33</v>
+        <v>191.04</v>
       </c>
       <c r="E226" t="n">
         <v>980</v>
       </c>
       <c r="F226" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G226" t="n">
-        <v>9.93</v>
+        <v>19.49</v>
       </c>
       <c r="H226" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I226" t="n">
-        <v>27067.14</v>
+        <v>48425.59</v>
       </c>
     </row>
     <row r="227">
@@ -8363,26 +8363,26 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>DPI66154</t>
+          <t>DPI67072</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>73.08</v>
+        <v>126.86</v>
       </c>
       <c r="E227" t="n">
         <v>980</v>
       </c>
       <c r="F227" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G227" t="n">
-        <v>7.46</v>
+        <v>12.94</v>
       </c>
       <c r="H227" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I227" t="n">
-        <v>20323.86</v>
+        <v>32156.1</v>
       </c>
     </row>
     <row r="228">
@@ -8398,26 +8398,26 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DPI66373</t>
+          <t>DPI66153</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>98.05</v>
+        <v>97.33</v>
       </c>
       <c r="E228" t="n">
         <v>980</v>
       </c>
       <c r="F228" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G228" t="n">
-        <v>10.01</v>
+        <v>9.93</v>
       </c>
       <c r="H228" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I228" t="n">
-        <v>27268.49</v>
+        <v>24670.74</v>
       </c>
     </row>
     <row r="229">
@@ -8443,16 +8443,16 @@
         <v>980</v>
       </c>
       <c r="F229" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G229" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="H229" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I229" t="n">
-        <v>22165.64</v>
+        <v>20203.19</v>
       </c>
     </row>
     <row r="230">
@@ -8478,16 +8478,16 @@
         <v>980</v>
       </c>
       <c r="F230" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="G230" t="n">
         <v>12.37</v>
       </c>
       <c r="H230" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
       <c r="I230" t="n">
-        <v>33707.34</v>
+        <v>30723.04</v>
       </c>
     </row>
     <row r="231">
@@ -8498,31 +8498,31 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DPI66597</t>
+          <t>DPI66179</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>90.83</v>
+        <v>130.31</v>
       </c>
       <c r="E231" t="n">
         <v>980</v>
       </c>
       <c r="F231" t="n">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="G231" t="n">
-        <v>9.27</v>
+        <v>13.3</v>
       </c>
       <c r="H231" t="n">
-        <v>272542.49</v>
+        <v>420179.55</v>
       </c>
       <c r="I231" t="n">
-        <v>25261.57</v>
+        <v>55869.31</v>
       </c>
     </row>
     <row r="232">
@@ -8538,11 +8538,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DPI66069</t>
+          <t>DPI64218</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>182.8</v>
+        <v>52.55</v>
       </c>
       <c r="E232" t="n">
         <v>980</v>
@@ -8551,13 +8551,13 @@
         <v>969</v>
       </c>
       <c r="G232" t="n">
-        <v>18.65</v>
+        <v>5.36</v>
       </c>
       <c r="H232" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I232" t="n">
-        <v>78206.03999999999</v>
+        <v>22532.55</v>
       </c>
     </row>
     <row r="233">
@@ -8589,10 +8589,10 @@
         <v>10.04</v>
       </c>
       <c r="H233" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I233" t="n">
-        <v>42104.05</v>
+        <v>42195.27</v>
       </c>
     </row>
     <row r="234">
@@ -8624,10 +8624,10 @@
         <v>3.93</v>
       </c>
       <c r="H234" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I234" t="n">
-        <v>16494.02</v>
+        <v>16529.76</v>
       </c>
     </row>
     <row r="235">
@@ -8659,10 +8659,10 @@
         <v>19.12</v>
       </c>
       <c r="H235" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I235" t="n">
-        <v>80179.39</v>
+        <v>80353.10000000001</v>
       </c>
     </row>
     <row r="236">
@@ -8694,10 +8694,10 @@
         <v>16.91</v>
       </c>
       <c r="H236" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I236" t="n">
-        <v>70893.8</v>
+        <v>71047.39</v>
       </c>
     </row>
     <row r="237">
@@ -8729,10 +8729,10 @@
         <v>16.03</v>
       </c>
       <c r="H237" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I237" t="n">
-        <v>67207.08</v>
+        <v>67352.67999999999</v>
       </c>
     </row>
     <row r="238">
@@ -8764,10 +8764,10 @@
         <v>8.44</v>
       </c>
       <c r="H238" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I238" t="n">
-        <v>35392.01</v>
+        <v>35468.68</v>
       </c>
     </row>
     <row r="239">
@@ -8799,10 +8799,10 @@
         <v>5.75</v>
       </c>
       <c r="H239" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
       <c r="I239" t="n">
-        <v>24094.02</v>
+        <v>24146.22</v>
       </c>
     </row>
     <row r="240">
@@ -8818,11 +8818,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DPI64436</t>
+          <t>DPI63958</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>86.91</v>
+        <v>120.83</v>
       </c>
       <c r="E240" t="n">
         <v>980</v>
@@ -8831,13 +8831,13 @@
         <v>961</v>
       </c>
       <c r="G240" t="n">
-        <v>8.869999999999999</v>
+        <v>12.33</v>
       </c>
       <c r="H240" t="n">
         <v>400421.92</v>
       </c>
       <c r="I240" t="n">
-        <v>35511.67</v>
+        <v>49372.39</v>
       </c>
     </row>
     <row r="241">
@@ -8853,11 +8853,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DPI64456</t>
+          <t>DPI64638</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>111.28</v>
+        <v>88.97</v>
       </c>
       <c r="E241" t="n">
         <v>980</v>
@@ -8866,13 +8866,13 @@
         <v>961</v>
       </c>
       <c r="G241" t="n">
-        <v>11.36</v>
+        <v>9.08</v>
       </c>
       <c r="H241" t="n">
         <v>400421.92</v>
       </c>
       <c r="I241" t="n">
-        <v>45470.26</v>
+        <v>36352.65</v>
       </c>
     </row>
     <row r="242">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DPI66946</t>
+          <t>DPI66307</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>126.11</v>
+        <v>125.94</v>
       </c>
       <c r="E242" t="n">
         <v>980</v>
@@ -8901,13 +8901,13 @@
         <v>961</v>
       </c>
       <c r="G242" t="n">
-        <v>12.87</v>
+        <v>12.85</v>
       </c>
       <c r="H242" t="n">
         <v>400421.92</v>
       </c>
       <c r="I242" t="n">
-        <v>51526.82</v>
+        <v>51458.3</v>
       </c>
     </row>
     <row r="243">
@@ -8923,11 +8923,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>DPI64136</t>
+          <t>DPI66039</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>70.68000000000001</v>
+        <v>114.76</v>
       </c>
       <c r="E243" t="n">
         <v>980</v>
@@ -8936,13 +8936,13 @@
         <v>961</v>
       </c>
       <c r="G243" t="n">
-        <v>7.21</v>
+        <v>11.71</v>
       </c>
       <c r="H243" t="n">
         <v>400421.92</v>
       </c>
       <c r="I243" t="n">
-        <v>28879.7</v>
+        <v>46891.43</v>
       </c>
     </row>
     <row r="244">
@@ -8993,11 +8993,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DPI66039</t>
+          <t>DPI64136</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>114.76</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="E245" t="n">
         <v>980</v>
@@ -9006,13 +9006,13 @@
         <v>961</v>
       </c>
       <c r="G245" t="n">
-        <v>11.71</v>
+        <v>7.21</v>
       </c>
       <c r="H245" t="n">
         <v>400421.92</v>
       </c>
       <c r="I245" t="n">
-        <v>46891.43</v>
+        <v>28879.7</v>
       </c>
     </row>
     <row r="246">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DPI66307</t>
+          <t>DPI66946</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>125.94</v>
+        <v>126.11</v>
       </c>
       <c r="E246" t="n">
         <v>980</v>
@@ -9041,13 +9041,13 @@
         <v>961</v>
       </c>
       <c r="G246" t="n">
-        <v>12.85</v>
+        <v>12.87</v>
       </c>
       <c r="H246" t="n">
         <v>400421.92</v>
       </c>
       <c r="I246" t="n">
-        <v>51458.3</v>
+        <v>51526.82</v>
       </c>
     </row>
     <row r="247">
@@ -9063,11 +9063,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DPI64638</t>
+          <t>DPI64456</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>88.97</v>
+        <v>111.28</v>
       </c>
       <c r="E247" t="n">
         <v>980</v>
@@ -9076,13 +9076,13 @@
         <v>961</v>
       </c>
       <c r="G247" t="n">
-        <v>9.08</v>
+        <v>11.36</v>
       </c>
       <c r="H247" t="n">
         <v>400421.92</v>
       </c>
       <c r="I247" t="n">
-        <v>36352.65</v>
+        <v>45470.26</v>
       </c>
     </row>
     <row r="248">
@@ -9098,11 +9098,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DPI63958</t>
+          <t>DPI64436</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>120.83</v>
+        <v>86.91</v>
       </c>
       <c r="E248" t="n">
         <v>980</v>
@@ -9111,13 +9111,13 @@
         <v>961</v>
       </c>
       <c r="G248" t="n">
-        <v>12.33</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H248" t="n">
         <v>400421.92</v>
       </c>
       <c r="I248" t="n">
-        <v>49372.39</v>
+        <v>35511.67</v>
       </c>
     </row>
     <row r="249">
@@ -9133,26 +9133,26 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DPI66179</t>
+          <t>DPI70009</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>130.31</v>
+        <v>60.09</v>
       </c>
       <c r="E249" t="n">
         <v>980</v>
       </c>
       <c r="F249" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G249" t="n">
-        <v>13.3</v>
+        <v>6.13</v>
       </c>
       <c r="H249" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I249" t="n">
-        <v>39894.66</v>
+        <v>26076.5</v>
       </c>
     </row>
     <row r="250">
@@ -9168,26 +9168,26 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>DPI64218</t>
+          <t>DPI66742</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>52.55</v>
+        <v>200.32</v>
       </c>
       <c r="E250" t="n">
         <v>980</v>
       </c>
       <c r="F250" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G250" t="n">
-        <v>5.36</v>
+        <v>20.44</v>
       </c>
       <c r="H250" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I250" t="n">
-        <v>16089.84</v>
+        <v>86926.96000000001</v>
       </c>
     </row>
     <row r="251">
@@ -9203,26 +9203,26 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>DPI64301</t>
+          <t>DPI67178</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>99.51000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E251" t="n">
         <v>980</v>
       </c>
       <c r="F251" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G251" t="n">
-        <v>10.15</v>
+        <v>8.5</v>
       </c>
       <c r="H251" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I251" t="n">
-        <v>30464.86</v>
+        <v>36150.03</v>
       </c>
     </row>
     <row r="252">
@@ -9238,26 +9238,26 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>DPI70255</t>
+          <t>DPI64724</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>63.7</v>
+        <v>84.75</v>
       </c>
       <c r="E252" t="n">
         <v>980</v>
       </c>
       <c r="F252" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G252" t="n">
-        <v>6.5</v>
+        <v>8.65</v>
       </c>
       <c r="H252" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I252" t="n">
-        <v>19501.08</v>
+        <v>36774.78</v>
       </c>
     </row>
     <row r="253">
@@ -9273,26 +9273,26 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DPI66645</t>
+          <t>DPI63915</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>127.76</v>
+        <v>131.72</v>
       </c>
       <c r="E253" t="n">
         <v>980</v>
       </c>
       <c r="F253" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G253" t="n">
-        <v>13.04</v>
+        <v>13.44</v>
       </c>
       <c r="H253" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I253" t="n">
-        <v>39115.33</v>
+        <v>57157.25</v>
       </c>
     </row>
     <row r="254">
@@ -9308,26 +9308,26 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DPI64244</t>
+          <t>DPI64297</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>126.9</v>
+        <v>126.1</v>
       </c>
       <c r="E254" t="n">
         <v>980</v>
       </c>
       <c r="F254" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G254" t="n">
-        <v>12.95</v>
+        <v>12.87</v>
       </c>
       <c r="H254" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I254" t="n">
-        <v>38851.66</v>
+        <v>54718.15</v>
       </c>
     </row>
     <row r="255">
@@ -9343,26 +9343,26 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>DPI66128</t>
+          <t>DPI66067</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>221.49</v>
+        <v>139.3</v>
       </c>
       <c r="E255" t="n">
         <v>980</v>
       </c>
       <c r="F255" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G255" t="n">
-        <v>22.6</v>
+        <v>14.21</v>
       </c>
       <c r="H255" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I255" t="n">
-        <v>67811.59</v>
+        <v>60448.2</v>
       </c>
     </row>
     <row r="256">
@@ -9378,26 +9378,26 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>DPI64094</t>
+          <t>DPI70213</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>75.03</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="E256" t="n">
         <v>980</v>
       </c>
       <c r="F256" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G256" t="n">
-        <v>7.66</v>
+        <v>7.93</v>
       </c>
       <c r="H256" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I256" t="n">
-        <v>22969.96</v>
+        <v>33709.87</v>
       </c>
     </row>
     <row r="257">
@@ -9413,26 +9413,26 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DPI70142</t>
+          <t>DPI70105</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>63.66</v>
+        <v>75.19</v>
       </c>
       <c r="E257" t="n">
         <v>980</v>
       </c>
       <c r="F257" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="G257" t="n">
-        <v>6.5</v>
+        <v>7.67</v>
       </c>
       <c r="H257" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
       <c r="I257" t="n">
-        <v>19490.78</v>
+        <v>32629.16</v>
       </c>
     </row>
     <row r="258">
@@ -9448,26 +9448,26 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DPI70009</t>
+          <t>DPI66923</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>60.09</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="E258" t="n">
         <v>980</v>
       </c>
       <c r="F258" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G258" t="n">
-        <v>6.13</v>
+        <v>7</v>
       </c>
       <c r="H258" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I258" t="n">
-        <v>28466.76</v>
+        <v>29987.26</v>
       </c>
     </row>
     <row r="259">
@@ -9483,26 +9483,26 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DPI63827</t>
+          <t>DPI66658</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>130.01</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E259" t="n">
         <v>980</v>
       </c>
       <c r="F259" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G259" t="n">
-        <v>13.27</v>
+        <v>8</v>
       </c>
       <c r="H259" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I259" t="n">
-        <v>61584.83</v>
+        <v>34266.9</v>
       </c>
     </row>
     <row r="260">
@@ -9518,26 +9518,26 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DPI66313</t>
+          <t>DPI70047</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>124.82</v>
+        <v>76.39</v>
       </c>
       <c r="E260" t="n">
         <v>980</v>
       </c>
       <c r="F260" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G260" t="n">
-        <v>12.74</v>
+        <v>7.8</v>
       </c>
       <c r="H260" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I260" t="n">
-        <v>59129.63</v>
+        <v>33409.12</v>
       </c>
     </row>
     <row r="261">
@@ -9553,26 +9553,26 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>DPI66576</t>
+          <t>DPI66679</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>125.61</v>
+        <v>131.96</v>
       </c>
       <c r="E261" t="n">
         <v>980</v>
       </c>
       <c r="F261" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G261" t="n">
-        <v>12.82</v>
+        <v>13.47</v>
       </c>
       <c r="H261" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I261" t="n">
-        <v>59503.18</v>
+        <v>57712.64</v>
       </c>
     </row>
     <row r="262">
@@ -9588,26 +9588,26 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>DPI64592</t>
+          <t>DPI64431</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>96.81999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="E262" t="n">
         <v>980</v>
       </c>
       <c r="F262" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G262" t="n">
-        <v>9.880000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H262" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I262" t="n">
-        <v>45864.46</v>
+        <v>34432.21</v>
       </c>
     </row>
     <row r="263">
@@ -9633,16 +9633,16 @@
         <v>980</v>
       </c>
       <c r="F263" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G263" t="n">
         <v>11.06</v>
       </c>
       <c r="H263" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I263" t="n">
-        <v>51336.95</v>
+        <v>47395.51</v>
       </c>
     </row>
     <row r="264">
@@ -9658,26 +9658,26 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DPI66679</t>
+          <t>DPI70081</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>131.96</v>
+        <v>54.11</v>
       </c>
       <c r="E264" t="n">
         <v>980</v>
       </c>
       <c r="F264" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G264" t="n">
-        <v>13.47</v>
+        <v>5.52</v>
       </c>
       <c r="H264" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I264" t="n">
-        <v>62512.07</v>
+        <v>23665.31</v>
       </c>
     </row>
     <row r="265">
@@ -9693,26 +9693,26 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DPI70047</t>
+          <t>DPI66576</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>76.39</v>
+        <v>125.61</v>
       </c>
       <c r="E265" t="n">
         <v>980</v>
       </c>
       <c r="F265" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G265" t="n">
-        <v>7.8</v>
+        <v>12.82</v>
       </c>
       <c r="H265" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I265" t="n">
-        <v>36187.45</v>
+        <v>54934.77</v>
       </c>
     </row>
     <row r="266">
@@ -9728,26 +9728,26 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DPI66923</t>
+          <t>DPI66313</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>68.56999999999999</v>
+        <v>124.82</v>
       </c>
       <c r="E266" t="n">
         <v>980</v>
       </c>
       <c r="F266" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G266" t="n">
-        <v>7</v>
+        <v>12.74</v>
       </c>
       <c r="H266" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I266" t="n">
-        <v>32481.03</v>
+        <v>54589.9</v>
       </c>
     </row>
     <row r="267">
@@ -9763,26 +9763,26 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>DFT80078</t>
+          <t>DPI63827</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>42.46</v>
+        <v>130.01</v>
       </c>
       <c r="E267" t="n">
         <v>980</v>
       </c>
       <c r="F267" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G267" t="n">
-        <v>4.33</v>
+        <v>13.27</v>
       </c>
       <c r="H267" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
       <c r="I267" t="n">
-        <v>20114.06</v>
+        <v>56856.59</v>
       </c>
     </row>
     <row r="268">
@@ -9814,10 +9814,10 @@
         <v>10.41</v>
       </c>
       <c r="H268" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I268" t="n">
-        <v>145213.42</v>
+        <v>52577.58</v>
       </c>
     </row>
     <row r="269">
@@ -9849,10 +9849,10 @@
         <v>13.99</v>
       </c>
       <c r="H269" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I269" t="n">
-        <v>195198.21</v>
+        <v>70675.63</v>
       </c>
     </row>
     <row r="270">
@@ -9884,10 +9884,10 @@
         <v>8.359999999999999</v>
       </c>
       <c r="H270" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I270" t="n">
-        <v>116606.55</v>
+        <v>42219.86</v>
       </c>
     </row>
     <row r="271">
@@ -9919,10 +9919,10 @@
         <v>25.39</v>
       </c>
       <c r="H271" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I271" t="n">
-        <v>354258.21</v>
+        <v>128266.66</v>
       </c>
     </row>
     <row r="272">
@@ -9954,10 +9954,10 @@
         <v>6.08</v>
       </c>
       <c r="H272" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I272" t="n">
-        <v>84871.02</v>
+        <v>30729.34</v>
       </c>
     </row>
     <row r="273">
@@ -9989,10 +9989,10 @@
         <v>9.4</v>
       </c>
       <c r="H273" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I273" t="n">
-        <v>131120.5</v>
+        <v>47474.94</v>
       </c>
     </row>
     <row r="274">
@@ -10024,10 +10024,10 @@
         <v>4.28</v>
       </c>
       <c r="H274" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I274" t="n">
-        <v>59658.62</v>
+        <v>21600.66</v>
       </c>
     </row>
     <row r="275">
@@ -10059,10 +10059,10 @@
         <v>1.37</v>
       </c>
       <c r="H275" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I275" t="n">
-        <v>19161.57</v>
+        <v>6937.85</v>
       </c>
     </row>
     <row r="276">
@@ -10094,10 +10094,10 @@
         <v>20.36</v>
       </c>
       <c r="H276" t="n">
-        <v>1395183.69</v>
+        <v>505155.69</v>
       </c>
       <c r="I276" t="n">
-        <v>284110.65</v>
+        <v>102868.26</v>
       </c>
     </row>
     <row r="277">
@@ -10129,10 +10129,10 @@
         <v>7.36</v>
       </c>
       <c r="H277" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I277" t="n">
-        <v>79172.91</v>
+        <v>13632.34</v>
       </c>
     </row>
     <row r="278">
@@ -10164,10 +10164,10 @@
         <v>7.27</v>
       </c>
       <c r="H278" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I278" t="n">
-        <v>78146.58</v>
+        <v>13455.62</v>
       </c>
     </row>
     <row r="279">
@@ -10199,10 +10199,10 @@
         <v>7.4</v>
       </c>
       <c r="H279" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I279" t="n">
-        <v>79536.05</v>
+        <v>13694.87</v>
       </c>
     </row>
     <row r="280">
@@ -10234,10 +10234,10 @@
         <v>7.39</v>
       </c>
       <c r="H280" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I280" t="n">
-        <v>79490.52</v>
+        <v>13687.03</v>
       </c>
     </row>
     <row r="281">
@@ -10269,10 +10269,10 @@
         <v>2.67</v>
       </c>
       <c r="H281" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I281" t="n">
-        <v>28705.91</v>
+        <v>4942.71</v>
       </c>
     </row>
     <row r="282">
@@ -10304,10 +10304,10 @@
         <v>6.05</v>
       </c>
       <c r="H282" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I282" t="n">
-        <v>65067.13</v>
+        <v>11203.55</v>
       </c>
     </row>
     <row r="283">
@@ -10339,10 +10339,10 @@
         <v>5.82</v>
       </c>
       <c r="H283" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I283" t="n">
-        <v>62528.68</v>
+        <v>10766.46</v>
       </c>
     </row>
     <row r="284">
@@ -10374,10 +10374,10 @@
         <v>11.21</v>
       </c>
       <c r="H284" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I284" t="n">
-        <v>120537.32</v>
+        <v>20754.65</v>
       </c>
     </row>
     <row r="285">
@@ -10409,10 +10409,10 @@
         <v>4.53</v>
       </c>
       <c r="H285" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I285" t="n">
-        <v>48692.34</v>
+        <v>8384.059999999999</v>
       </c>
     </row>
     <row r="286">
@@ -10444,10 +10444,10 @@
         <v>15.32</v>
       </c>
       <c r="H286" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I286" t="n">
-        <v>164685.06</v>
+        <v>28356.2</v>
       </c>
     </row>
     <row r="287">
@@ -10479,10 +10479,10 @@
         <v>7.88</v>
       </c>
       <c r="H287" t="n">
-        <v>1075152.5</v>
+        <v>185124.5</v>
       </c>
       <c r="I287" t="n">
-        <v>84759.98</v>
+        <v>14594.35</v>
       </c>
     </row>
     <row r="288">
@@ -10514,10 +10514,10 @@
         <v>2.25</v>
       </c>
       <c r="H288" t="n">
-        <v>1057752.83</v>
+        <v>167724.83</v>
       </c>
       <c r="I288" t="n">
-        <v>23834.53</v>
+        <v>3779.37</v>
       </c>
     </row>
     <row r="289">
@@ -10549,10 +10549,10 @@
         <v>13.12</v>
       </c>
       <c r="H289" t="n">
-        <v>1057752.83</v>
+        <v>167724.83</v>
       </c>
       <c r="I289" t="n">
-        <v>138809.18</v>
+        <v>22010.57</v>
       </c>
     </row>
     <row r="290">
@@ -10584,10 +10584,10 @@
         <v>10.89</v>
       </c>
       <c r="H290" t="n">
-        <v>1057752.83</v>
+        <v>167724.83</v>
       </c>
       <c r="I290" t="n">
-        <v>115217.24</v>
+        <v>18269.67</v>
       </c>
     </row>
     <row r="291">
@@ -10619,10 +10619,10 @@
         <v>24.87</v>
       </c>
       <c r="H291" t="n">
-        <v>1057752.83</v>
+        <v>167724.83</v>
       </c>
       <c r="I291" t="n">
-        <v>263108.4</v>
+        <v>41720.34</v>
       </c>
     </row>
     <row r="292">
@@ -10654,10 +10654,10 @@
         <v>20.46</v>
       </c>
       <c r="H292" t="n">
-        <v>1057752.83</v>
+        <v>167724.83</v>
       </c>
       <c r="I292" t="n">
-        <v>216387.41</v>
+        <v>34311.93</v>
       </c>
     </row>
     <row r="293">
@@ -10689,10 +10689,10 @@
         <v>23.33</v>
       </c>
       <c r="H293" t="n">
-        <v>1345003.83</v>
+        <v>454975.83</v>
       </c>
       <c r="I293" t="n">
-        <v>313750.96</v>
+        <v>106132.86</v>
       </c>
     </row>
     <row r="294">
@@ -10724,10 +10724,10 @@
         <v>28.98</v>
       </c>
       <c r="H294" t="n">
-        <v>1345003.83</v>
+        <v>454975.83</v>
       </c>
       <c r="I294" t="n">
-        <v>389839.75</v>
+        <v>131871.49</v>
       </c>
     </row>
     <row r="295">
@@ -10759,10 +10759,10 @@
         <v>29.16</v>
       </c>
       <c r="H295" t="n">
-        <v>1345003.83</v>
+        <v>454975.83</v>
       </c>
       <c r="I295" t="n">
-        <v>392207.23</v>
+        <v>132672.34</v>
       </c>
     </row>
     <row r="296">
@@ -10794,10 +10794,10 @@
         <v>10.21</v>
       </c>
       <c r="H296" t="n">
-        <v>1387184.02</v>
+        <v>497156.02</v>
       </c>
       <c r="I296" t="n">
-        <v>141582.34</v>
+        <v>50742.02</v>
       </c>
     </row>
     <row r="297">
@@ -10829,10 +10829,10 @@
         <v>10.89</v>
       </c>
       <c r="H297" t="n">
-        <v>1387184.02</v>
+        <v>497156.02</v>
       </c>
       <c r="I297" t="n">
-        <v>151006.29</v>
+        <v>54119.49</v>
       </c>
     </row>
     <row r="298">
@@ -10864,10 +10864,10 @@
         <v>15.52</v>
       </c>
       <c r="H298" t="n">
-        <v>1387184.02</v>
+        <v>497156.02</v>
       </c>
       <c r="I298" t="n">
-        <v>215334.87</v>
+        <v>77174.35000000001</v>
       </c>
     </row>
     <row r="299">
@@ -10899,10 +10899,10 @@
         <v>12.55</v>
       </c>
       <c r="H299" t="n">
-        <v>1387184.02</v>
+        <v>497156.02</v>
       </c>
       <c r="I299" t="n">
-        <v>174073.82</v>
+        <v>62386.71</v>
       </c>
     </row>
     <row r="300">
@@ -10934,10 +10934,10 @@
         <v>16.55</v>
       </c>
       <c r="H300" t="n">
-        <v>1387184.02</v>
+        <v>497156.02</v>
       </c>
       <c r="I300" t="n">
-        <v>229632.3</v>
+        <v>82298.44</v>
       </c>
     </row>
     <row r="301">
@@ -10969,10 +10969,10 @@
         <v>9.58</v>
       </c>
       <c r="H301" t="n">
-        <v>1387184.02</v>
+        <v>497156.02</v>
       </c>
       <c r="I301" t="n">
-        <v>132856.91</v>
+        <v>47614.89</v>
       </c>
     </row>
     <row r="302">
@@ -11004,10 +11004,10 @@
         <v>9.76</v>
       </c>
       <c r="H302" t="n">
-        <v>1387184.02</v>
+        <v>497156.02</v>
       </c>
       <c r="I302" t="n">
-        <v>135358.16</v>
+        <v>48511.32</v>
       </c>
     </row>
     <row r="303">
@@ -11039,10 +11039,10 @@
         <v>19.02</v>
       </c>
       <c r="H303" t="n">
-        <v>1057988.32</v>
+        <v>167960.32</v>
       </c>
       <c r="I303" t="n">
-        <v>201257.9</v>
+        <v>31950.58</v>
       </c>
     </row>
     <row r="304">
@@ -11074,10 +11074,10 @@
         <v>8.9</v>
       </c>
       <c r="H304" t="n">
-        <v>1057988.32</v>
+        <v>167960.32</v>
       </c>
       <c r="I304" t="n">
-        <v>94162.25999999999</v>
+        <v>14948.67</v>
       </c>
     </row>
     <row r="305">
@@ -11109,10 +11109,10 @@
         <v>13.37</v>
       </c>
       <c r="H305" t="n">
-        <v>1057988.32</v>
+        <v>167960.32</v>
       </c>
       <c r="I305" t="n">
-        <v>141495.65</v>
+        <v>22463.06</v>
       </c>
     </row>
     <row r="306">
@@ -11144,10 +11144,10 @@
         <v>22.67</v>
       </c>
       <c r="H306" t="n">
-        <v>1057988.32</v>
+        <v>167960.32</v>
       </c>
       <c r="I306" t="n">
-        <v>239798.62</v>
+        <v>38069.09</v>
       </c>
     </row>
     <row r="307">
@@ -11179,10 +11179,10 @@
         <v>12.57</v>
       </c>
       <c r="H307" t="n">
-        <v>1057988.32</v>
+        <v>167960.32</v>
       </c>
       <c r="I307" t="n">
-        <v>133009.56</v>
+        <v>21115.86</v>
       </c>
     </row>
     <row r="308">
@@ -11214,10 +11214,10 @@
         <v>6.7</v>
       </c>
       <c r="H308" t="n">
-        <v>1057988.32</v>
+        <v>167960.32</v>
       </c>
       <c r="I308" t="n">
-        <v>70841.09</v>
+        <v>11246.34</v>
       </c>
     </row>
     <row r="309">
@@ -14838,26 +14838,26 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>DPI63822</t>
+          <t>DPI64273</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>164.81</v>
+        <v>135.21</v>
       </c>
       <c r="E412" t="n">
         <v>980</v>
       </c>
       <c r="F412" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G412" t="n">
-        <v>16.82</v>
+        <v>13.8</v>
       </c>
       <c r="H412" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I412" t="n">
-        <v>197890.86</v>
+        <v>163774.07</v>
       </c>
     </row>
     <row r="413">
@@ -14873,26 +14873,26 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>DPI64378</t>
+          <t>DPI64665</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>105.69</v>
+        <v>69.66</v>
       </c>
       <c r="E413" t="n">
         <v>980</v>
       </c>
       <c r="F413" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G413" t="n">
-        <v>10.78</v>
+        <v>7.11</v>
       </c>
       <c r="H413" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I413" t="n">
-        <v>126900.15</v>
+        <v>84381.37</v>
       </c>
     </row>
     <row r="414">
@@ -14908,26 +14908,26 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>DPI64255</t>
+          <t>DPI66263</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>119.39</v>
+        <v>123.87</v>
       </c>
       <c r="E414" t="n">
         <v>980</v>
       </c>
       <c r="F414" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G414" t="n">
-        <v>12.18</v>
+        <v>12.64</v>
       </c>
       <c r="H414" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I414" t="n">
-        <v>143355.4</v>
+        <v>150042.81</v>
       </c>
     </row>
     <row r="415">
@@ -14943,26 +14943,26 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>DPI63920</t>
+          <t>DPI64502</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>105.6</v>
+        <v>96.36</v>
       </c>
       <c r="E415" t="n">
         <v>980</v>
       </c>
       <c r="F415" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G415" t="n">
-        <v>10.78</v>
+        <v>9.83</v>
       </c>
       <c r="H415" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I415" t="n">
-        <v>126795.13</v>
+        <v>116717.06</v>
       </c>
     </row>
     <row r="416">
@@ -14978,26 +14978,26 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>DPI66659</t>
+          <t>DPI70120</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>133.62</v>
+        <v>93.91</v>
       </c>
       <c r="E416" t="n">
         <v>980</v>
       </c>
       <c r="F416" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G416" t="n">
-        <v>13.63</v>
+        <v>9.58</v>
       </c>
       <c r="H416" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I416" t="n">
-        <v>160432.92</v>
+        <v>113744.63</v>
       </c>
     </row>
     <row r="417">
@@ -15013,26 +15013,26 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>DPI64476</t>
+          <t>DPI64647</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>105.61</v>
+        <v>103.29</v>
       </c>
       <c r="E417" t="n">
         <v>980</v>
       </c>
       <c r="F417" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G417" t="n">
-        <v>10.78</v>
+        <v>10.54</v>
       </c>
       <c r="H417" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I417" t="n">
-        <v>126811.62</v>
+        <v>125115.6</v>
       </c>
     </row>
     <row r="418">
@@ -15048,26 +15048,26 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>DPI66175</t>
+          <t>DPI64032</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>174.81</v>
+        <v>85.3</v>
       </c>
       <c r="E418" t="n">
         <v>980</v>
       </c>
       <c r="F418" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G418" t="n">
-        <v>17.84</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H418" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I418" t="n">
-        <v>209898.82</v>
+        <v>103325.88</v>
       </c>
     </row>
     <row r="419">
@@ -15083,26 +15083,26 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>DPI70317</t>
+          <t>DPI66402</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>69.34999999999999</v>
+        <v>148.74</v>
       </c>
       <c r="E419" t="n">
         <v>980</v>
       </c>
       <c r="F419" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G419" t="n">
-        <v>7.08</v>
+        <v>15.18</v>
       </c>
       <c r="H419" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
       <c r="I419" t="n">
-        <v>83268.33</v>
+        <v>180161.1</v>
       </c>
     </row>
     <row r="420">
@@ -15113,31 +15113,31 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>DPI64696</t>
+          <t>DPI64758</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>137.67</v>
+        <v>99.53</v>
       </c>
       <c r="E420" t="n">
         <v>980</v>
       </c>
       <c r="F420" t="n">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="G420" t="n">
-        <v>14.05</v>
+        <v>10.16</v>
       </c>
       <c r="H420" t="n">
-        <v>1194686.49</v>
+        <v>1187034.55</v>
       </c>
       <c r="I420" t="n">
-        <v>167834.86</v>
+        <v>120559.42</v>
       </c>
     </row>
     <row r="421">
@@ -15153,11 +15153,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>DPI64179</t>
+          <t>DPI70302</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>138.73</v>
+        <v>51.33</v>
       </c>
       <c r="E421" t="n">
         <v>980</v>
@@ -15166,13 +15166,13 @@
         <v>968</v>
       </c>
       <c r="G421" t="n">
-        <v>14.16</v>
+        <v>5.24</v>
       </c>
       <c r="H421" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I421" t="n">
-        <v>169126.93</v>
+        <v>62576.63</v>
       </c>
     </row>
     <row r="422">
@@ -15188,11 +15188,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>DPI64651</t>
+          <t>DPI66262</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>129.73</v>
+        <v>130.59</v>
       </c>
       <c r="E422" t="n">
         <v>980</v>
@@ -15201,13 +15201,13 @@
         <v>968</v>
       </c>
       <c r="G422" t="n">
-        <v>13.24</v>
+        <v>13.33</v>
       </c>
       <c r="H422" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I422" t="n">
-        <v>158143.67</v>
+        <v>159213.32</v>
       </c>
     </row>
     <row r="423">
@@ -15223,11 +15223,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DPI70179</t>
+          <t>DPI70273</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>97.11</v>
+        <v>39.41</v>
       </c>
       <c r="E423" t="n">
         <v>980</v>
@@ -15236,13 +15236,13 @@
         <v>968</v>
       </c>
       <c r="G423" t="n">
-        <v>9.91</v>
+        <v>4.02</v>
       </c>
       <c r="H423" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I423" t="n">
-        <v>118384.85</v>
+        <v>48041.12</v>
       </c>
     </row>
     <row r="424">
@@ -15258,11 +15258,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>DPI70273</t>
+          <t>DPI70179</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>39.41</v>
+        <v>97.11</v>
       </c>
       <c r="E424" t="n">
         <v>980</v>
@@ -15271,13 +15271,13 @@
         <v>968</v>
       </c>
       <c r="G424" t="n">
-        <v>4.02</v>
+        <v>9.91</v>
       </c>
       <c r="H424" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I424" t="n">
-        <v>48037.92</v>
+        <v>118392.75</v>
       </c>
     </row>
     <row r="425">
@@ -15293,11 +15293,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>DPI66144</t>
+          <t>DPI64651</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>99.38</v>
+        <v>129.73</v>
       </c>
       <c r="E425" t="n">
         <v>980</v>
@@ -15306,13 +15306,13 @@
         <v>968</v>
       </c>
       <c r="G425" t="n">
-        <v>10.14</v>
+        <v>13.24</v>
       </c>
       <c r="H425" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I425" t="n">
-        <v>121145.84</v>
+        <v>158154.22</v>
       </c>
     </row>
     <row r="426">
@@ -15328,11 +15328,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>DPI63847</t>
+          <t>DPI66144</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>144.26</v>
+        <v>99.38</v>
       </c>
       <c r="E426" t="n">
         <v>980</v>
@@ -15341,13 +15341,13 @@
         <v>968</v>
       </c>
       <c r="G426" t="n">
-        <v>14.72</v>
+        <v>10.14</v>
       </c>
       <c r="H426" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I426" t="n">
-        <v>175868.54</v>
+        <v>121153.92</v>
       </c>
     </row>
     <row r="427">
@@ -15363,11 +15363,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>DPI66262</t>
+          <t>DPI63847</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>130.59</v>
+        <v>144.26</v>
       </c>
       <c r="E427" t="n">
         <v>980</v>
@@ -15376,13 +15376,13 @@
         <v>968</v>
       </c>
       <c r="G427" t="n">
-        <v>13.33</v>
+        <v>14.72</v>
       </c>
       <c r="H427" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I427" t="n">
-        <v>159202.7</v>
+        <v>175880.27</v>
       </c>
     </row>
     <row r="428">
@@ -15398,11 +15398,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>DPI70302</t>
+          <t>DPI64179</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>51.33</v>
+        <v>138.73</v>
       </c>
       <c r="E428" t="n">
         <v>980</v>
@@ -15411,13 +15411,13 @@
         <v>968</v>
       </c>
       <c r="G428" t="n">
-        <v>5.24</v>
+        <v>14.16</v>
       </c>
       <c r="H428" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
       <c r="I428" t="n">
-        <v>62572.46</v>
+        <v>169138.21</v>
       </c>
     </row>
     <row r="429">
@@ -15428,31 +15428,31 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>DPI66263</t>
+          <t>DPI64696</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>123.87</v>
+        <v>137.67</v>
       </c>
       <c r="E429" t="n">
         <v>980</v>
       </c>
       <c r="F429" t="n">
-        <v>949</v>
+        <v>968</v>
       </c>
       <c r="G429" t="n">
-        <v>12.64</v>
+        <v>14.05</v>
       </c>
       <c r="H429" t="n">
-        <v>1208267.36</v>
+        <v>1194766.18</v>
       </c>
       <c r="I429" t="n">
-        <v>152726.67</v>
+        <v>167846.06</v>
       </c>
     </row>
     <row r="430">
@@ -15468,26 +15468,26 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>DPI64665</t>
+          <t>DPI63822</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>69.66</v>
+        <v>164.81</v>
       </c>
       <c r="E430" t="n">
         <v>980</v>
       </c>
       <c r="F430" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G430" t="n">
-        <v>7.11</v>
+        <v>16.82</v>
       </c>
       <c r="H430" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I430" t="n">
-        <v>85890.72</v>
+        <v>197890.86</v>
       </c>
     </row>
     <row r="431">
@@ -15503,26 +15503,26 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>DPI64502</t>
+          <t>DPI64378</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>96.36</v>
+        <v>105.69</v>
       </c>
       <c r="E431" t="n">
         <v>980</v>
       </c>
       <c r="F431" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G431" t="n">
-        <v>9.83</v>
+        <v>10.78</v>
       </c>
       <c r="H431" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I431" t="n">
-        <v>118804.81</v>
+        <v>126900.15</v>
       </c>
     </row>
     <row r="432">
@@ -15538,26 +15538,26 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>DPI70120</t>
+          <t>DPI64255</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>93.91</v>
+        <v>119.39</v>
       </c>
       <c r="E432" t="n">
         <v>980</v>
       </c>
       <c r="F432" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G432" t="n">
-        <v>9.58</v>
+        <v>12.18</v>
       </c>
       <c r="H432" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I432" t="n">
-        <v>115779.21</v>
+        <v>143355.4</v>
       </c>
     </row>
     <row r="433">
@@ -15573,26 +15573,26 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>DPI64647</t>
+          <t>DPI63920</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>103.29</v>
+        <v>105.6</v>
       </c>
       <c r="E433" t="n">
         <v>980</v>
       </c>
       <c r="F433" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G433" t="n">
-        <v>10.54</v>
+        <v>10.78</v>
       </c>
       <c r="H433" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I433" t="n">
-        <v>127353.57</v>
+        <v>126795.13</v>
       </c>
     </row>
     <row r="434">
@@ -15608,26 +15608,26 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>DPI64032</t>
+          <t>DPI66659</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>85.3</v>
+        <v>133.62</v>
       </c>
       <c r="E434" t="n">
         <v>980</v>
       </c>
       <c r="F434" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G434" t="n">
-        <v>8.699999999999999</v>
+        <v>13.63</v>
       </c>
       <c r="H434" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I434" t="n">
-        <v>105174.1</v>
+        <v>160432.92</v>
       </c>
     </row>
     <row r="435">
@@ -15643,26 +15643,26 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>DPI66402</t>
+          <t>DPI64476</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>148.74</v>
+        <v>105.61</v>
       </c>
       <c r="E435" t="n">
         <v>980</v>
       </c>
       <c r="F435" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G435" t="n">
-        <v>15.18</v>
+        <v>10.78</v>
       </c>
       <c r="H435" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I435" t="n">
-        <v>183383.69</v>
+        <v>126811.62</v>
       </c>
     </row>
     <row r="436">
@@ -15678,26 +15678,26 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>DPI64409</t>
+          <t>DPI66175</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>92.92</v>
+        <v>174.81</v>
       </c>
       <c r="E436" t="n">
         <v>980</v>
       </c>
       <c r="F436" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G436" t="n">
-        <v>9.48</v>
+        <v>17.84</v>
       </c>
       <c r="H436" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I436" t="n">
-        <v>114564.53</v>
+        <v>209898.82</v>
       </c>
     </row>
     <row r="437">
@@ -15713,26 +15713,26 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>DPI64273</t>
+          <t>DPI70317</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>135.21</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="E437" t="n">
         <v>980</v>
       </c>
       <c r="F437" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="G437" t="n">
-        <v>13.8</v>
+        <v>7.08</v>
       </c>
       <c r="H437" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
       <c r="I437" t="n">
-        <v>166703.54</v>
+        <v>83268.33</v>
       </c>
     </row>
     <row r="438">
@@ -16098,26 +16098,26 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>DPI66684</t>
+          <t>DPI66264</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>92.23999999999999</v>
+        <v>147.75</v>
       </c>
       <c r="E448" t="n">
         <v>980</v>
       </c>
       <c r="F448" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G448" t="n">
-        <v>9.41</v>
+        <v>15.08</v>
       </c>
       <c r="H448" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I448" t="n">
-        <v>134521.01</v>
+        <v>194402.2</v>
       </c>
     </row>
     <row r="449">
@@ -16133,26 +16133,26 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>DPI64236</t>
+          <t>DPI66684</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>69.73999999999999</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E449" t="n">
         <v>980</v>
       </c>
       <c r="F449" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G449" t="n">
-        <v>7.12</v>
+        <v>9.41</v>
       </c>
       <c r="H449" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I449" t="n">
-        <v>101706.43</v>
+        <v>121363.42</v>
       </c>
     </row>
     <row r="450">
@@ -16168,26 +16168,26 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>DPI66734</t>
+          <t>DPI67031</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>111.78</v>
+        <v>136.7</v>
       </c>
       <c r="E450" t="n">
         <v>980</v>
       </c>
       <c r="F450" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G450" t="n">
-        <v>11.41</v>
+        <v>13.95</v>
       </c>
       <c r="H450" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I450" t="n">
-        <v>163025.91</v>
+        <v>179870.94</v>
       </c>
     </row>
     <row r="451">
@@ -16203,26 +16203,26 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>DPI70073</t>
+          <t>DPI64352</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>53.01</v>
+        <v>100.22</v>
       </c>
       <c r="E451" t="n">
         <v>980</v>
       </c>
       <c r="F451" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G451" t="n">
-        <v>5.41</v>
+        <v>10.23</v>
       </c>
       <c r="H451" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I451" t="n">
-        <v>77306.64999999999</v>
+        <v>131867.64</v>
       </c>
     </row>
     <row r="452">
@@ -16238,26 +16238,26 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>DPI70038</t>
+          <t>DPI64288</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>100.52</v>
+        <v>116.14</v>
       </c>
       <c r="E452" t="n">
         <v>980</v>
       </c>
       <c r="F452" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G452" t="n">
-        <v>10.26</v>
+        <v>11.85</v>
       </c>
       <c r="H452" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I452" t="n">
-        <v>146597.34</v>
+        <v>152813.09</v>
       </c>
     </row>
     <row r="453">
@@ -16273,26 +16273,26 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>DPI64149</t>
+          <t>DPI67024</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>43.53</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="E453" t="n">
         <v>980</v>
       </c>
       <c r="F453" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G453" t="n">
-        <v>4.44</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H453" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I453" t="n">
-        <v>63479.22</v>
+        <v>127168.01</v>
       </c>
     </row>
     <row r="454">
@@ -16308,26 +16308,26 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>DPI66572</t>
+          <t>DPI70041</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>80.69</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="E454" t="n">
         <v>980</v>
       </c>
       <c r="F454" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G454" t="n">
-        <v>8.23</v>
+        <v>7.42</v>
       </c>
       <c r="H454" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I454" t="n">
-        <v>117675.91</v>
+        <v>95632.84</v>
       </c>
     </row>
     <row r="455">
@@ -16343,26 +16343,26 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>DPI64234</t>
+          <t>DPI66646</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>68.98</v>
+        <v>154.63</v>
       </c>
       <c r="E455" t="n">
         <v>980</v>
       </c>
       <c r="F455" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="G455" t="n">
-        <v>7.04</v>
+        <v>15.78</v>
       </c>
       <c r="H455" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
       <c r="I455" t="n">
-        <v>100598.82</v>
+        <v>203456.53</v>
       </c>
     </row>
     <row r="456">
@@ -16373,31 +16373,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>DPI64176</t>
+          <t>DPI64104</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>51.79</v>
+        <v>105.14</v>
       </c>
       <c r="E456" t="n">
         <v>980</v>
       </c>
       <c r="F456" t="n">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="G456" t="n">
-        <v>5.29</v>
+        <v>10.73</v>
       </c>
       <c r="H456" t="n">
-        <v>1429248.42</v>
+        <v>1430444.75</v>
       </c>
       <c r="I456" t="n">
-        <v>75536.19</v>
+        <v>153461.79</v>
       </c>
     </row>
     <row r="457">
@@ -16408,31 +16408,31 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>DPI66460</t>
+          <t>DPI64236</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>71.19</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E457" t="n">
         <v>980</v>
       </c>
       <c r="F457" t="n">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="G457" t="n">
-        <v>7.26</v>
+        <v>7.12</v>
       </c>
       <c r="H457" t="n">
-        <v>1429248.42</v>
+        <v>1430444.75</v>
       </c>
       <c r="I457" t="n">
-        <v>103824.89</v>
+        <v>101791.56</v>
       </c>
     </row>
     <row r="458">
@@ -16443,31 +16443,31 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>DPI63993</t>
+          <t>DPI66734</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>56.56</v>
+        <v>111.78</v>
       </c>
       <c r="E458" t="n">
         <v>980</v>
       </c>
       <c r="F458" t="n">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="G458" t="n">
-        <v>5.77</v>
+        <v>11.41</v>
       </c>
       <c r="H458" t="n">
-        <v>1429248.42</v>
+        <v>1430444.75</v>
       </c>
       <c r="I458" t="n">
-        <v>82486.36</v>
+        <v>163162.37</v>
       </c>
     </row>
     <row r="459">
@@ -16478,31 +16478,31 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>DPI64044</t>
+          <t>DPI70073</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>65.98999999999999</v>
+        <v>53.01</v>
       </c>
       <c r="E459" t="n">
         <v>980</v>
       </c>
       <c r="F459" t="n">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="G459" t="n">
-        <v>6.73</v>
+        <v>5.41</v>
       </c>
       <c r="H459" t="n">
-        <v>1429248.42</v>
+        <v>1430444.75</v>
       </c>
       <c r="I459" t="n">
-        <v>96240.39999999999</v>
+        <v>77371.36</v>
       </c>
     </row>
     <row r="460">
@@ -16513,31 +16513,31 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>DPI64639</t>
+          <t>DPI70038</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>76.79000000000001</v>
+        <v>100.52</v>
       </c>
       <c r="E460" t="n">
         <v>980</v>
       </c>
       <c r="F460" t="n">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="G460" t="n">
-        <v>7.84</v>
+        <v>10.26</v>
       </c>
       <c r="H460" t="n">
-        <v>1429248.42</v>
+        <v>1430444.75</v>
       </c>
       <c r="I460" t="n">
-        <v>111994.48</v>
+        <v>146720.05</v>
       </c>
     </row>
     <row r="461">
@@ -16553,26 +16553,26 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>DPI64758</t>
+          <t>DPI64149</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>99.53</v>
+        <v>43.53</v>
       </c>
       <c r="E461" t="n">
         <v>980</v>
       </c>
       <c r="F461" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G461" t="n">
-        <v>10.16</v>
+        <v>4.44</v>
       </c>
       <c r="H461" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I461" t="n">
-        <v>116509.13</v>
+        <v>63532.36</v>
       </c>
     </row>
     <row r="462">
@@ -16588,26 +16588,26 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>DPI66421</t>
+          <t>DPI66572</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>273.07</v>
+        <v>80.69</v>
       </c>
       <c r="E462" t="n">
         <v>980</v>
       </c>
       <c r="F462" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G462" t="n">
-        <v>27.86</v>
+        <v>8.23</v>
       </c>
       <c r="H462" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I462" t="n">
-        <v>319641.14</v>
+        <v>117774.41</v>
       </c>
     </row>
     <row r="463">
@@ -16623,26 +16623,26 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>DPI67128</t>
+          <t>DPI64234</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>107.28</v>
+        <v>68.98</v>
       </c>
       <c r="E463" t="n">
         <v>980</v>
       </c>
       <c r="F463" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G463" t="n">
-        <v>10.95</v>
+        <v>7.04</v>
       </c>
       <c r="H463" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I463" t="n">
-        <v>125577.67</v>
+        <v>100683.02</v>
       </c>
     </row>
     <row r="464">
@@ -16658,26 +16658,26 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>DPI70100</t>
+          <t>DPI64176</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>65.40000000000001</v>
+        <v>51.79</v>
       </c>
       <c r="E464" t="n">
         <v>980</v>
       </c>
       <c r="F464" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G464" t="n">
-        <v>6.67</v>
+        <v>5.29</v>
       </c>
       <c r="H464" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I464" t="n">
-        <v>76551.61</v>
+        <v>75599.41</v>
       </c>
     </row>
     <row r="465">
@@ -16693,26 +16693,26 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>DPI64303</t>
+          <t>DPI66460</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>103.22</v>
+        <v>71.19</v>
       </c>
       <c r="E465" t="n">
         <v>980</v>
       </c>
       <c r="F465" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G465" t="n">
-        <v>10.53</v>
+        <v>7.26</v>
       </c>
       <c r="H465" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I465" t="n">
-        <v>120828.79</v>
+        <v>103911.8</v>
       </c>
     </row>
     <row r="466">
@@ -16728,26 +16728,26 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>DPI66528</t>
+          <t>DPI63993</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>108.07</v>
+        <v>56.56</v>
       </c>
       <c r="E466" t="n">
         <v>980</v>
       </c>
       <c r="F466" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G466" t="n">
-        <v>11.03</v>
+        <v>5.77</v>
       </c>
       <c r="H466" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I466" t="n">
-        <v>126504.97</v>
+        <v>82555.39999999999</v>
       </c>
     </row>
     <row r="467">
@@ -16763,26 +16763,26 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DPI64692</t>
+          <t>DPI64044</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>133.08</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E467" t="n">
         <v>980</v>
       </c>
       <c r="F467" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G467" t="n">
-        <v>13.58</v>
+        <v>6.73</v>
       </c>
       <c r="H467" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I467" t="n">
-        <v>155778.71</v>
+        <v>96320.95</v>
       </c>
     </row>
     <row r="468">
@@ -16798,26 +16798,26 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>DPI67198</t>
+          <t>DPI64639</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>90.89</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="E468" t="n">
         <v>980</v>
       </c>
       <c r="F468" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G468" t="n">
-        <v>9.27</v>
+        <v>7.84</v>
       </c>
       <c r="H468" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
       <c r="I468" t="n">
-        <v>106392.84</v>
+        <v>112088.22</v>
       </c>
     </row>
     <row r="469">
@@ -16833,26 +16833,26 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>DPI64104</t>
+          <t>DPI64409</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>105.14</v>
+        <v>92.92</v>
       </c>
       <c r="E469" t="n">
         <v>980</v>
       </c>
       <c r="F469" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G469" t="n">
-        <v>10.73</v>
+        <v>9.48</v>
       </c>
       <c r="H469" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I469" t="n">
-        <v>138497.76</v>
+        <v>108820.44</v>
       </c>
     </row>
     <row r="470">
@@ -16868,26 +16868,26 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>DPI66646</t>
+          <t>DPI66421</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>154.63</v>
+        <v>273.07</v>
       </c>
       <c r="E470" t="n">
         <v>980</v>
       </c>
       <c r="F470" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G470" t="n">
-        <v>15.78</v>
+        <v>27.86</v>
       </c>
       <c r="H470" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I470" t="n">
-        <v>203694.74</v>
+        <v>319789.24</v>
       </c>
     </row>
     <row r="471">
@@ -16903,26 +16903,26 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>DPI70041</t>
+          <t>DPI67128</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>72.68000000000001</v>
+        <v>107.28</v>
       </c>
       <c r="E471" t="n">
         <v>980</v>
       </c>
       <c r="F471" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G471" t="n">
-        <v>7.42</v>
+        <v>10.95</v>
       </c>
       <c r="H471" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I471" t="n">
-        <v>95744.8</v>
+        <v>125635.86</v>
       </c>
     </row>
     <row r="472">
@@ -16938,26 +16938,26 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>DPI67024</t>
+          <t>DPI70100</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>96.65000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E472" t="n">
         <v>980</v>
       </c>
       <c r="F472" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G472" t="n">
-        <v>9.859999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="H472" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I472" t="n">
-        <v>127316.9</v>
+        <v>76587.08</v>
       </c>
     </row>
     <row r="473">
@@ -16973,26 +16973,26 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>DPI64288</t>
+          <t>DPI64303</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>116.14</v>
+        <v>103.22</v>
       </c>
       <c r="E473" t="n">
         <v>980</v>
       </c>
       <c r="F473" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G473" t="n">
-        <v>11.85</v>
+        <v>10.53</v>
       </c>
       <c r="H473" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I473" t="n">
-        <v>152992</v>
+        <v>120884.77</v>
       </c>
     </row>
     <row r="474">
@@ -17008,26 +17008,26 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>DPI64352</t>
+          <t>DPI66528</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>100.22</v>
+        <v>108.07</v>
       </c>
       <c r="E474" t="n">
         <v>980</v>
       </c>
       <c r="F474" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G474" t="n">
-        <v>10.23</v>
+        <v>11.03</v>
       </c>
       <c r="H474" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I474" t="n">
-        <v>132022.03</v>
+        <v>126563.59</v>
       </c>
     </row>
     <row r="475">
@@ -17043,26 +17043,26 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>DPI67031</t>
+          <t>DPI64692</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>136.7</v>
+        <v>133.08</v>
       </c>
       <c r="E475" t="n">
         <v>980</v>
       </c>
       <c r="F475" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G475" t="n">
-        <v>13.95</v>
+        <v>13.58</v>
       </c>
       <c r="H475" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I475" t="n">
-        <v>180081.53</v>
+        <v>155850.89</v>
       </c>
     </row>
     <row r="476">
@@ -17078,26 +17078,26 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>DPI66264</t>
+          <t>DPI67198</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>147.75</v>
+        <v>90.89</v>
       </c>
       <c r="E476" t="n">
         <v>980</v>
       </c>
       <c r="F476" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="G476" t="n">
-        <v>15.08</v>
+        <v>9.27</v>
       </c>
       <c r="H476" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
       <c r="I476" t="n">
-        <v>194629.81</v>
+        <v>106442.13</v>
       </c>
     </row>
     <row r="477">

--- a/store_wise_monthly_costs.xlsx
+++ b/store_wise_monthly_costs.xlsx
@@ -5878,26 +5878,26 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DPI66339</t>
+          <t>DPI64218</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>131.28</v>
+        <v>52.55</v>
       </c>
       <c r="E156" t="n">
         <v>980</v>
       </c>
       <c r="F156" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G156" t="n">
-        <v>13.4</v>
+        <v>5.36</v>
       </c>
       <c r="H156" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I156" t="n">
-        <v>53130.91</v>
+        <v>15775.97</v>
       </c>
     </row>
     <row r="157">
@@ -5913,26 +5913,26 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DFT80044</t>
+          <t>DPI66289</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>26.45</v>
+        <v>38.55</v>
       </c>
       <c r="E157" t="n">
         <v>980</v>
       </c>
       <c r="F157" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G157" t="n">
-        <v>2.7</v>
+        <v>3.93</v>
       </c>
       <c r="H157" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I157" t="n">
-        <v>10703.17</v>
+        <v>11573.17</v>
       </c>
     </row>
     <row r="158">
@@ -5948,26 +5948,26 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DPI64216</t>
+          <t>DPI64039</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>79.38</v>
+        <v>98.41</v>
       </c>
       <c r="E158" t="n">
         <v>980</v>
       </c>
       <c r="F158" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G158" t="n">
-        <v>8.1</v>
+        <v>10.04</v>
       </c>
       <c r="H158" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I158" t="n">
-        <v>32126.24</v>
+        <v>29542.65</v>
       </c>
     </row>
     <row r="159">
@@ -5983,26 +5983,26 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DFT80088</t>
+          <t>DPI66069</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>35.23</v>
+        <v>182.8</v>
       </c>
       <c r="E159" t="n">
         <v>980</v>
       </c>
       <c r="F159" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G159" t="n">
-        <v>3.6</v>
+        <v>18.65</v>
       </c>
       <c r="H159" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I159" t="n">
-        <v>14258.02</v>
+        <v>54873.91</v>
       </c>
     </row>
     <row r="160">
@@ -6018,26 +6018,26 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DPI64413</t>
+          <t>DPI70255</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>72.22</v>
+        <v>63.7</v>
       </c>
       <c r="E160" t="n">
         <v>980</v>
       </c>
       <c r="F160" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G160" t="n">
-        <v>7.37</v>
+        <v>6.5</v>
       </c>
       <c r="H160" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I160" t="n">
-        <v>29225.58</v>
+        <v>19120.66</v>
       </c>
     </row>
     <row r="161">
@@ -6053,26 +6053,26 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>DPI70096</t>
+          <t>DPI66645</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>59.61</v>
+        <v>127.76</v>
       </c>
       <c r="E161" t="n">
         <v>980</v>
       </c>
       <c r="F161" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G161" t="n">
-        <v>6.08</v>
+        <v>13.04</v>
       </c>
       <c r="H161" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I161" t="n">
-        <v>24122.88</v>
+        <v>38352.29</v>
       </c>
     </row>
     <row r="162">
@@ -6088,26 +6088,26 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DPI64037</t>
+          <t>DPI64413</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>27.36</v>
+        <v>72.22</v>
       </c>
       <c r="E162" t="n">
         <v>980</v>
       </c>
       <c r="F162" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G162" t="n">
-        <v>2.79</v>
+        <v>7.37</v>
       </c>
       <c r="H162" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I162" t="n">
-        <v>11074.62</v>
+        <v>21678.26</v>
       </c>
     </row>
     <row r="163">
@@ -6123,26 +6123,26 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DPI66172</t>
+          <t>DPI64244</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>12.83</v>
+        <v>126.9</v>
       </c>
       <c r="E163" t="n">
         <v>980</v>
       </c>
       <c r="F163" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G163" t="n">
-        <v>1.31</v>
+        <v>12.95</v>
       </c>
       <c r="H163" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I163" t="n">
-        <v>5190.31</v>
+        <v>38093.76</v>
       </c>
     </row>
     <row r="164">
@@ -6158,26 +6158,26 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DPI64057</t>
+          <t>DFT80088</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>116.77</v>
+        <v>35.23</v>
       </c>
       <c r="E164" t="n">
         <v>980</v>
       </c>
       <c r="F164" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G164" t="n">
-        <v>11.92</v>
+        <v>3.6</v>
       </c>
       <c r="H164" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I164" t="n">
-        <v>47257.76</v>
+        <v>10575.98</v>
       </c>
     </row>
     <row r="165">
@@ -6193,26 +6193,26 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DPI63802</t>
+          <t>DPI64216</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>120.78</v>
+        <v>79.38</v>
       </c>
       <c r="E165" t="n">
         <v>980</v>
       </c>
       <c r="F165" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G165" t="n">
-        <v>12.32</v>
+        <v>8.1</v>
       </c>
       <c r="H165" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I165" t="n">
-        <v>48879.65</v>
+        <v>23829.84</v>
       </c>
     </row>
     <row r="166">
@@ -6228,26 +6228,26 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DPI66051</t>
+          <t>DPI70316</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>99.67</v>
+        <v>48.44</v>
       </c>
       <c r="E166" t="n">
         <v>980</v>
       </c>
       <c r="F166" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="G166" t="n">
-        <v>10.17</v>
+        <v>4.94</v>
       </c>
       <c r="H166" t="n">
-        <v>396606.2</v>
+        <v>294185.11</v>
       </c>
       <c r="I166" t="n">
-        <v>40336.74</v>
+        <v>14539.92</v>
       </c>
     </row>
     <row r="167">
@@ -6258,31 +6258,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DPI64169</t>
+          <t>DPI70142</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>59.46</v>
+        <v>63.66</v>
       </c>
       <c r="E167" t="n">
         <v>980</v>
       </c>
       <c r="F167" t="n">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="G167" t="n">
-        <v>6.07</v>
+        <v>6.5</v>
       </c>
       <c r="H167" t="n">
-        <v>396606.2</v>
+        <v>379616.42</v>
       </c>
       <c r="I167" t="n">
-        <v>24061.51</v>
+        <v>24660.27</v>
       </c>
     </row>
     <row r="168">
@@ -6293,31 +6293,31 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DPI66715</t>
+          <t>DPI66742</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>131.63</v>
+        <v>200.32</v>
       </c>
       <c r="E168" t="n">
         <v>980</v>
       </c>
       <c r="F168" t="n">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="G168" t="n">
-        <v>13.43</v>
+        <v>20.44</v>
       </c>
       <c r="H168" t="n">
-        <v>396606.2</v>
+        <v>379616.42</v>
       </c>
       <c r="I168" t="n">
-        <v>53270.94</v>
+        <v>77597.92999999999</v>
       </c>
     </row>
     <row r="169">
@@ -6333,26 +6333,26 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DPI64052</t>
+          <t>DPI63915</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>192.78</v>
+        <v>131.72</v>
       </c>
       <c r="E169" t="n">
         <v>980</v>
       </c>
       <c r="F169" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="G169" t="n">
-        <v>19.67</v>
+        <v>13.44</v>
       </c>
       <c r="H169" t="n">
-        <v>461199.37</v>
+        <v>379616.42</v>
       </c>
       <c r="I169" t="n">
-        <v>90724.53999999999</v>
+        <v>51023.12</v>
       </c>
     </row>
     <row r="170">
@@ -6368,26 +6368,26 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DPI67187</t>
+          <t>DPI64724</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>102.41</v>
+        <v>84.75</v>
       </c>
       <c r="E170" t="n">
         <v>980</v>
       </c>
       <c r="F170" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="G170" t="n">
-        <v>10.45</v>
+        <v>8.65</v>
       </c>
       <c r="H170" t="n">
-        <v>461199.37</v>
+        <v>379616.42</v>
       </c>
       <c r="I170" t="n">
-        <v>48197.59</v>
+        <v>32828.1</v>
       </c>
     </row>
     <row r="171">
@@ -6403,26 +6403,26 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DFT80077</t>
+          <t>DPI67178</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>46.73</v>
+        <v>83.31</v>
       </c>
       <c r="E171" t="n">
         <v>980</v>
       </c>
       <c r="F171" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="G171" t="n">
-        <v>4.77</v>
+        <v>8.5</v>
       </c>
       <c r="H171" t="n">
-        <v>461199.37</v>
+        <v>379616.42</v>
       </c>
       <c r="I171" t="n">
-        <v>21991.92</v>
+        <v>32270.4</v>
       </c>
     </row>
     <row r="172">
@@ -6438,26 +6438,26 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DPI64666</t>
+          <t>DPI64297</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>93.56999999999999</v>
+        <v>126.1</v>
       </c>
       <c r="E172" t="n">
         <v>980</v>
       </c>
       <c r="F172" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="G172" t="n">
-        <v>9.550000000000001</v>
+        <v>12.87</v>
       </c>
       <c r="H172" t="n">
-        <v>461199.37</v>
+        <v>379616.42</v>
       </c>
       <c r="I172" t="n">
-        <v>44035.93</v>
+        <v>48845.79</v>
       </c>
     </row>
     <row r="173">
@@ -6473,26 +6473,26 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>DPI70190</t>
+          <t>DPI66067</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>60.35</v>
+        <v>139.3</v>
       </c>
       <c r="E173" t="n">
         <v>980</v>
       </c>
       <c r="F173" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="G173" t="n">
-        <v>6.16</v>
+        <v>14.21</v>
       </c>
       <c r="H173" t="n">
-        <v>461199.37</v>
+        <v>379616.42</v>
       </c>
       <c r="I173" t="n">
-        <v>28402.73</v>
+        <v>53960.89</v>
       </c>
     </row>
     <row r="174">
@@ -6508,26 +6508,26 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DPI70253</t>
+          <t>DPI70213</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>56.09</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="E174" t="n">
         <v>980</v>
       </c>
       <c r="F174" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="G174" t="n">
-        <v>5.72</v>
+        <v>7.93</v>
       </c>
       <c r="H174" t="n">
-        <v>461199.37</v>
+        <v>379616.42</v>
       </c>
       <c r="I174" t="n">
-        <v>26394.3</v>
+        <v>30092.12</v>
       </c>
     </row>
     <row r="175">
@@ -6543,26 +6543,26 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DPI64056</t>
+          <t>DPI64136</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>84.19</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="E175" t="n">
         <v>980</v>
       </c>
       <c r="F175" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="G175" t="n">
-        <v>8.59</v>
+        <v>7.21</v>
       </c>
       <c r="H175" t="n">
-        <v>461199.37</v>
+        <v>379616.42</v>
       </c>
       <c r="I175" t="n">
-        <v>39620.65</v>
+        <v>27379.14</v>
       </c>
     </row>
     <row r="176">
@@ -6573,31 +6573,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>DPI67074</t>
+          <t>DPI66736</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>115.58</v>
+        <v>136.37</v>
       </c>
       <c r="E176" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="F176" t="n">
-        <v>969</v>
+        <v>520</v>
       </c>
       <c r="G176" t="n">
-        <v>11.79</v>
+        <v>20.66</v>
       </c>
       <c r="H176" t="n">
-        <v>461199.37</v>
+        <v>423299.77</v>
       </c>
       <c r="I176" t="n">
-        <v>54391.36</v>
+        <v>87461.35000000001</v>
       </c>
     </row>
     <row r="177">
@@ -6608,31 +6608,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>DPI64628</t>
+          <t>DPI70229</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>83.72</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E177" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="F177" t="n">
-        <v>969</v>
+        <v>520</v>
       </c>
       <c r="G177" t="n">
-        <v>8.539999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="H177" t="n">
-        <v>461199.37</v>
+        <v>423299.77</v>
       </c>
       <c r="I177" t="n">
-        <v>39398.19</v>
+        <v>42230.86</v>
       </c>
     </row>
     <row r="178">
@@ -6643,31 +6643,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>DPI64119</t>
+          <t>DPI64018</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>91.45999999999999</v>
+        <v>161.85</v>
       </c>
       <c r="E178" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="F178" t="n">
-        <v>969</v>
+        <v>520</v>
       </c>
       <c r="G178" t="n">
-        <v>9.33</v>
+        <v>24.52</v>
       </c>
       <c r="H178" t="n">
-        <v>461199.37</v>
+        <v>423299.77</v>
       </c>
       <c r="I178" t="n">
-        <v>43041.05</v>
+        <v>103804.77</v>
       </c>
     </row>
     <row r="179">
@@ -6678,31 +6678,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>DFT80078</t>
+          <t>DPI66096</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>42.46</v>
+        <v>156.26</v>
       </c>
       <c r="E179" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="F179" t="n">
-        <v>969</v>
+        <v>520</v>
       </c>
       <c r="G179" t="n">
-        <v>4.33</v>
+        <v>23.68</v>
       </c>
       <c r="H179" t="n">
-        <v>461199.37</v>
+        <v>423299.77</v>
       </c>
       <c r="I179" t="n">
-        <v>19982.53</v>
+        <v>100221.1</v>
       </c>
     </row>
     <row r="180">
@@ -6713,31 +6713,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>DPI64450</t>
+          <t>DPI64196</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>49.06</v>
+        <v>79.7</v>
       </c>
       <c r="E180" t="n">
         <v>980</v>
       </c>
       <c r="F180" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G180" t="n">
-        <v>5.01</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I180" t="n">
-        <v>27026.52</v>
+        <v>36551.93</v>
       </c>
     </row>
     <row r="181">
@@ -6748,31 +6748,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DPI66387</t>
+          <t>DPI64624</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>108.78</v>
+        <v>119.04</v>
       </c>
       <c r="E181" t="n">
         <v>980</v>
       </c>
       <c r="F181" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G181" t="n">
-        <v>11.1</v>
+        <v>12.15</v>
       </c>
       <c r="H181" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I181" t="n">
-        <v>59924.2</v>
+        <v>54591.43</v>
       </c>
     </row>
     <row r="182">
@@ -6783,31 +6783,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>DPI64301</t>
+          <t>DPI66102</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>99.51000000000001</v>
+        <v>124.24</v>
       </c>
       <c r="E182" t="n">
         <v>980</v>
       </c>
       <c r="F182" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G182" t="n">
-        <v>10.15</v>
+        <v>12.68</v>
       </c>
       <c r="H182" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I182" t="n">
-        <v>54814.55</v>
+        <v>56979.24</v>
       </c>
     </row>
     <row r="183">
@@ -6818,31 +6818,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>DPI66590</t>
+          <t>DPI64166</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>142.23</v>
+        <v>56.77</v>
       </c>
       <c r="E183" t="n">
         <v>980</v>
       </c>
       <c r="F183" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G183" t="n">
-        <v>14.51</v>
+        <v>5.79</v>
       </c>
       <c r="H183" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I183" t="n">
-        <v>78351.61</v>
+        <v>26035.6</v>
       </c>
     </row>
     <row r="184">
@@ -6853,31 +6853,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>DPI70316</t>
+          <t>DPI66384</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>48.44</v>
+        <v>156.23</v>
       </c>
       <c r="E184" t="n">
         <v>980</v>
       </c>
       <c r="F184" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G184" t="n">
-        <v>4.94</v>
+        <v>15.94</v>
       </c>
       <c r="H184" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I184" t="n">
-        <v>26681.77</v>
+        <v>71647.08</v>
       </c>
     </row>
     <row r="185">
@@ -6888,31 +6888,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>DPI66096</t>
+          <t>DPI66408</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>156.26</v>
+        <v>147.34</v>
       </c>
       <c r="E185" t="n">
         <v>980</v>
       </c>
       <c r="F185" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G185" t="n">
-        <v>15.95</v>
+        <v>15.03</v>
       </c>
       <c r="H185" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I185" t="n">
-        <v>86079.97</v>
+        <v>67569.44</v>
       </c>
     </row>
     <row r="186">
@@ -6923,31 +6923,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>DPI64018</t>
+          <t>DPI64392</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>161.85</v>
+        <v>79.42</v>
       </c>
       <c r="E186" t="n">
         <v>980</v>
       </c>
       <c r="F186" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G186" t="n">
-        <v>16.52</v>
+        <v>8.1</v>
       </c>
       <c r="H186" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I186" t="n">
-        <v>89157.98</v>
+        <v>36424.07</v>
       </c>
     </row>
     <row r="187">
@@ -6958,31 +6958,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>DPI66736</t>
+          <t>DPI66618</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>136.37</v>
+        <v>133.15</v>
       </c>
       <c r="E187" t="n">
         <v>980</v>
       </c>
       <c r="F187" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G187" t="n">
-        <v>13.92</v>
+        <v>13.59</v>
       </c>
       <c r="H187" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I187" t="n">
-        <v>75120.60000000001</v>
+        <v>61063.14</v>
       </c>
     </row>
     <row r="188">
@@ -6993,31 +6993,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>DPI70229</t>
+          <t>DPI64431</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>65.84999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="E188" t="n">
         <v>980</v>
       </c>
       <c r="F188" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G188" t="n">
-        <v>6.72</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H188" t="n">
-        <v>539849.98</v>
+        <v>449432.3</v>
       </c>
       <c r="I188" t="n">
-        <v>36272.11</v>
+        <v>36106.38</v>
       </c>
     </row>
     <row r="189">
@@ -7028,31 +7028,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DPI66653</t>
+          <t>DPI66923</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>109.8</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="E189" t="n">
         <v>980</v>
       </c>
       <c r="F189" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2</v>
+        <v>7</v>
       </c>
       <c r="H189" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I189" t="n">
-        <v>50418.44</v>
+        <v>28475.19</v>
       </c>
     </row>
     <row r="190">
@@ -7063,31 +7063,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>DPI64624</t>
+          <t>DFT80077</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>119.04</v>
+        <v>46.73</v>
       </c>
       <c r="E190" t="n">
         <v>980</v>
       </c>
       <c r="F190" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G190" t="n">
-        <v>12.15</v>
+        <v>4.77</v>
       </c>
       <c r="H190" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I190" t="n">
-        <v>54660.63</v>
+        <v>19406.6</v>
       </c>
     </row>
     <row r="191">
@@ -7098,31 +7098,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>DPI66102</t>
+          <t>DPI66636</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>124.24</v>
+        <v>75.55</v>
       </c>
       <c r="E191" t="n">
         <v>980</v>
       </c>
       <c r="F191" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G191" t="n">
-        <v>12.68</v>
+        <v>7.71</v>
       </c>
       <c r="H191" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I191" t="n">
-        <v>57051.47</v>
+        <v>31374.81</v>
       </c>
     </row>
     <row r="192">
@@ -7133,31 +7133,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DPI64166</t>
+          <t>DPI64666</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>56.77</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="E192" t="n">
         <v>980</v>
       </c>
       <c r="F192" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G192" t="n">
-        <v>5.79</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H192" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I192" t="n">
-        <v>26068.6</v>
+        <v>38859.17</v>
       </c>
     </row>
     <row r="193">
@@ -7168,31 +7168,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DPI66384</t>
+          <t>DPI70190</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>156.23</v>
+        <v>60.35</v>
       </c>
       <c r="E193" t="n">
         <v>980</v>
       </c>
       <c r="F193" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G193" t="n">
-        <v>15.94</v>
+        <v>6.16</v>
       </c>
       <c r="H193" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I193" t="n">
-        <v>71737.89999999999</v>
+        <v>25063.77</v>
       </c>
     </row>
     <row r="194">
@@ -7203,31 +7203,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DPI64392</t>
+          <t>DPI70253</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>79.42</v>
+        <v>56.09</v>
       </c>
       <c r="E194" t="n">
         <v>980</v>
       </c>
       <c r="F194" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G194" t="n">
-        <v>8.1</v>
+        <v>5.72</v>
       </c>
       <c r="H194" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I194" t="n">
-        <v>36470.24</v>
+        <v>23291.45</v>
       </c>
     </row>
     <row r="195">
@@ -7238,31 +7238,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DPI66408</t>
+          <t>DPI64056</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>147.34</v>
+        <v>84.19</v>
       </c>
       <c r="E195" t="n">
         <v>980</v>
       </c>
       <c r="F195" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G195" t="n">
-        <v>15.03</v>
+        <v>8.59</v>
       </c>
       <c r="H195" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I195" t="n">
-        <v>67655.09</v>
+        <v>34962.94</v>
       </c>
     </row>
     <row r="196">
@@ -7273,31 +7273,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DPI66618</t>
+          <t>DPI67074</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>133.15</v>
+        <v>115.58</v>
       </c>
       <c r="E196" t="n">
         <v>980</v>
       </c>
       <c r="F196" t="n">
-        <v>925</v>
+        <v>819</v>
       </c>
       <c r="G196" t="n">
-        <v>13.59</v>
+        <v>11.79</v>
       </c>
       <c r="H196" t="n">
-        <v>450001.99</v>
+        <v>406981.88</v>
       </c>
       <c r="I196" t="n">
-        <v>61140.54</v>
+        <v>47997.24</v>
       </c>
     </row>
     <row r="197">
@@ -7308,31 +7308,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DPI67148</t>
+          <t>DPI64628</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>215.01</v>
+        <v>83.72</v>
       </c>
       <c r="E197" t="n">
         <v>980</v>
       </c>
       <c r="F197" t="n">
-        <v>977</v>
+        <v>819</v>
       </c>
       <c r="G197" t="n">
-        <v>21.94</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H197" t="n">
-        <v>422378.22</v>
+        <v>406981.88</v>
       </c>
       <c r="I197" t="n">
-        <v>92668.75</v>
+        <v>34766.63</v>
       </c>
     </row>
     <row r="198">
@@ -7343,31 +7343,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DPI64742</t>
+          <t>DPI64119</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>107.69</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="E198" t="n">
         <v>980</v>
       </c>
       <c r="F198" t="n">
-        <v>977</v>
+        <v>819</v>
       </c>
       <c r="G198" t="n">
-        <v>10.99</v>
+        <v>9.33</v>
       </c>
       <c r="H198" t="n">
-        <v>422378.22</v>
+        <v>406981.88</v>
       </c>
       <c r="I198" t="n">
-        <v>46415.19</v>
+        <v>37981.25</v>
       </c>
     </row>
     <row r="199">
@@ -7378,31 +7378,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>DPI63976</t>
+          <t>DFT80078</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>114.26</v>
+        <v>42.46</v>
       </c>
       <c r="E199" t="n">
         <v>980</v>
       </c>
       <c r="F199" t="n">
-        <v>977</v>
+        <v>819</v>
       </c>
       <c r="G199" t="n">
-        <v>11.66</v>
+        <v>4.33</v>
       </c>
       <c r="H199" t="n">
-        <v>422378.22</v>
+        <v>406981.88</v>
       </c>
       <c r="I199" t="n">
-        <v>49244</v>
+        <v>17633.43</v>
       </c>
     </row>
     <row r="200">
@@ -7418,26 +7418,26 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DPI70296</t>
+          <t>DPI66658</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>53.75</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E200" t="n">
         <v>980</v>
       </c>
       <c r="F200" t="n">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="G200" t="n">
-        <v>5.48</v>
+        <v>8</v>
       </c>
       <c r="H200" t="n">
-        <v>422378.22</v>
+        <v>421596.09</v>
       </c>
       <c r="I200" t="n">
-        <v>23165.55</v>
+        <v>33707.47</v>
       </c>
     </row>
     <row r="201">
@@ -7453,26 +7453,26 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DPI67180</t>
+          <t>DPI67148</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>101.47</v>
+        <v>215.01</v>
       </c>
       <c r="E201" t="n">
         <v>980</v>
       </c>
       <c r="F201" t="n">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="G201" t="n">
-        <v>10.35</v>
+        <v>21.94</v>
       </c>
       <c r="H201" t="n">
-        <v>422378.22</v>
+        <v>421596.09</v>
       </c>
       <c r="I201" t="n">
-        <v>43732.52</v>
+        <v>92497.14999999999</v>
       </c>
     </row>
     <row r="202">
@@ -7488,26 +7488,26 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DPI64634</t>
+          <t>DPI64742</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>86.12</v>
+        <v>107.69</v>
       </c>
       <c r="E202" t="n">
         <v>980</v>
       </c>
       <c r="F202" t="n">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="G202" t="n">
-        <v>8.789999999999999</v>
+        <v>10.99</v>
       </c>
       <c r="H202" t="n">
-        <v>422378.22</v>
+        <v>421596.09</v>
       </c>
       <c r="I202" t="n">
-        <v>37116.74</v>
+        <v>46329.24</v>
       </c>
     </row>
     <row r="203">
@@ -7523,26 +7523,26 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DPI67224</t>
+          <t>DPI63976</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>85.72</v>
+        <v>114.26</v>
       </c>
       <c r="E203" t="n">
         <v>980</v>
       </c>
       <c r="F203" t="n">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="G203" t="n">
-        <v>8.75</v>
+        <v>11.66</v>
       </c>
       <c r="H203" t="n">
-        <v>422378.22</v>
+        <v>421596.09</v>
       </c>
       <c r="I203" t="n">
-        <v>36945.98</v>
+        <v>49152.81</v>
       </c>
     </row>
     <row r="204">
@@ -7558,26 +7558,26 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DPI66209</t>
+          <t>DPI70296</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>136.76</v>
+        <v>53.75</v>
       </c>
       <c r="E204" t="n">
         <v>980</v>
       </c>
       <c r="F204" t="n">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="G204" t="n">
-        <v>13.96</v>
+        <v>5.48</v>
       </c>
       <c r="H204" t="n">
-        <v>422378.22</v>
+        <v>421596.09</v>
       </c>
       <c r="I204" t="n">
-        <v>58943.23</v>
+        <v>23122.65</v>
       </c>
     </row>
     <row r="205">
@@ -7593,26 +7593,26 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DPI66636</t>
+          <t>DPI67180</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>75.55</v>
+        <v>101.47</v>
       </c>
       <c r="E205" t="n">
         <v>980</v>
       </c>
       <c r="F205" t="n">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="G205" t="n">
-        <v>7.71</v>
+        <v>10.35</v>
       </c>
       <c r="H205" t="n">
-        <v>422378.22</v>
+        <v>421596.09</v>
       </c>
       <c r="I205" t="n">
-        <v>32561.74</v>
+        <v>43651.54</v>
       </c>
     </row>
     <row r="206">
@@ -7623,31 +7623,31 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DPI70109</t>
+          <t>DPI64634</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>64.45999999999999</v>
+        <v>86.12</v>
       </c>
       <c r="E206" t="n">
         <v>980</v>
       </c>
       <c r="F206" t="n">
-        <v>824</v>
+        <v>979</v>
       </c>
       <c r="G206" t="n">
-        <v>6.58</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H206" t="n">
-        <v>557988.3</v>
+        <v>421596.09</v>
       </c>
       <c r="I206" t="n">
-        <v>36701.33</v>
+        <v>37048.01</v>
       </c>
     </row>
     <row r="207">
@@ -7658,31 +7658,31 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DPI66129</t>
+          <t>DPI67224</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>200.46</v>
+        <v>85.72</v>
       </c>
       <c r="E207" t="n">
         <v>980</v>
       </c>
       <c r="F207" t="n">
-        <v>824</v>
+        <v>979</v>
       </c>
       <c r="G207" t="n">
-        <v>20.46</v>
+        <v>8.75</v>
       </c>
       <c r="H207" t="n">
-        <v>557988.3</v>
+        <v>421596.09</v>
       </c>
       <c r="I207" t="n">
-        <v>114138.12</v>
+        <v>36877.57</v>
       </c>
     </row>
     <row r="208">
@@ -7693,31 +7693,31 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DPI64495</t>
+          <t>DPI66209</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>186.61</v>
+        <v>136.76</v>
       </c>
       <c r="E208" t="n">
         <v>980</v>
       </c>
       <c r="F208" t="n">
-        <v>824</v>
+        <v>979</v>
       </c>
       <c r="G208" t="n">
-        <v>19.04</v>
+        <v>13.96</v>
       </c>
       <c r="H208" t="n">
-        <v>557988.3</v>
+        <v>421596.09</v>
       </c>
       <c r="I208" t="n">
-        <v>106249.97</v>
+        <v>58834.08</v>
       </c>
     </row>
     <row r="209">
@@ -7733,11 +7733,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DFT80080</t>
+          <t>DPI70109</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>38.28</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="E209" t="n">
         <v>980</v>
@@ -7746,13 +7746,13 @@
         <v>824</v>
       </c>
       <c r="G209" t="n">
-        <v>3.91</v>
+        <v>6.58</v>
       </c>
       <c r="H209" t="n">
         <v>557988.3</v>
       </c>
       <c r="I209" t="n">
-        <v>21793.39</v>
+        <v>36701.33</v>
       </c>
     </row>
     <row r="210">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DPI64548</t>
+          <t>DPI66129</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>118.62</v>
+        <v>200.46</v>
       </c>
       <c r="E210" t="n">
         <v>980</v>
@@ -7781,13 +7781,13 @@
         <v>824</v>
       </c>
       <c r="G210" t="n">
-        <v>12.1</v>
+        <v>20.46</v>
       </c>
       <c r="H210" t="n">
         <v>557988.3</v>
       </c>
       <c r="I210" t="n">
-        <v>67537.16</v>
+        <v>114138.12</v>
       </c>
     </row>
     <row r="211">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>DPI70107</t>
+          <t>DPI64495</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>57.32</v>
+        <v>186.61</v>
       </c>
       <c r="E211" t="n">
         <v>980</v>
@@ -7816,13 +7816,13 @@
         <v>824</v>
       </c>
       <c r="G211" t="n">
-        <v>5.85</v>
+        <v>19.04</v>
       </c>
       <c r="H211" t="n">
         <v>557988.3</v>
       </c>
       <c r="I211" t="n">
-        <v>32634.24</v>
+        <v>106249.97</v>
       </c>
     </row>
     <row r="212">
@@ -7838,11 +7838,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>DPI70214</t>
+          <t>DFT80080</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>53.89</v>
+        <v>38.28</v>
       </c>
       <c r="E212" t="n">
         <v>980</v>
@@ -7851,13 +7851,13 @@
         <v>824</v>
       </c>
       <c r="G212" t="n">
-        <v>5.5</v>
+        <v>3.91</v>
       </c>
       <c r="H212" t="n">
         <v>557988.3</v>
       </c>
       <c r="I212" t="n">
-        <v>30685.39</v>
+        <v>21793.39</v>
       </c>
     </row>
     <row r="213">
@@ -7873,11 +7873,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DPI66634</t>
+          <t>DPI64548</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>104.69</v>
+        <v>118.62</v>
       </c>
       <c r="E213" t="n">
         <v>980</v>
@@ -7886,13 +7886,13 @@
         <v>824</v>
       </c>
       <c r="G213" t="n">
-        <v>10.68</v>
+        <v>12.1</v>
       </c>
       <c r="H213" t="n">
         <v>557988.3</v>
       </c>
       <c r="I213" t="n">
-        <v>59608.09</v>
+        <v>67537.16</v>
       </c>
     </row>
     <row r="214">
@@ -7903,31 +7903,31 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DPI70142</t>
+          <t>DPI70107</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>63.66</v>
+        <v>57.32</v>
       </c>
       <c r="E214" t="n">
         <v>980</v>
       </c>
       <c r="F214" t="n">
-        <v>960</v>
+        <v>824</v>
       </c>
       <c r="G214" t="n">
-        <v>6.5</v>
+        <v>5.85</v>
       </c>
       <c r="H214" t="n">
-        <v>299542.34</v>
+        <v>557988.3</v>
       </c>
       <c r="I214" t="n">
-        <v>19458.58</v>
+        <v>32634.24</v>
       </c>
     </row>
     <row r="215">
@@ -7938,31 +7938,31 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DPI66069</t>
+          <t>DPI70214</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>182.8</v>
+        <v>53.89</v>
       </c>
       <c r="E215" t="n">
         <v>980</v>
       </c>
       <c r="F215" t="n">
-        <v>960</v>
+        <v>824</v>
       </c>
       <c r="G215" t="n">
-        <v>18.65</v>
+        <v>5.5</v>
       </c>
       <c r="H215" t="n">
-        <v>299542.34</v>
+        <v>557988.3</v>
       </c>
       <c r="I215" t="n">
-        <v>55873.19</v>
+        <v>30685.39</v>
       </c>
     </row>
     <row r="216">
@@ -7973,31 +7973,31 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DPI64686</t>
+          <t>DPI66634</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>97.63</v>
+        <v>104.69</v>
       </c>
       <c r="E216" t="n">
         <v>980</v>
       </c>
       <c r="F216" t="n">
-        <v>960</v>
+        <v>824</v>
       </c>
       <c r="G216" t="n">
-        <v>9.960000000000001</v>
+        <v>10.68</v>
       </c>
       <c r="H216" t="n">
-        <v>299542.34</v>
+        <v>557988.3</v>
       </c>
       <c r="I216" t="n">
-        <v>29841.03</v>
+        <v>59608.09</v>
       </c>
     </row>
     <row r="217">
@@ -8013,26 +8013,26 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DPI70255</t>
+          <t>DPI64052</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>63.7</v>
+        <v>192.78</v>
       </c>
       <c r="E217" t="n">
         <v>980</v>
       </c>
       <c r="F217" t="n">
-        <v>960</v>
+        <v>865</v>
       </c>
       <c r="G217" t="n">
-        <v>6.5</v>
+        <v>19.67</v>
       </c>
       <c r="H217" t="n">
-        <v>299542.34</v>
+        <v>166140.82</v>
       </c>
       <c r="I217" t="n">
-        <v>19468.86</v>
+        <v>32682.28</v>
       </c>
     </row>
     <row r="218">
@@ -8048,26 +8048,26 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DPI66645</t>
+          <t>DPI66179</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>127.76</v>
+        <v>130.31</v>
       </c>
       <c r="E218" t="n">
         <v>980</v>
       </c>
       <c r="F218" t="n">
-        <v>960</v>
+        <v>865</v>
       </c>
       <c r="G218" t="n">
-        <v>13.04</v>
+        <v>13.3</v>
       </c>
       <c r="H218" t="n">
-        <v>299542.34</v>
+        <v>166140.82</v>
       </c>
       <c r="I218" t="n">
-        <v>39050.71</v>
+        <v>22090.97</v>
       </c>
     </row>
     <row r="219">
@@ -8083,26 +8083,26 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>DPI64244</t>
+          <t>DPI66597</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>126.9</v>
+        <v>90.83</v>
       </c>
       <c r="E219" t="n">
         <v>980</v>
       </c>
       <c r="F219" t="n">
-        <v>960</v>
+        <v>865</v>
       </c>
       <c r="G219" t="n">
-        <v>12.95</v>
+        <v>9.27</v>
       </c>
       <c r="H219" t="n">
-        <v>299542.34</v>
+        <v>166140.82</v>
       </c>
       <c r="I219" t="n">
-        <v>38787.46</v>
+        <v>15399.35</v>
       </c>
     </row>
     <row r="220">
@@ -8118,26 +8118,26 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>DPI66128</t>
+          <t>DPI63958</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>221.49</v>
+        <v>120.83</v>
       </c>
       <c r="E220" t="n">
         <v>980</v>
       </c>
       <c r="F220" t="n">
-        <v>960</v>
+        <v>865</v>
       </c>
       <c r="G220" t="n">
-        <v>22.6</v>
+        <v>12.33</v>
       </c>
       <c r="H220" t="n">
-        <v>299542.34</v>
+        <v>166140.82</v>
       </c>
       <c r="I220" t="n">
-        <v>67699.53999999999</v>
+        <v>20485.32</v>
       </c>
     </row>
     <row r="221">
@@ -8153,26 +8153,26 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>DPI64094</t>
+          <t>DPI66039</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>75.03</v>
+        <v>114.76</v>
       </c>
       <c r="E221" t="n">
         <v>980</v>
       </c>
       <c r="F221" t="n">
-        <v>960</v>
+        <v>865</v>
       </c>
       <c r="G221" t="n">
-        <v>7.66</v>
+        <v>11.71</v>
       </c>
       <c r="H221" t="n">
-        <v>299542.34</v>
+        <v>166140.82</v>
       </c>
       <c r="I221" t="n">
-        <v>22932.01</v>
+        <v>19455.93</v>
       </c>
     </row>
     <row r="222">
@@ -8183,31 +8183,31 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DPI66597</t>
+          <t>DPI66307</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>90.83</v>
+        <v>125.94</v>
       </c>
       <c r="E222" t="n">
         <v>980</v>
       </c>
       <c r="F222" t="n">
-        <v>975</v>
+        <v>865</v>
       </c>
       <c r="G222" t="n">
-        <v>9.27</v>
+        <v>12.85</v>
       </c>
       <c r="H222" t="n">
-        <v>248412.78</v>
+        <v>166140.82</v>
       </c>
       <c r="I222" t="n">
-        <v>23025.02</v>
+        <v>21350.79</v>
       </c>
     </row>
     <row r="223">
@@ -8218,31 +8218,31 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DPI66373</t>
+          <t>DPI64638</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>98.05</v>
+        <v>88.97</v>
       </c>
       <c r="E223" t="n">
         <v>980</v>
       </c>
       <c r="F223" t="n">
-        <v>975</v>
+        <v>865</v>
       </c>
       <c r="G223" t="n">
-        <v>10.01</v>
+        <v>9.08</v>
       </c>
       <c r="H223" t="n">
-        <v>248412.78</v>
+        <v>166140.82</v>
       </c>
       <c r="I223" t="n">
-        <v>24854.26</v>
+        <v>15083.24</v>
       </c>
     </row>
     <row r="224">
@@ -8258,26 +8258,26 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DPI66154</t>
+          <t>DPI70009</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>73.08</v>
+        <v>60.09</v>
       </c>
       <c r="E224" t="n">
         <v>980</v>
       </c>
       <c r="F224" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="G224" t="n">
-        <v>7.46</v>
+        <v>6.13</v>
       </c>
       <c r="H224" t="n">
-        <v>248412.78</v>
+        <v>331208.44</v>
       </c>
       <c r="I224" t="n">
-        <v>18524.47</v>
+        <v>20309.6</v>
       </c>
     </row>
     <row r="225">
@@ -8293,26 +8293,26 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DPI64592</t>
+          <t>DPI63827</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>96.81999999999999</v>
+        <v>130.01</v>
       </c>
       <c r="E225" t="n">
         <v>980</v>
       </c>
       <c r="F225" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="G225" t="n">
-        <v>9.880000000000001</v>
+        <v>13.27</v>
       </c>
       <c r="H225" t="n">
-        <v>248412.78</v>
+        <v>331208.44</v>
       </c>
       <c r="I225" t="n">
-        <v>24542.12</v>
+        <v>43937.67</v>
       </c>
     </row>
     <row r="226">
@@ -8328,26 +8328,26 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DPI66449</t>
+          <t>DPI66313</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>191.04</v>
+        <v>124.82</v>
       </c>
       <c r="E226" t="n">
         <v>980</v>
       </c>
       <c r="F226" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="G226" t="n">
-        <v>19.49</v>
+        <v>12.74</v>
       </c>
       <c r="H226" t="n">
-        <v>248412.78</v>
+        <v>331208.44</v>
       </c>
       <c r="I226" t="n">
-        <v>48425.59</v>
+        <v>42186.01</v>
       </c>
     </row>
     <row r="227">
@@ -8363,26 +8363,26 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>DPI67072</t>
+          <t>DPI66576</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>126.86</v>
+        <v>125.61</v>
       </c>
       <c r="E227" t="n">
         <v>980</v>
       </c>
       <c r="F227" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="G227" t="n">
-        <v>12.94</v>
+        <v>12.82</v>
       </c>
       <c r="H227" t="n">
-        <v>248412.78</v>
+        <v>331208.44</v>
       </c>
       <c r="I227" t="n">
-        <v>32156.1</v>
+        <v>42452.52</v>
       </c>
     </row>
     <row r="228">
@@ -8398,26 +8398,26 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DPI66153</t>
+          <t>DPI64592</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>97.33</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="E228" t="n">
         <v>980</v>
       </c>
       <c r="F228" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="G228" t="n">
-        <v>9.93</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H228" t="n">
-        <v>248412.78</v>
+        <v>331208.44</v>
       </c>
       <c r="I228" t="n">
-        <v>24670.74</v>
+        <v>32721.98</v>
       </c>
     </row>
     <row r="229">
@@ -8433,26 +8433,26 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DPI64196</t>
+          <t>DPI63919</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>79.7</v>
+        <v>108.37</v>
       </c>
       <c r="E229" t="n">
         <v>980</v>
       </c>
       <c r="F229" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="G229" t="n">
-        <v>8.130000000000001</v>
+        <v>11.06</v>
       </c>
       <c r="H229" t="n">
-        <v>248412.78</v>
+        <v>331208.44</v>
       </c>
       <c r="I229" t="n">
-        <v>20203.19</v>
+        <v>36626.33</v>
       </c>
     </row>
     <row r="230">
@@ -8468,26 +8468,26 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DPI66221</t>
+          <t>DPI66679</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>121.2</v>
+        <v>131.96</v>
       </c>
       <c r="E230" t="n">
         <v>980</v>
       </c>
       <c r="F230" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="G230" t="n">
-        <v>12.37</v>
+        <v>13.47</v>
       </c>
       <c r="H230" t="n">
-        <v>248412.78</v>
+        <v>331208.44</v>
       </c>
       <c r="I230" t="n">
-        <v>30723.04</v>
+        <v>44599.21</v>
       </c>
     </row>
     <row r="231">
@@ -8498,31 +8498,31 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DPI66179</t>
+          <t>DPI70047</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>130.31</v>
+        <v>76.39</v>
       </c>
       <c r="E231" t="n">
         <v>980</v>
       </c>
       <c r="F231" t="n">
-        <v>969</v>
+        <v>854</v>
       </c>
       <c r="G231" t="n">
-        <v>13.3</v>
+        <v>7.8</v>
       </c>
       <c r="H231" t="n">
-        <v>420179.55</v>
+        <v>331208.44</v>
       </c>
       <c r="I231" t="n">
-        <v>55869.31</v>
+        <v>25817.92</v>
       </c>
     </row>
     <row r="232">
@@ -8538,26 +8538,26 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DPI64218</t>
+          <t>DPI64094</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>52.55</v>
+        <v>75.03</v>
       </c>
       <c r="E232" t="n">
         <v>980</v>
       </c>
       <c r="F232" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G232" t="n">
-        <v>5.36</v>
+        <v>7.66</v>
       </c>
       <c r="H232" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I232" t="n">
-        <v>22532.55</v>
+        <v>30686.18</v>
       </c>
     </row>
     <row r="233">
@@ -8573,26 +8573,26 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DPI64039</t>
+          <t>DPI66128</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>98.41</v>
+        <v>221.49</v>
       </c>
       <c r="E233" t="n">
         <v>980</v>
       </c>
       <c r="F233" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G233" t="n">
-        <v>10.04</v>
+        <v>22.6</v>
       </c>
       <c r="H233" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I233" t="n">
-        <v>42195.27</v>
+        <v>90591.28999999999</v>
       </c>
     </row>
     <row r="234">
@@ -8608,26 +8608,26 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>DPI66289</t>
+          <t>DPI70096</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>38.55</v>
+        <v>59.61</v>
       </c>
       <c r="E234" t="n">
         <v>980</v>
       </c>
       <c r="F234" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G234" t="n">
-        <v>3.93</v>
+        <v>6.08</v>
       </c>
       <c r="H234" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I234" t="n">
-        <v>16529.76</v>
+        <v>24379.72</v>
       </c>
     </row>
     <row r="235">
@@ -8643,26 +8643,26 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DPI66203</t>
+          <t>DPI64037</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>187.41</v>
+        <v>27.36</v>
       </c>
       <c r="E235" t="n">
         <v>980</v>
       </c>
       <c r="F235" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G235" t="n">
-        <v>19.12</v>
+        <v>2.79</v>
       </c>
       <c r="H235" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I235" t="n">
-        <v>80353.10000000001</v>
+        <v>11192.53</v>
       </c>
     </row>
     <row r="236">
@@ -8678,26 +8678,26 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DPI66574</t>
+          <t>DPI66172</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>165.71</v>
+        <v>12.83</v>
       </c>
       <c r="E236" t="n">
         <v>980</v>
       </c>
       <c r="F236" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G236" t="n">
-        <v>16.91</v>
+        <v>1.31</v>
       </c>
       <c r="H236" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I236" t="n">
-        <v>71047.39</v>
+        <v>5245.57</v>
       </c>
     </row>
     <row r="237">
@@ -8713,26 +8713,26 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>DPI66078</t>
+          <t>DPI64057</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>157.09</v>
+        <v>116.77</v>
       </c>
       <c r="E237" t="n">
         <v>980</v>
       </c>
       <c r="F237" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G237" t="n">
-        <v>16.03</v>
+        <v>11.92</v>
       </c>
       <c r="H237" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I237" t="n">
-        <v>67352.67999999999</v>
+        <v>47760.91</v>
       </c>
     </row>
     <row r="238">
@@ -8748,26 +8748,26 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>DPI64433</t>
+          <t>DPI63802</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>82.72</v>
+        <v>120.78</v>
       </c>
       <c r="E238" t="n">
         <v>980</v>
       </c>
       <c r="F238" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G238" t="n">
-        <v>8.44</v>
+        <v>12.32</v>
       </c>
       <c r="H238" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I238" t="n">
-        <v>35468.68</v>
+        <v>49400.06</v>
       </c>
     </row>
     <row r="239">
@@ -8783,26 +8783,26 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DPI64480</t>
+          <t>DPI66051</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>56.32</v>
+        <v>99.67</v>
       </c>
       <c r="E239" t="n">
         <v>980</v>
       </c>
       <c r="F239" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="G239" t="n">
-        <v>5.75</v>
+        <v>10.17</v>
       </c>
       <c r="H239" t="n">
-        <v>420179.55</v>
+        <v>400828.8</v>
       </c>
       <c r="I239" t="n">
-        <v>24146.22</v>
+        <v>40766.2</v>
       </c>
     </row>
     <row r="240">
@@ -8813,31 +8813,31 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DPI63958</t>
+          <t>DPI64169</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>120.83</v>
+        <v>59.46</v>
       </c>
       <c r="E240" t="n">
         <v>980</v>
       </c>
       <c r="F240" t="n">
-        <v>961</v>
+        <v>925</v>
       </c>
       <c r="G240" t="n">
-        <v>12.33</v>
+        <v>6.07</v>
       </c>
       <c r="H240" t="n">
-        <v>400421.92</v>
+        <v>400828.8</v>
       </c>
       <c r="I240" t="n">
-        <v>49372.39</v>
+        <v>24317.69</v>
       </c>
     </row>
     <row r="241">
@@ -8848,31 +8848,31 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DPI64638</t>
+          <t>DPI66715</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>88.97</v>
+        <v>131.63</v>
       </c>
       <c r="E241" t="n">
         <v>980</v>
       </c>
       <c r="F241" t="n">
-        <v>961</v>
+        <v>925</v>
       </c>
       <c r="G241" t="n">
-        <v>9.08</v>
+        <v>13.43</v>
       </c>
       <c r="H241" t="n">
-        <v>400421.92</v>
+        <v>400828.8</v>
       </c>
       <c r="I241" t="n">
-        <v>36352.65</v>
+        <v>53838.11</v>
       </c>
     </row>
     <row r="242">
@@ -8888,26 +8888,26 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DPI66307</t>
+          <t>DPI66653</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>125.94</v>
+        <v>109.8</v>
       </c>
       <c r="E242" t="n">
         <v>980</v>
       </c>
       <c r="F242" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="G242" t="n">
-        <v>12.85</v>
+        <v>11.2</v>
       </c>
       <c r="H242" t="n">
-        <v>400421.92</v>
+        <v>238853.93</v>
       </c>
       <c r="I242" t="n">
-        <v>51458.3</v>
+        <v>26761.31</v>
       </c>
     </row>
     <row r="243">
@@ -8923,26 +8923,26 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>DPI66039</t>
+          <t>DPI66449</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>114.76</v>
+        <v>191.04</v>
       </c>
       <c r="E243" t="n">
         <v>980</v>
       </c>
       <c r="F243" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="G243" t="n">
-        <v>11.71</v>
+        <v>19.49</v>
       </c>
       <c r="H243" t="n">
-        <v>400421.92</v>
+        <v>238853.93</v>
       </c>
       <c r="I243" t="n">
-        <v>46891.43</v>
+        <v>46562.19</v>
       </c>
     </row>
     <row r="244">
@@ -8958,26 +8958,26 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DPI67121</t>
+          <t>DPI67072</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>115.03</v>
+        <v>126.86</v>
       </c>
       <c r="E244" t="n">
         <v>980</v>
       </c>
       <c r="F244" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="G244" t="n">
-        <v>11.74</v>
+        <v>12.94</v>
       </c>
       <c r="H244" t="n">
-        <v>400421.92</v>
+        <v>238853.93</v>
       </c>
       <c r="I244" t="n">
-        <v>47000.66</v>
+        <v>30918.75</v>
       </c>
     </row>
     <row r="245">
@@ -8993,26 +8993,26 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DPI64136</t>
+          <t>DPI66153</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>70.68000000000001</v>
+        <v>97.33</v>
       </c>
       <c r="E245" t="n">
         <v>980</v>
       </c>
       <c r="F245" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="G245" t="n">
-        <v>7.21</v>
+        <v>9.93</v>
       </c>
       <c r="H245" t="n">
-        <v>400421.92</v>
+        <v>238853.93</v>
       </c>
       <c r="I245" t="n">
-        <v>28879.7</v>
+        <v>23721.42</v>
       </c>
     </row>
     <row r="246">
@@ -9028,26 +9028,26 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DPI66946</t>
+          <t>DPI70081</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>126.11</v>
+        <v>54.11</v>
       </c>
       <c r="E246" t="n">
         <v>980</v>
       </c>
       <c r="F246" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="G246" t="n">
-        <v>12.87</v>
+        <v>5.52</v>
       </c>
       <c r="H246" t="n">
-        <v>400421.92</v>
+        <v>238853.93</v>
       </c>
       <c r="I246" t="n">
-        <v>51526.82</v>
+        <v>13188.62</v>
       </c>
     </row>
     <row r="247">
@@ -9063,26 +9063,26 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DPI64456</t>
+          <t>DPI66154</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>111.28</v>
+        <v>73.08</v>
       </c>
       <c r="E247" t="n">
         <v>980</v>
       </c>
       <c r="F247" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="G247" t="n">
-        <v>11.36</v>
+        <v>7.46</v>
       </c>
       <c r="H247" t="n">
-        <v>400421.92</v>
+        <v>238853.93</v>
       </c>
       <c r="I247" t="n">
-        <v>45470.26</v>
+        <v>17811.66</v>
       </c>
     </row>
     <row r="248">
@@ -9098,26 +9098,26 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DPI64436</t>
+          <t>DPI66373</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>86.91</v>
+        <v>98.05</v>
       </c>
       <c r="E248" t="n">
         <v>980</v>
       </c>
       <c r="F248" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="G248" t="n">
-        <v>8.869999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="H248" t="n">
-        <v>400421.92</v>
+        <v>238853.93</v>
       </c>
       <c r="I248" t="n">
-        <v>35511.67</v>
+        <v>23897.88</v>
       </c>
     </row>
     <row r="249">
@@ -9128,31 +9128,31 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DPI70009</t>
+          <t>DPI66221</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>60.09</v>
+        <v>121.2</v>
       </c>
       <c r="E249" t="n">
         <v>980</v>
       </c>
       <c r="F249" t="n">
-        <v>978</v>
+        <v>871</v>
       </c>
       <c r="G249" t="n">
-        <v>6.13</v>
+        <v>12.37</v>
       </c>
       <c r="H249" t="n">
-        <v>425254.88</v>
+        <v>238853.93</v>
       </c>
       <c r="I249" t="n">
-        <v>26076.5</v>
+        <v>29540.83</v>
       </c>
     </row>
     <row r="250">
@@ -9168,26 +9168,26 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>DPI66742</t>
+          <t>DPI64480</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>200.32</v>
+        <v>56.32</v>
       </c>
       <c r="E250" t="n">
         <v>980</v>
       </c>
       <c r="F250" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G250" t="n">
-        <v>20.44</v>
+        <v>5.75</v>
       </c>
       <c r="H250" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I250" t="n">
-        <v>86926.96000000001</v>
+        <v>22175.3</v>
       </c>
     </row>
     <row r="251">
@@ -9203,26 +9203,26 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>DPI67178</t>
+          <t>DPI66078</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>83.31</v>
+        <v>157.09</v>
       </c>
       <c r="E251" t="n">
         <v>980</v>
       </c>
       <c r="F251" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G251" t="n">
-        <v>8.5</v>
+        <v>16.03</v>
       </c>
       <c r="H251" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I251" t="n">
-        <v>36150.03</v>
+        <v>61855.06</v>
       </c>
     </row>
     <row r="252">
@@ -9238,26 +9238,26 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>DPI64724</t>
+          <t>DPI64433</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>84.75</v>
+        <v>82.72</v>
       </c>
       <c r="E252" t="n">
         <v>980</v>
       </c>
       <c r="F252" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G252" t="n">
-        <v>8.65</v>
+        <v>8.44</v>
       </c>
       <c r="H252" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I252" t="n">
-        <v>36774.78</v>
+        <v>32573.58</v>
       </c>
     </row>
     <row r="253">
@@ -9273,26 +9273,26 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DPI63915</t>
+          <t>DPI67187</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>131.72</v>
+        <v>102.41</v>
       </c>
       <c r="E253" t="n">
         <v>980</v>
       </c>
       <c r="F253" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G253" t="n">
-        <v>13.44</v>
+        <v>10.45</v>
       </c>
       <c r="H253" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I253" t="n">
-        <v>57157.25</v>
+        <v>40326.63</v>
       </c>
     </row>
     <row r="254">
@@ -9308,26 +9308,26 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DPI64297</t>
+          <t>DPI70105</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>126.1</v>
+        <v>75.19</v>
       </c>
       <c r="E254" t="n">
         <v>980</v>
       </c>
       <c r="F254" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G254" t="n">
-        <v>12.87</v>
+        <v>7.67</v>
       </c>
       <c r="H254" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I254" t="n">
-        <v>54718.15</v>
+        <v>29608.19</v>
       </c>
     </row>
     <row r="255">
@@ -9343,26 +9343,26 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>DPI66067</t>
+          <t>DPI64436</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>139.3</v>
+        <v>86.91</v>
       </c>
       <c r="E255" t="n">
         <v>980</v>
       </c>
       <c r="F255" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G255" t="n">
-        <v>14.21</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H255" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I255" t="n">
-        <v>60448.2</v>
+        <v>34222.25</v>
       </c>
     </row>
     <row r="256">
@@ -9378,26 +9378,26 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>DPI70213</t>
+          <t>DPI64456</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>77.68000000000001</v>
+        <v>111.28</v>
       </c>
       <c r="E256" t="n">
         <v>980</v>
       </c>
       <c r="F256" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G256" t="n">
-        <v>7.93</v>
+        <v>11.36</v>
       </c>
       <c r="H256" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I256" t="n">
-        <v>33709.87</v>
+        <v>43819.24</v>
       </c>
     </row>
     <row r="257">
@@ -9413,26 +9413,26 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DPI70105</t>
+          <t>DPI66946</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>75.19</v>
+        <v>126.11</v>
       </c>
       <c r="E257" t="n">
         <v>980</v>
       </c>
       <c r="F257" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="G257" t="n">
-        <v>7.67</v>
+        <v>12.87</v>
       </c>
       <c r="H257" t="n">
-        <v>425254.88</v>
+        <v>385882.65</v>
       </c>
       <c r="I257" t="n">
-        <v>32629.16</v>
+        <v>49655.88</v>
       </c>
     </row>
     <row r="258">
@@ -9443,31 +9443,31 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DPI66923</t>
+          <t>DPI66574</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>68.56999999999999</v>
+        <v>165.71</v>
       </c>
       <c r="E258" t="n">
         <v>980</v>
       </c>
       <c r="F258" t="n">
-        <v>977</v>
+        <v>963</v>
       </c>
       <c r="G258" t="n">
-        <v>7</v>
+        <v>16.91</v>
       </c>
       <c r="H258" t="n">
-        <v>428593.16</v>
+        <v>385882.65</v>
       </c>
       <c r="I258" t="n">
-        <v>29987.26</v>
+        <v>65248.19</v>
       </c>
     </row>
     <row r="259">
@@ -9483,26 +9483,26 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DPI66658</t>
+          <t>DPI67121</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>78.34999999999999</v>
+        <v>115.03</v>
       </c>
       <c r="E259" t="n">
         <v>980</v>
       </c>
       <c r="F259" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G259" t="n">
-        <v>8</v>
+        <v>11.74</v>
       </c>
       <c r="H259" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I259" t="n">
-        <v>34266.9</v>
+        <v>20180.62</v>
       </c>
     </row>
     <row r="260">
@@ -9518,26 +9518,26 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DPI70047</t>
+          <t>DPI64450</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>76.39</v>
+        <v>49.06</v>
       </c>
       <c r="E260" t="n">
         <v>980</v>
       </c>
       <c r="F260" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G260" t="n">
-        <v>7.8</v>
+        <v>5.01</v>
       </c>
       <c r="H260" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I260" t="n">
-        <v>33409.12</v>
+        <v>8607.27</v>
       </c>
     </row>
     <row r="261">
@@ -9553,26 +9553,26 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>DPI66679</t>
+          <t>DPI64686</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>131.96</v>
+        <v>97.63</v>
       </c>
       <c r="E261" t="n">
         <v>980</v>
       </c>
       <c r="F261" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G261" t="n">
-        <v>13.47</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H261" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I261" t="n">
-        <v>57712.64</v>
+        <v>17127.9</v>
       </c>
     </row>
     <row r="262">
@@ -9588,26 +9588,26 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>DPI64431</t>
+          <t>DPI66203</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>78.73</v>
+        <v>187.41</v>
       </c>
       <c r="E262" t="n">
         <v>980</v>
       </c>
       <c r="F262" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G262" t="n">
-        <v>8.029999999999999</v>
+        <v>19.12</v>
       </c>
       <c r="H262" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I262" t="n">
-        <v>34432.21</v>
+        <v>32878.82</v>
       </c>
     </row>
     <row r="263">
@@ -9623,26 +9623,26 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DPI63919</t>
+          <t>DPI64301</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>108.37</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="E263" t="n">
         <v>980</v>
       </c>
       <c r="F263" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G263" t="n">
-        <v>11.06</v>
+        <v>10.15</v>
       </c>
       <c r="H263" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I263" t="n">
-        <v>47395.51</v>
+        <v>17457.07</v>
       </c>
     </row>
     <row r="264">
@@ -9658,26 +9658,26 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DPI70081</t>
+          <t>DFT80044</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>54.11</v>
+        <v>26.45</v>
       </c>
       <c r="E264" t="n">
         <v>980</v>
       </c>
       <c r="F264" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G264" t="n">
-        <v>5.52</v>
+        <v>2.7</v>
       </c>
       <c r="H264" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I264" t="n">
-        <v>23665.31</v>
+        <v>4639.82</v>
       </c>
     </row>
     <row r="265">
@@ -9693,26 +9693,26 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DPI66576</t>
+          <t>DPI66590</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>125.61</v>
+        <v>142.23</v>
       </c>
       <c r="E265" t="n">
         <v>980</v>
       </c>
       <c r="F265" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G265" t="n">
-        <v>12.82</v>
+        <v>14.51</v>
       </c>
       <c r="H265" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I265" t="n">
-        <v>54934.77</v>
+        <v>24953.03</v>
       </c>
     </row>
     <row r="266">
@@ -9728,26 +9728,26 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DPI66313</t>
+          <t>DPI66339</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>124.82</v>
+        <v>131.28</v>
       </c>
       <c r="E266" t="n">
         <v>980</v>
       </c>
       <c r="F266" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G266" t="n">
-        <v>12.74</v>
+        <v>13.4</v>
       </c>
       <c r="H266" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I266" t="n">
-        <v>54589.9</v>
+        <v>23032.24</v>
       </c>
     </row>
     <row r="267">
@@ -9763,26 +9763,26 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>DPI63827</t>
+          <t>DPI66387</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>130.01</v>
+        <v>108.78</v>
       </c>
       <c r="E267" t="n">
         <v>980</v>
       </c>
       <c r="F267" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="G267" t="n">
-        <v>13.27</v>
+        <v>11.1</v>
       </c>
       <c r="H267" t="n">
-        <v>428593.16</v>
+        <v>171928.75</v>
       </c>
       <c r="I267" t="n">
-        <v>56856.59</v>
+        <v>19084.36</v>
       </c>
     </row>
     <row r="268">
@@ -14838,26 +14838,26 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>DPI64273</t>
+          <t>DPI63822</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>135.21</v>
+        <v>164.81</v>
       </c>
       <c r="E412" t="n">
         <v>980</v>
       </c>
       <c r="F412" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G412" t="n">
-        <v>13.8</v>
+        <v>16.82</v>
       </c>
       <c r="H412" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I412" t="n">
-        <v>163774.07</v>
+        <v>197890.86</v>
       </c>
     </row>
     <row r="413">
@@ -14873,26 +14873,26 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>DPI64665</t>
+          <t>DPI64378</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>69.66</v>
+        <v>105.69</v>
       </c>
       <c r="E413" t="n">
         <v>980</v>
       </c>
       <c r="F413" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G413" t="n">
-        <v>7.11</v>
+        <v>10.78</v>
       </c>
       <c r="H413" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I413" t="n">
-        <v>84381.37</v>
+        <v>126900.15</v>
       </c>
     </row>
     <row r="414">
@@ -14908,26 +14908,26 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>DPI66263</t>
+          <t>DPI64255</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>123.87</v>
+        <v>119.39</v>
       </c>
       <c r="E414" t="n">
         <v>980</v>
       </c>
       <c r="F414" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G414" t="n">
-        <v>12.64</v>
+        <v>12.18</v>
       </c>
       <c r="H414" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I414" t="n">
-        <v>150042.81</v>
+        <v>143355.4</v>
       </c>
     </row>
     <row r="415">
@@ -14943,26 +14943,26 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>DPI64502</t>
+          <t>DPI63920</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>96.36</v>
+        <v>105.6</v>
       </c>
       <c r="E415" t="n">
         <v>980</v>
       </c>
       <c r="F415" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G415" t="n">
-        <v>9.83</v>
+        <v>10.78</v>
       </c>
       <c r="H415" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I415" t="n">
-        <v>116717.06</v>
+        <v>126795.13</v>
       </c>
     </row>
     <row r="416">
@@ -14978,26 +14978,26 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>DPI70120</t>
+          <t>DPI66659</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>93.91</v>
+        <v>133.62</v>
       </c>
       <c r="E416" t="n">
         <v>980</v>
       </c>
       <c r="F416" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G416" t="n">
-        <v>9.58</v>
+        <v>13.63</v>
       </c>
       <c r="H416" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I416" t="n">
-        <v>113744.63</v>
+        <v>160432.92</v>
       </c>
     </row>
     <row r="417">
@@ -15013,26 +15013,26 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>DPI64647</t>
+          <t>DPI64476</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>103.29</v>
+        <v>105.61</v>
       </c>
       <c r="E417" t="n">
         <v>980</v>
       </c>
       <c r="F417" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G417" t="n">
-        <v>10.54</v>
+        <v>10.78</v>
       </c>
       <c r="H417" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I417" t="n">
-        <v>125115.6</v>
+        <v>126811.62</v>
       </c>
     </row>
     <row r="418">
@@ -15048,26 +15048,26 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>DPI64032</t>
+          <t>DPI66175</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>85.3</v>
+        <v>174.81</v>
       </c>
       <c r="E418" t="n">
         <v>980</v>
       </c>
       <c r="F418" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G418" t="n">
-        <v>8.699999999999999</v>
+        <v>17.84</v>
       </c>
       <c r="H418" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I418" t="n">
-        <v>103325.88</v>
+        <v>209898.82</v>
       </c>
     </row>
     <row r="419">
@@ -15083,26 +15083,26 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>DPI66402</t>
+          <t>DPI70317</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>148.74</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="E419" t="n">
         <v>980</v>
       </c>
       <c r="F419" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="G419" t="n">
-        <v>15.18</v>
+        <v>7.08</v>
       </c>
       <c r="H419" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
       <c r="I419" t="n">
-        <v>180161.1</v>
+        <v>83268.33</v>
       </c>
     </row>
     <row r="420">
@@ -15113,31 +15113,31 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>DPI64758</t>
+          <t>DPI64696</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>99.53</v>
+        <v>137.67</v>
       </c>
       <c r="E420" t="n">
         <v>980</v>
       </c>
       <c r="F420" t="n">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="G420" t="n">
-        <v>10.16</v>
+        <v>14.05</v>
       </c>
       <c r="H420" t="n">
-        <v>1187034.55</v>
+        <v>1194686.49</v>
       </c>
       <c r="I420" t="n">
-        <v>120559.42</v>
+        <v>167834.86</v>
       </c>
     </row>
     <row r="421">
@@ -15153,11 +15153,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>DPI70302</t>
+          <t>DPI64179</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>51.33</v>
+        <v>138.73</v>
       </c>
       <c r="E421" t="n">
         <v>980</v>
@@ -15166,13 +15166,13 @@
         <v>968</v>
       </c>
       <c r="G421" t="n">
-        <v>5.24</v>
+        <v>14.16</v>
       </c>
       <c r="H421" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I421" t="n">
-        <v>62576.63</v>
+        <v>169126.93</v>
       </c>
     </row>
     <row r="422">
@@ -15188,11 +15188,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>DPI66262</t>
+          <t>DPI64651</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>130.59</v>
+        <v>129.73</v>
       </c>
       <c r="E422" t="n">
         <v>980</v>
@@ -15201,13 +15201,13 @@
         <v>968</v>
       </c>
       <c r="G422" t="n">
-        <v>13.33</v>
+        <v>13.24</v>
       </c>
       <c r="H422" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I422" t="n">
-        <v>159213.32</v>
+        <v>158143.67</v>
       </c>
     </row>
     <row r="423">
@@ -15223,11 +15223,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DPI70273</t>
+          <t>DPI70179</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>39.41</v>
+        <v>97.11</v>
       </c>
       <c r="E423" t="n">
         <v>980</v>
@@ -15236,13 +15236,13 @@
         <v>968</v>
       </c>
       <c r="G423" t="n">
-        <v>4.02</v>
+        <v>9.91</v>
       </c>
       <c r="H423" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I423" t="n">
-        <v>48041.12</v>
+        <v>118384.85</v>
       </c>
     </row>
     <row r="424">
@@ -15258,11 +15258,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>DPI70179</t>
+          <t>DPI70273</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>97.11</v>
+        <v>39.41</v>
       </c>
       <c r="E424" t="n">
         <v>980</v>
@@ -15271,13 +15271,13 @@
         <v>968</v>
       </c>
       <c r="G424" t="n">
-        <v>9.91</v>
+        <v>4.02</v>
       </c>
       <c r="H424" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I424" t="n">
-        <v>118392.75</v>
+        <v>48037.92</v>
       </c>
     </row>
     <row r="425">
@@ -15293,11 +15293,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>DPI64651</t>
+          <t>DPI66144</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>129.73</v>
+        <v>99.38</v>
       </c>
       <c r="E425" t="n">
         <v>980</v>
@@ -15306,13 +15306,13 @@
         <v>968</v>
       </c>
       <c r="G425" t="n">
-        <v>13.24</v>
+        <v>10.14</v>
       </c>
       <c r="H425" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I425" t="n">
-        <v>158154.22</v>
+        <v>121145.84</v>
       </c>
     </row>
     <row r="426">
@@ -15328,11 +15328,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>DPI66144</t>
+          <t>DPI63847</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>99.38</v>
+        <v>144.26</v>
       </c>
       <c r="E426" t="n">
         <v>980</v>
@@ -15341,13 +15341,13 @@
         <v>968</v>
       </c>
       <c r="G426" t="n">
-        <v>10.14</v>
+        <v>14.72</v>
       </c>
       <c r="H426" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I426" t="n">
-        <v>121153.92</v>
+        <v>175868.54</v>
       </c>
     </row>
     <row r="427">
@@ -15363,11 +15363,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>DPI63847</t>
+          <t>DPI66262</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>144.26</v>
+        <v>130.59</v>
       </c>
       <c r="E427" t="n">
         <v>980</v>
@@ -15376,13 +15376,13 @@
         <v>968</v>
       </c>
       <c r="G427" t="n">
-        <v>14.72</v>
+        <v>13.33</v>
       </c>
       <c r="H427" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I427" t="n">
-        <v>175880.27</v>
+        <v>159202.7</v>
       </c>
     </row>
     <row r="428">
@@ -15398,11 +15398,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>DPI64179</t>
+          <t>DPI70302</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>138.73</v>
+        <v>51.33</v>
       </c>
       <c r="E428" t="n">
         <v>980</v>
@@ -15411,13 +15411,13 @@
         <v>968</v>
       </c>
       <c r="G428" t="n">
-        <v>14.16</v>
+        <v>5.24</v>
       </c>
       <c r="H428" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
       <c r="I428" t="n">
-        <v>169138.21</v>
+        <v>62572.46</v>
       </c>
     </row>
     <row r="429">
@@ -15428,31 +15428,31 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>DPI64696</t>
+          <t>DPI66263</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>137.67</v>
+        <v>123.87</v>
       </c>
       <c r="E429" t="n">
         <v>980</v>
       </c>
       <c r="F429" t="n">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="G429" t="n">
-        <v>14.05</v>
+        <v>12.64</v>
       </c>
       <c r="H429" t="n">
-        <v>1194766.18</v>
+        <v>1208267.36</v>
       </c>
       <c r="I429" t="n">
-        <v>167846.06</v>
+        <v>152726.67</v>
       </c>
     </row>
     <row r="430">
@@ -15468,26 +15468,26 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>DPI63822</t>
+          <t>DPI64665</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>164.81</v>
+        <v>69.66</v>
       </c>
       <c r="E430" t="n">
         <v>980</v>
       </c>
       <c r="F430" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G430" t="n">
-        <v>16.82</v>
+        <v>7.11</v>
       </c>
       <c r="H430" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I430" t="n">
-        <v>197890.86</v>
+        <v>85890.72</v>
       </c>
     </row>
     <row r="431">
@@ -15503,26 +15503,26 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>DPI64378</t>
+          <t>DPI64502</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>105.69</v>
+        <v>96.36</v>
       </c>
       <c r="E431" t="n">
         <v>980</v>
       </c>
       <c r="F431" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G431" t="n">
-        <v>10.78</v>
+        <v>9.83</v>
       </c>
       <c r="H431" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I431" t="n">
-        <v>126900.15</v>
+        <v>118804.81</v>
       </c>
     </row>
     <row r="432">
@@ -15538,26 +15538,26 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>DPI64255</t>
+          <t>DPI70120</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>119.39</v>
+        <v>93.91</v>
       </c>
       <c r="E432" t="n">
         <v>980</v>
       </c>
       <c r="F432" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G432" t="n">
-        <v>12.18</v>
+        <v>9.58</v>
       </c>
       <c r="H432" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I432" t="n">
-        <v>143355.4</v>
+        <v>115779.21</v>
       </c>
     </row>
     <row r="433">
@@ -15573,26 +15573,26 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>DPI63920</t>
+          <t>DPI64647</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>105.6</v>
+        <v>103.29</v>
       </c>
       <c r="E433" t="n">
         <v>980</v>
       </c>
       <c r="F433" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G433" t="n">
-        <v>10.78</v>
+        <v>10.54</v>
       </c>
       <c r="H433" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I433" t="n">
-        <v>126795.13</v>
+        <v>127353.57</v>
       </c>
     </row>
     <row r="434">
@@ -15608,26 +15608,26 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>DPI66659</t>
+          <t>DPI64032</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>133.62</v>
+        <v>85.3</v>
       </c>
       <c r="E434" t="n">
         <v>980</v>
       </c>
       <c r="F434" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G434" t="n">
-        <v>13.63</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H434" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I434" t="n">
-        <v>160432.92</v>
+        <v>105174.1</v>
       </c>
     </row>
     <row r="435">
@@ -15643,26 +15643,26 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>DPI64476</t>
+          <t>DPI66402</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>105.61</v>
+        <v>148.74</v>
       </c>
       <c r="E435" t="n">
         <v>980</v>
       </c>
       <c r="F435" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G435" t="n">
-        <v>10.78</v>
+        <v>15.18</v>
       </c>
       <c r="H435" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I435" t="n">
-        <v>126811.62</v>
+        <v>183383.69</v>
       </c>
     </row>
     <row r="436">
@@ -15678,26 +15678,26 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>DPI66175</t>
+          <t>DPI64409</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>174.81</v>
+        <v>92.92</v>
       </c>
       <c r="E436" t="n">
         <v>980</v>
       </c>
       <c r="F436" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G436" t="n">
-        <v>17.84</v>
+        <v>9.48</v>
       </c>
       <c r="H436" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I436" t="n">
-        <v>209898.82</v>
+        <v>114564.53</v>
       </c>
     </row>
     <row r="437">
@@ -15713,26 +15713,26 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>DPI70317</t>
+          <t>DPI64273</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>69.34999999999999</v>
+        <v>135.21</v>
       </c>
       <c r="E437" t="n">
         <v>980</v>
       </c>
       <c r="F437" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G437" t="n">
-        <v>7.08</v>
+        <v>13.8</v>
       </c>
       <c r="H437" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
       <c r="I437" t="n">
-        <v>83268.33</v>
+        <v>166703.54</v>
       </c>
     </row>
     <row r="438">
@@ -16098,26 +16098,26 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>DPI66264</t>
+          <t>DPI66684</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>147.75</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E448" t="n">
         <v>980</v>
       </c>
       <c r="F448" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G448" t="n">
-        <v>15.08</v>
+        <v>9.41</v>
       </c>
       <c r="H448" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I448" t="n">
-        <v>194402.2</v>
+        <v>134521.01</v>
       </c>
     </row>
     <row r="449">
@@ -16133,26 +16133,26 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>DPI66684</t>
+          <t>DPI64236</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>92.23999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E449" t="n">
         <v>980</v>
       </c>
       <c r="F449" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G449" t="n">
-        <v>9.41</v>
+        <v>7.12</v>
       </c>
       <c r="H449" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I449" t="n">
-        <v>121363.42</v>
+        <v>101706.43</v>
       </c>
     </row>
     <row r="450">
@@ -16168,26 +16168,26 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>DPI67031</t>
+          <t>DPI66734</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>136.7</v>
+        <v>111.78</v>
       </c>
       <c r="E450" t="n">
         <v>980</v>
       </c>
       <c r="F450" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G450" t="n">
-        <v>13.95</v>
+        <v>11.41</v>
       </c>
       <c r="H450" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I450" t="n">
-        <v>179870.94</v>
+        <v>163025.91</v>
       </c>
     </row>
     <row r="451">
@@ -16203,26 +16203,26 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>DPI64352</t>
+          <t>DPI70073</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>100.22</v>
+        <v>53.01</v>
       </c>
       <c r="E451" t="n">
         <v>980</v>
       </c>
       <c r="F451" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G451" t="n">
-        <v>10.23</v>
+        <v>5.41</v>
       </c>
       <c r="H451" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I451" t="n">
-        <v>131867.64</v>
+        <v>77306.64999999999</v>
       </c>
     </row>
     <row r="452">
@@ -16238,26 +16238,26 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>DPI64288</t>
+          <t>DPI70038</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>116.14</v>
+        <v>100.52</v>
       </c>
       <c r="E452" t="n">
         <v>980</v>
       </c>
       <c r="F452" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G452" t="n">
-        <v>11.85</v>
+        <v>10.26</v>
       </c>
       <c r="H452" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I452" t="n">
-        <v>152813.09</v>
+        <v>146597.34</v>
       </c>
     </row>
     <row r="453">
@@ -16273,26 +16273,26 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>DPI67024</t>
+          <t>DPI64149</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>96.65000000000001</v>
+        <v>43.53</v>
       </c>
       <c r="E453" t="n">
         <v>980</v>
       </c>
       <c r="F453" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G453" t="n">
-        <v>9.859999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="H453" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I453" t="n">
-        <v>127168.01</v>
+        <v>63479.22</v>
       </c>
     </row>
     <row r="454">
@@ -16308,26 +16308,26 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>DPI70041</t>
+          <t>DPI66572</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>72.68000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="E454" t="n">
         <v>980</v>
       </c>
       <c r="F454" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G454" t="n">
-        <v>7.42</v>
+        <v>8.23</v>
       </c>
       <c r="H454" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I454" t="n">
-        <v>95632.84</v>
+        <v>117675.91</v>
       </c>
     </row>
     <row r="455">
@@ -16343,26 +16343,26 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>DPI66646</t>
+          <t>DPI64234</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>154.63</v>
+        <v>68.98</v>
       </c>
       <c r="E455" t="n">
         <v>980</v>
       </c>
       <c r="F455" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="G455" t="n">
-        <v>15.78</v>
+        <v>7.04</v>
       </c>
       <c r="H455" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
       <c r="I455" t="n">
-        <v>203456.53</v>
+        <v>100598.82</v>
       </c>
     </row>
     <row r="456">
@@ -16373,31 +16373,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>DPI64104</t>
+          <t>DPI64176</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>105.14</v>
+        <v>51.79</v>
       </c>
       <c r="E456" t="n">
         <v>980</v>
       </c>
       <c r="F456" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G456" t="n">
-        <v>10.73</v>
+        <v>5.29</v>
       </c>
       <c r="H456" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I456" t="n">
-        <v>153461.79</v>
+        <v>75536.19</v>
       </c>
     </row>
     <row r="457">
@@ -16408,31 +16408,31 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>DPI64236</t>
+          <t>DPI66460</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>69.73999999999999</v>
+        <v>71.19</v>
       </c>
       <c r="E457" t="n">
         <v>980</v>
       </c>
       <c r="F457" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G457" t="n">
-        <v>7.12</v>
+        <v>7.26</v>
       </c>
       <c r="H457" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I457" t="n">
-        <v>101791.56</v>
+        <v>103824.89</v>
       </c>
     </row>
     <row r="458">
@@ -16443,31 +16443,31 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>DPI66734</t>
+          <t>DPI63993</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>111.78</v>
+        <v>56.56</v>
       </c>
       <c r="E458" t="n">
         <v>980</v>
       </c>
       <c r="F458" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G458" t="n">
-        <v>11.41</v>
+        <v>5.77</v>
       </c>
       <c r="H458" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I458" t="n">
-        <v>163162.37</v>
+        <v>82486.36</v>
       </c>
     </row>
     <row r="459">
@@ -16478,31 +16478,31 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>DPI70073</t>
+          <t>DPI64044</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>53.01</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E459" t="n">
         <v>980</v>
       </c>
       <c r="F459" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G459" t="n">
-        <v>5.41</v>
+        <v>6.73</v>
       </c>
       <c r="H459" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I459" t="n">
-        <v>77371.36</v>
+        <v>96240.39999999999</v>
       </c>
     </row>
     <row r="460">
@@ -16513,31 +16513,31 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>DPI70038</t>
+          <t>DPI64639</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>100.52</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="E460" t="n">
         <v>980</v>
       </c>
       <c r="F460" t="n">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="G460" t="n">
-        <v>10.26</v>
+        <v>7.84</v>
       </c>
       <c r="H460" t="n">
-        <v>1430444.75</v>
+        <v>1429248.42</v>
       </c>
       <c r="I460" t="n">
-        <v>146720.05</v>
+        <v>111994.48</v>
       </c>
     </row>
     <row r="461">
@@ -16553,26 +16553,26 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>DPI64149</t>
+          <t>DPI64758</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>43.53</v>
+        <v>99.53</v>
       </c>
       <c r="E461" t="n">
         <v>980</v>
       </c>
       <c r="F461" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G461" t="n">
-        <v>4.44</v>
+        <v>10.16</v>
       </c>
       <c r="H461" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I461" t="n">
-        <v>63532.36</v>
+        <v>116509.13</v>
       </c>
     </row>
     <row r="462">
@@ -16588,26 +16588,26 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>DPI66572</t>
+          <t>DPI66421</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>80.69</v>
+        <v>273.07</v>
       </c>
       <c r="E462" t="n">
         <v>980</v>
       </c>
       <c r="F462" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G462" t="n">
-        <v>8.23</v>
+        <v>27.86</v>
       </c>
       <c r="H462" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I462" t="n">
-        <v>117774.41</v>
+        <v>319641.14</v>
       </c>
     </row>
     <row r="463">
@@ -16623,26 +16623,26 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>DPI64234</t>
+          <t>DPI67128</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>68.98</v>
+        <v>107.28</v>
       </c>
       <c r="E463" t="n">
         <v>980</v>
       </c>
       <c r="F463" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G463" t="n">
-        <v>7.04</v>
+        <v>10.95</v>
       </c>
       <c r="H463" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I463" t="n">
-        <v>100683.02</v>
+        <v>125577.67</v>
       </c>
     </row>
     <row r="464">
@@ -16658,26 +16658,26 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>DPI64176</t>
+          <t>DPI70100</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>51.79</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E464" t="n">
         <v>980</v>
       </c>
       <c r="F464" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G464" t="n">
-        <v>5.29</v>
+        <v>6.67</v>
       </c>
       <c r="H464" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I464" t="n">
-        <v>75599.41</v>
+        <v>76551.61</v>
       </c>
     </row>
     <row r="465">
@@ -16693,26 +16693,26 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>DPI66460</t>
+          <t>DPI64303</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>71.19</v>
+        <v>103.22</v>
       </c>
       <c r="E465" t="n">
         <v>980</v>
       </c>
       <c r="F465" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G465" t="n">
-        <v>7.26</v>
+        <v>10.53</v>
       </c>
       <c r="H465" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I465" t="n">
-        <v>103911.8</v>
+        <v>120828.79</v>
       </c>
     </row>
     <row r="466">
@@ -16728,26 +16728,26 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>DPI63993</t>
+          <t>DPI66528</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>56.56</v>
+        <v>108.07</v>
       </c>
       <c r="E466" t="n">
         <v>980</v>
       </c>
       <c r="F466" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G466" t="n">
-        <v>5.77</v>
+        <v>11.03</v>
       </c>
       <c r="H466" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I466" t="n">
-        <v>82555.39999999999</v>
+        <v>126504.97</v>
       </c>
     </row>
     <row r="467">
@@ -16763,26 +16763,26 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DPI64044</t>
+          <t>DPI64692</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>65.98999999999999</v>
+        <v>133.08</v>
       </c>
       <c r="E467" t="n">
         <v>980</v>
       </c>
       <c r="F467" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G467" t="n">
-        <v>6.73</v>
+        <v>13.58</v>
       </c>
       <c r="H467" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I467" t="n">
-        <v>96320.95</v>
+        <v>155778.71</v>
       </c>
     </row>
     <row r="468">
@@ -16798,26 +16798,26 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>DPI64639</t>
+          <t>DPI67198</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>76.79000000000001</v>
+        <v>90.89</v>
       </c>
       <c r="E468" t="n">
         <v>980</v>
       </c>
       <c r="F468" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="G468" t="n">
-        <v>7.84</v>
+        <v>9.27</v>
       </c>
       <c r="H468" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
       <c r="I468" t="n">
-        <v>112088.22</v>
+        <v>106392.84</v>
       </c>
     </row>
     <row r="469">
@@ -16833,26 +16833,26 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>DPI64409</t>
+          <t>DPI64104</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>92.92</v>
+        <v>105.14</v>
       </c>
       <c r="E469" t="n">
         <v>980</v>
       </c>
       <c r="F469" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G469" t="n">
-        <v>9.48</v>
+        <v>10.73</v>
       </c>
       <c r="H469" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I469" t="n">
-        <v>108820.44</v>
+        <v>138497.76</v>
       </c>
     </row>
     <row r="470">
@@ -16868,26 +16868,26 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>DPI66421</t>
+          <t>DPI66646</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>273.07</v>
+        <v>154.63</v>
       </c>
       <c r="E470" t="n">
         <v>980</v>
       </c>
       <c r="F470" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G470" t="n">
-        <v>27.86</v>
+        <v>15.78</v>
       </c>
       <c r="H470" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I470" t="n">
-        <v>319789.24</v>
+        <v>203694.74</v>
       </c>
     </row>
     <row r="471">
@@ -16903,26 +16903,26 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>DPI67128</t>
+          <t>DPI70041</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>107.28</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="E471" t="n">
         <v>980</v>
       </c>
       <c r="F471" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G471" t="n">
-        <v>10.95</v>
+        <v>7.42</v>
       </c>
       <c r="H471" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I471" t="n">
-        <v>125635.86</v>
+        <v>95744.8</v>
       </c>
     </row>
     <row r="472">
@@ -16938,26 +16938,26 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>DPI70100</t>
+          <t>DPI67024</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>65.40000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="E472" t="n">
         <v>980</v>
       </c>
       <c r="F472" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G472" t="n">
-        <v>6.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H472" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I472" t="n">
-        <v>76587.08</v>
+        <v>127316.9</v>
       </c>
     </row>
     <row r="473">
@@ -16973,26 +16973,26 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>DPI64303</t>
+          <t>DPI64288</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>103.22</v>
+        <v>116.14</v>
       </c>
       <c r="E473" t="n">
         <v>980</v>
       </c>
       <c r="F473" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G473" t="n">
-        <v>10.53</v>
+        <v>11.85</v>
       </c>
       <c r="H473" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I473" t="n">
-        <v>120884.77</v>
+        <v>152992</v>
       </c>
     </row>
     <row r="474">
@@ -17008,26 +17008,26 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>DPI66528</t>
+          <t>DPI64352</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>108.07</v>
+        <v>100.22</v>
       </c>
       <c r="E474" t="n">
         <v>980</v>
       </c>
       <c r="F474" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G474" t="n">
-        <v>11.03</v>
+        <v>10.23</v>
       </c>
       <c r="H474" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I474" t="n">
-        <v>126563.59</v>
+        <v>132022.03</v>
       </c>
     </row>
     <row r="475">
@@ -17043,26 +17043,26 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>DPI64692</t>
+          <t>DPI67031</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>133.08</v>
+        <v>136.7</v>
       </c>
       <c r="E475" t="n">
         <v>980</v>
       </c>
       <c r="F475" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G475" t="n">
-        <v>13.58</v>
+        <v>13.95</v>
       </c>
       <c r="H475" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I475" t="n">
-        <v>155850.89</v>
+        <v>180081.53</v>
       </c>
     </row>
     <row r="476">
@@ -17078,26 +17078,26 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>DPI67198</t>
+          <t>DPI66264</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>90.89</v>
+        <v>147.75</v>
       </c>
       <c r="E476" t="n">
         <v>980</v>
       </c>
       <c r="F476" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="G476" t="n">
-        <v>9.27</v>
+        <v>15.08</v>
       </c>
       <c r="H476" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
       <c r="I476" t="n">
-        <v>106442.13</v>
+        <v>194629.81</v>
       </c>
     </row>
     <row r="477">

--- a/store_wise_monthly_costs.xlsx
+++ b/store_wise_monthly_costs.xlsx
@@ -5878,26 +5878,26 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DPI64218</t>
+          <t>DPI66387</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>52.55</v>
+        <v>108.78</v>
       </c>
       <c r="E156" t="n">
         <v>980</v>
       </c>
       <c r="F156" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G156" t="n">
-        <v>5.36</v>
+        <v>11.1</v>
       </c>
       <c r="H156" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I156" t="n">
-        <v>15775.97</v>
+        <v>44354.55</v>
       </c>
     </row>
     <row r="157">
@@ -5913,26 +5913,26 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DPI66289</t>
+          <t>DPI70316</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>38.55</v>
+        <v>48.44</v>
       </c>
       <c r="E157" t="n">
         <v>980</v>
       </c>
       <c r="F157" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G157" t="n">
-        <v>3.93</v>
+        <v>4.94</v>
       </c>
       <c r="H157" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I157" t="n">
-        <v>11573.17</v>
+        <v>19749.25</v>
       </c>
     </row>
     <row r="158">
@@ -5948,26 +5948,26 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DPI64039</t>
+          <t>DPI64216</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>98.41</v>
+        <v>79.38</v>
       </c>
       <c r="E158" t="n">
         <v>980</v>
       </c>
       <c r="F158" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G158" t="n">
-        <v>10.04</v>
+        <v>8.1</v>
       </c>
       <c r="H158" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I158" t="n">
-        <v>29542.65</v>
+        <v>32367.52</v>
       </c>
     </row>
     <row r="159">
@@ -5983,26 +5983,26 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DPI66069</t>
+          <t>DFT80088</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>182.8</v>
+        <v>35.23</v>
       </c>
       <c r="E159" t="n">
         <v>980</v>
       </c>
       <c r="F159" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G159" t="n">
-        <v>18.65</v>
+        <v>3.6</v>
       </c>
       <c r="H159" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I159" t="n">
-        <v>54873.91</v>
+        <v>14365.11</v>
       </c>
     </row>
     <row r="160">
@@ -6018,26 +6018,26 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DPI70255</t>
+          <t>DPI64413</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>63.7</v>
+        <v>72.22</v>
       </c>
       <c r="E160" t="n">
         <v>980</v>
       </c>
       <c r="F160" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G160" t="n">
-        <v>6.5</v>
+        <v>7.37</v>
       </c>
       <c r="H160" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I160" t="n">
-        <v>19120.66</v>
+        <v>29445.08</v>
       </c>
     </row>
     <row r="161">
@@ -6053,26 +6053,26 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>DPI66645</t>
+          <t>DPI70096</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>127.76</v>
+        <v>59.61</v>
       </c>
       <c r="E161" t="n">
         <v>980</v>
       </c>
       <c r="F161" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G161" t="n">
-        <v>13.04</v>
+        <v>6.08</v>
       </c>
       <c r="H161" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I161" t="n">
-        <v>38352.29</v>
+        <v>24304.06</v>
       </c>
     </row>
     <row r="162">
@@ -6088,26 +6088,26 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DPI64413</t>
+          <t>DPI64037</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>72.22</v>
+        <v>27.36</v>
       </c>
       <c r="E162" t="n">
         <v>980</v>
       </c>
       <c r="F162" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G162" t="n">
-        <v>7.37</v>
+        <v>2.79</v>
       </c>
       <c r="H162" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I162" t="n">
-        <v>21678.26</v>
+        <v>11157.79</v>
       </c>
     </row>
     <row r="163">
@@ -6123,26 +6123,26 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DPI64244</t>
+          <t>DPI66172</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>126.9</v>
+        <v>12.83</v>
       </c>
       <c r="E163" t="n">
         <v>980</v>
       </c>
       <c r="F163" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G163" t="n">
-        <v>12.95</v>
+        <v>1.31</v>
       </c>
       <c r="H163" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I163" t="n">
-        <v>38093.76</v>
+        <v>5229.29</v>
       </c>
     </row>
     <row r="164">
@@ -6158,26 +6158,26 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DFT80088</t>
+          <t>DPI64057</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>35.23</v>
+        <v>116.77</v>
       </c>
       <c r="E164" t="n">
         <v>980</v>
       </c>
       <c r="F164" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G164" t="n">
-        <v>3.6</v>
+        <v>11.92</v>
       </c>
       <c r="H164" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I164" t="n">
-        <v>10575.98</v>
+        <v>47612.69</v>
       </c>
     </row>
     <row r="165">
@@ -6193,26 +6193,26 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DPI64216</t>
+          <t>DPI63802</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>79.38</v>
+        <v>120.78</v>
       </c>
       <c r="E165" t="n">
         <v>980</v>
       </c>
       <c r="F165" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G165" t="n">
-        <v>8.1</v>
+        <v>12.32</v>
       </c>
       <c r="H165" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I165" t="n">
-        <v>23829.84</v>
+        <v>49246.75</v>
       </c>
     </row>
     <row r="166">
@@ -6228,26 +6228,26 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DPI70316</t>
+          <t>DPI66051</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>48.44</v>
+        <v>99.67</v>
       </c>
       <c r="E166" t="n">
         <v>980</v>
       </c>
       <c r="F166" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="G166" t="n">
-        <v>4.94</v>
+        <v>10.17</v>
       </c>
       <c r="H166" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
       <c r="I166" t="n">
-        <v>14539.92</v>
+        <v>40639.69</v>
       </c>
     </row>
     <row r="167">
@@ -6258,31 +6258,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DPI70142</t>
+          <t>DPI64169</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>63.66</v>
+        <v>59.46</v>
       </c>
       <c r="E167" t="n">
         <v>980</v>
       </c>
       <c r="F167" t="n">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="G167" t="n">
-        <v>6.5</v>
+        <v>6.07</v>
       </c>
       <c r="H167" t="n">
-        <v>379616.42</v>
+        <v>399584.88</v>
       </c>
       <c r="I167" t="n">
-        <v>24660.27</v>
+        <v>24242.22</v>
       </c>
     </row>
     <row r="168">
@@ -6293,31 +6293,31 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DPI66742</t>
+          <t>DPI66715</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>200.32</v>
+        <v>131.63</v>
       </c>
       <c r="E168" t="n">
         <v>980</v>
       </c>
       <c r="F168" t="n">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="G168" t="n">
-        <v>20.44</v>
+        <v>13.43</v>
       </c>
       <c r="H168" t="n">
-        <v>379616.42</v>
+        <v>399584.88</v>
       </c>
       <c r="I168" t="n">
-        <v>77597.92999999999</v>
+        <v>53671.03</v>
       </c>
     </row>
     <row r="169">
@@ -6333,26 +6333,26 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DPI63915</t>
+          <t>DPI70081</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>131.72</v>
+        <v>54.11</v>
       </c>
       <c r="E169" t="n">
         <v>980</v>
       </c>
       <c r="F169" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G169" t="n">
-        <v>13.44</v>
+        <v>5.52</v>
       </c>
       <c r="H169" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
       <c r="I169" t="n">
-        <v>51023.12</v>
+        <v>24900.89</v>
       </c>
     </row>
     <row r="170">
@@ -6368,26 +6368,26 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DPI64724</t>
+          <t>DPI64624</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>84.75</v>
+        <v>119.04</v>
       </c>
       <c r="E170" t="n">
         <v>980</v>
       </c>
       <c r="F170" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G170" t="n">
-        <v>8.65</v>
+        <v>12.15</v>
       </c>
       <c r="H170" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
       <c r="I170" t="n">
-        <v>32828.1</v>
+        <v>54778.25</v>
       </c>
     </row>
     <row r="171">
@@ -6403,26 +6403,26 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DPI67178</t>
+          <t>DPI66102</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>83.31</v>
+        <v>124.24</v>
       </c>
       <c r="E171" t="n">
         <v>980</v>
       </c>
       <c r="F171" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G171" t="n">
-        <v>8.5</v>
+        <v>12.68</v>
       </c>
       <c r="H171" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
       <c r="I171" t="n">
-        <v>32270.4</v>
+        <v>57174.23</v>
       </c>
     </row>
     <row r="172">
@@ -6438,26 +6438,26 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DPI64297</t>
+          <t>DPI64166</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>126.1</v>
+        <v>56.77</v>
       </c>
       <c r="E172" t="n">
         <v>980</v>
       </c>
       <c r="F172" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G172" t="n">
-        <v>12.87</v>
+        <v>5.79</v>
       </c>
       <c r="H172" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
       <c r="I172" t="n">
-        <v>48845.79</v>
+        <v>26124.7</v>
       </c>
     </row>
     <row r="173">
@@ -6473,26 +6473,26 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>DPI66067</t>
+          <t>DPI66384</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>139.3</v>
+        <v>156.23</v>
       </c>
       <c r="E173" t="n">
         <v>980</v>
       </c>
       <c r="F173" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G173" t="n">
-        <v>14.21</v>
+        <v>15.94</v>
       </c>
       <c r="H173" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
       <c r="I173" t="n">
-        <v>53960.89</v>
+        <v>71892.25999999999</v>
       </c>
     </row>
     <row r="174">
@@ -6508,26 +6508,26 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DPI70213</t>
+          <t>DPI66408</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>77.68000000000001</v>
+        <v>147.34</v>
       </c>
       <c r="E174" t="n">
         <v>980</v>
       </c>
       <c r="F174" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G174" t="n">
-        <v>7.93</v>
+        <v>15.03</v>
       </c>
       <c r="H174" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
       <c r="I174" t="n">
-        <v>30092.12</v>
+        <v>67800.67</v>
       </c>
     </row>
     <row r="175">
@@ -6543,26 +6543,26 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DPI64136</t>
+          <t>DPI64392</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>70.68000000000001</v>
+        <v>79.42</v>
       </c>
       <c r="E175" t="n">
         <v>980</v>
       </c>
       <c r="F175" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G175" t="n">
-        <v>7.21</v>
+        <v>8.1</v>
       </c>
       <c r="H175" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
       <c r="I175" t="n">
-        <v>27379.14</v>
+        <v>36548.72</v>
       </c>
     </row>
     <row r="176">
@@ -6573,31 +6573,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>DPI66736</t>
+          <t>DPI66618</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>136.37</v>
+        <v>133.15</v>
       </c>
       <c r="E176" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="F176" t="n">
-        <v>520</v>
+        <v>979</v>
       </c>
       <c r="G176" t="n">
-        <v>20.66</v>
+        <v>13.59</v>
       </c>
       <c r="H176" t="n">
-        <v>423299.77</v>
+        <v>450970.31</v>
       </c>
       <c r="I176" t="n">
-        <v>87461.35000000001</v>
+        <v>61272.11</v>
       </c>
     </row>
     <row r="177">
@@ -6608,31 +6608,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>DPI70229</t>
+          <t>DPI66653</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>65.84999999999999</v>
+        <v>109.8</v>
       </c>
       <c r="E177" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="F177" t="n">
-        <v>520</v>
+        <v>979</v>
       </c>
       <c r="G177" t="n">
-        <v>9.98</v>
+        <v>11.2</v>
       </c>
       <c r="H177" t="n">
-        <v>423299.77</v>
+        <v>450970.31</v>
       </c>
       <c r="I177" t="n">
-        <v>42230.86</v>
+        <v>50526.93</v>
       </c>
     </row>
     <row r="178">
@@ -6648,26 +6648,26 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>DPI64018</t>
+          <t>DPI67178</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>161.85</v>
+        <v>83.31</v>
       </c>
       <c r="E178" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="F178" t="n">
-        <v>520</v>
+        <v>965</v>
       </c>
       <c r="G178" t="n">
-        <v>24.52</v>
+        <v>8.5</v>
       </c>
       <c r="H178" t="n">
-        <v>423299.77</v>
+        <v>438859.68</v>
       </c>
       <c r="I178" t="n">
-        <v>103804.77</v>
+        <v>37306.54</v>
       </c>
     </row>
     <row r="179">
@@ -6683,26 +6683,26 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>DPI66096</t>
+          <t>DPI64297</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>156.26</v>
+        <v>126.1</v>
       </c>
       <c r="E179" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="F179" t="n">
-        <v>520</v>
+        <v>965</v>
       </c>
       <c r="G179" t="n">
-        <v>23.68</v>
+        <v>12.87</v>
       </c>
       <c r="H179" t="n">
-        <v>423299.77</v>
+        <v>438859.68</v>
       </c>
       <c r="I179" t="n">
-        <v>100221.1</v>
+        <v>56468.7</v>
       </c>
     </row>
     <row r="180">
@@ -6713,31 +6713,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>DPI64196</t>
+          <t>DPI63915</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>79.7</v>
+        <v>131.72</v>
       </c>
       <c r="E180" t="n">
         <v>980</v>
       </c>
       <c r="F180" t="n">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G180" t="n">
-        <v>8.130000000000001</v>
+        <v>13.44</v>
       </c>
       <c r="H180" t="n">
-        <v>449432.3</v>
+        <v>438859.68</v>
       </c>
       <c r="I180" t="n">
-        <v>36551.93</v>
+        <v>58985.83</v>
       </c>
     </row>
     <row r="181">
@@ -6748,31 +6748,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DPI64624</t>
+          <t>DPI64724</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>119.04</v>
+        <v>84.75</v>
       </c>
       <c r="E181" t="n">
         <v>980</v>
       </c>
       <c r="F181" t="n">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G181" t="n">
-        <v>12.15</v>
+        <v>8.65</v>
       </c>
       <c r="H181" t="n">
-        <v>449432.3</v>
+        <v>438859.68</v>
       </c>
       <c r="I181" t="n">
-        <v>54591.43</v>
+        <v>37951.29</v>
       </c>
     </row>
     <row r="182">
@@ -6783,31 +6783,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>DPI66102</t>
+          <t>DPI66742</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>124.24</v>
+        <v>200.32</v>
       </c>
       <c r="E182" t="n">
         <v>980</v>
       </c>
       <c r="F182" t="n">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G182" t="n">
-        <v>12.68</v>
+        <v>20.44</v>
       </c>
       <c r="H182" t="n">
-        <v>449432.3</v>
+        <v>438859.68</v>
       </c>
       <c r="I182" t="n">
-        <v>56979.24</v>
+        <v>89707.92999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6818,31 +6818,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>DPI64166</t>
+          <t>DPI66067</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>56.77</v>
+        <v>139.3</v>
       </c>
       <c r="E183" t="n">
         <v>980</v>
       </c>
       <c r="F183" t="n">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G183" t="n">
-        <v>5.79</v>
+        <v>14.21</v>
       </c>
       <c r="H183" t="n">
-        <v>449432.3</v>
+        <v>438859.68</v>
       </c>
       <c r="I183" t="n">
-        <v>26035.6</v>
+        <v>62382.07</v>
       </c>
     </row>
     <row r="184">
@@ -6853,31 +6853,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>DPI66384</t>
+          <t>DPI70213</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>156.23</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="E184" t="n">
         <v>980</v>
       </c>
       <c r="F184" t="n">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G184" t="n">
-        <v>15.94</v>
+        <v>7.93</v>
       </c>
       <c r="H184" t="n">
-        <v>449432.3</v>
+        <v>438859.68</v>
       </c>
       <c r="I184" t="n">
-        <v>71647.08</v>
+        <v>34788.32</v>
       </c>
     </row>
     <row r="185">
@@ -6888,31 +6888,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>DPI66408</t>
+          <t>DPI70105</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>147.34</v>
+        <v>75.19</v>
       </c>
       <c r="E185" t="n">
         <v>980</v>
       </c>
       <c r="F185" t="n">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G185" t="n">
-        <v>15.03</v>
+        <v>7.67</v>
       </c>
       <c r="H185" t="n">
-        <v>449432.3</v>
+        <v>438859.68</v>
       </c>
       <c r="I185" t="n">
-        <v>67569.44</v>
+        <v>33673.03</v>
       </c>
     </row>
     <row r="186">
@@ -6923,31 +6923,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>DPI64392</t>
+          <t>DFT80077</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>79.42</v>
+        <v>46.73</v>
       </c>
       <c r="E186" t="n">
         <v>980</v>
       </c>
       <c r="F186" t="n">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="G186" t="n">
-        <v>8.1</v>
+        <v>4.77</v>
       </c>
       <c r="H186" t="n">
-        <v>449432.3</v>
+        <v>438859.68</v>
       </c>
       <c r="I186" t="n">
-        <v>36424.07</v>
+        <v>20926.67</v>
       </c>
     </row>
     <row r="187">
@@ -6963,26 +6963,26 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>DPI66618</t>
+          <t>DPI64450</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>133.15</v>
+        <v>49.06</v>
       </c>
       <c r="E187" t="n">
         <v>980</v>
       </c>
       <c r="F187" t="n">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="G187" t="n">
-        <v>13.59</v>
+        <v>5.01</v>
       </c>
       <c r="H187" t="n">
-        <v>449432.3</v>
+        <v>539070.01</v>
       </c>
       <c r="I187" t="n">
-        <v>61063.14</v>
+        <v>26987.47</v>
       </c>
     </row>
     <row r="188">
@@ -6998,26 +6998,26 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>DPI64431</t>
+          <t>DPI64686</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>78.73</v>
+        <v>97.63</v>
       </c>
       <c r="E188" t="n">
         <v>980</v>
       </c>
       <c r="F188" t="n">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="G188" t="n">
-        <v>8.029999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H188" t="n">
-        <v>449432.3</v>
+        <v>539070.01</v>
       </c>
       <c r="I188" t="n">
-        <v>36106.38</v>
+        <v>53703.28</v>
       </c>
     </row>
     <row r="189">
@@ -7028,31 +7028,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DPI66923</t>
+          <t>DPI66339</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>68.56999999999999</v>
+        <v>131.28</v>
       </c>
       <c r="E189" t="n">
         <v>980</v>
       </c>
       <c r="F189" t="n">
-        <v>819</v>
+        <v>966</v>
       </c>
       <c r="G189" t="n">
-        <v>7</v>
+        <v>13.4</v>
       </c>
       <c r="H189" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
       <c r="I189" t="n">
-        <v>28475.19</v>
+        <v>72215.91</v>
       </c>
     </row>
     <row r="190">
@@ -7063,31 +7063,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>DFT80077</t>
+          <t>DPI66590</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>46.73</v>
+        <v>142.23</v>
       </c>
       <c r="E190" t="n">
         <v>980</v>
       </c>
       <c r="F190" t="n">
-        <v>819</v>
+        <v>966</v>
       </c>
       <c r="G190" t="n">
-        <v>4.77</v>
+        <v>14.51</v>
       </c>
       <c r="H190" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
       <c r="I190" t="n">
-        <v>19406.6</v>
+        <v>78238.41</v>
       </c>
     </row>
     <row r="191">
@@ -7098,31 +7098,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>DPI66636</t>
+          <t>DFT80044</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>75.55</v>
+        <v>26.45</v>
       </c>
       <c r="E191" t="n">
         <v>980</v>
       </c>
       <c r="F191" t="n">
-        <v>819</v>
+        <v>966</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71</v>
+        <v>2.7</v>
       </c>
       <c r="H191" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
       <c r="I191" t="n">
-        <v>31374.81</v>
+        <v>14547.82</v>
       </c>
     </row>
     <row r="192">
@@ -7133,31 +7133,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DPI64666</t>
+          <t>DPI66096</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>93.56999999999999</v>
+        <v>156.26</v>
       </c>
       <c r="E192" t="n">
         <v>980</v>
       </c>
       <c r="F192" t="n">
-        <v>819</v>
+        <v>966</v>
       </c>
       <c r="G192" t="n">
-        <v>9.550000000000001</v>
+        <v>15.95</v>
       </c>
       <c r="H192" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
       <c r="I192" t="n">
-        <v>38859.17</v>
+        <v>85955.60000000001</v>
       </c>
     </row>
     <row r="193">
@@ -7168,31 +7168,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DPI70190</t>
+          <t>DPI64018</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>60.35</v>
+        <v>161.85</v>
       </c>
       <c r="E193" t="n">
         <v>980</v>
       </c>
       <c r="F193" t="n">
-        <v>819</v>
+        <v>966</v>
       </c>
       <c r="G193" t="n">
-        <v>6.16</v>
+        <v>16.52</v>
       </c>
       <c r="H193" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
       <c r="I193" t="n">
-        <v>25063.77</v>
+        <v>89029.17</v>
       </c>
     </row>
     <row r="194">
@@ -7203,31 +7203,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DPI70253</t>
+          <t>DPI70229</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>56.09</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E194" t="n">
         <v>980</v>
       </c>
       <c r="F194" t="n">
-        <v>819</v>
+        <v>966</v>
       </c>
       <c r="G194" t="n">
-        <v>5.72</v>
+        <v>6.72</v>
       </c>
       <c r="H194" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
       <c r="I194" t="n">
-        <v>23291.45</v>
+        <v>36219.71</v>
       </c>
     </row>
     <row r="195">
@@ -7238,31 +7238,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DPI64056</t>
+          <t>DPI66736</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>84.19</v>
+        <v>136.37</v>
       </c>
       <c r="E195" t="n">
         <v>980</v>
       </c>
       <c r="F195" t="n">
-        <v>819</v>
+        <v>966</v>
       </c>
       <c r="G195" t="n">
-        <v>8.59</v>
+        <v>13.92</v>
       </c>
       <c r="H195" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
       <c r="I195" t="n">
-        <v>34962.94</v>
+        <v>75012.07000000001</v>
       </c>
     </row>
     <row r="196">
@@ -7273,31 +7273,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DPI67074</t>
+          <t>DPI66658</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>115.58</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E196" t="n">
         <v>980</v>
       </c>
       <c r="F196" t="n">
-        <v>819</v>
+        <v>979</v>
       </c>
       <c r="G196" t="n">
-        <v>11.79</v>
+        <v>8</v>
       </c>
       <c r="H196" t="n">
-        <v>406981.88</v>
+        <v>421596.09</v>
       </c>
       <c r="I196" t="n">
-        <v>47997.24</v>
+        <v>33707.47</v>
       </c>
     </row>
     <row r="197">
@@ -7308,31 +7308,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DPI64628</t>
+          <t>DPI67148</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>83.72</v>
+        <v>215.01</v>
       </c>
       <c r="E197" t="n">
         <v>980</v>
       </c>
       <c r="F197" t="n">
-        <v>819</v>
+        <v>979</v>
       </c>
       <c r="G197" t="n">
-        <v>8.539999999999999</v>
+        <v>21.94</v>
       </c>
       <c r="H197" t="n">
-        <v>406981.88</v>
+        <v>421596.09</v>
       </c>
       <c r="I197" t="n">
-        <v>34766.63</v>
+        <v>92497.14999999999</v>
       </c>
     </row>
     <row r="198">
@@ -7343,31 +7343,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DPI64119</t>
+          <t>DPI64742</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>91.45999999999999</v>
+        <v>107.69</v>
       </c>
       <c r="E198" t="n">
         <v>980</v>
       </c>
       <c r="F198" t="n">
-        <v>819</v>
+        <v>979</v>
       </c>
       <c r="G198" t="n">
-        <v>9.33</v>
+        <v>10.99</v>
       </c>
       <c r="H198" t="n">
-        <v>406981.88</v>
+        <v>421596.09</v>
       </c>
       <c r="I198" t="n">
-        <v>37981.25</v>
+        <v>46329.24</v>
       </c>
     </row>
     <row r="199">
@@ -7378,31 +7378,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>DFT80078</t>
+          <t>DPI63976</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>42.46</v>
+        <v>114.26</v>
       </c>
       <c r="E199" t="n">
         <v>980</v>
       </c>
       <c r="F199" t="n">
-        <v>819</v>
+        <v>979</v>
       </c>
       <c r="G199" t="n">
-        <v>4.33</v>
+        <v>11.66</v>
       </c>
       <c r="H199" t="n">
-        <v>406981.88</v>
+        <v>421596.09</v>
       </c>
       <c r="I199" t="n">
-        <v>17633.43</v>
+        <v>49152.81</v>
       </c>
     </row>
     <row r="200">
@@ -7418,11 +7418,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DPI66658</t>
+          <t>DPI70296</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>78.34999999999999</v>
+        <v>53.75</v>
       </c>
       <c r="E200" t="n">
         <v>980</v>
@@ -7431,13 +7431,13 @@
         <v>979</v>
       </c>
       <c r="G200" t="n">
-        <v>8</v>
+        <v>5.48</v>
       </c>
       <c r="H200" t="n">
         <v>421596.09</v>
       </c>
       <c r="I200" t="n">
-        <v>33707.47</v>
+        <v>23122.65</v>
       </c>
     </row>
     <row r="201">
@@ -7453,11 +7453,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DPI67148</t>
+          <t>DPI67180</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>215.01</v>
+        <v>101.47</v>
       </c>
       <c r="E201" t="n">
         <v>980</v>
@@ -7466,13 +7466,13 @@
         <v>979</v>
       </c>
       <c r="G201" t="n">
-        <v>21.94</v>
+        <v>10.35</v>
       </c>
       <c r="H201" t="n">
         <v>421596.09</v>
       </c>
       <c r="I201" t="n">
-        <v>92497.14999999999</v>
+        <v>43651.54</v>
       </c>
     </row>
     <row r="202">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DPI64742</t>
+          <t>DPI64634</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>107.69</v>
+        <v>86.12</v>
       </c>
       <c r="E202" t="n">
         <v>980</v>
@@ -7501,13 +7501,13 @@
         <v>979</v>
       </c>
       <c r="G202" t="n">
-        <v>10.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H202" t="n">
         <v>421596.09</v>
       </c>
       <c r="I202" t="n">
-        <v>46329.24</v>
+        <v>37048.01</v>
       </c>
     </row>
     <row r="203">
@@ -7523,11 +7523,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DPI63976</t>
+          <t>DPI67224</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>114.26</v>
+        <v>85.72</v>
       </c>
       <c r="E203" t="n">
         <v>980</v>
@@ -7536,13 +7536,13 @@
         <v>979</v>
       </c>
       <c r="G203" t="n">
-        <v>11.66</v>
+        <v>8.75</v>
       </c>
       <c r="H203" t="n">
         <v>421596.09</v>
       </c>
       <c r="I203" t="n">
-        <v>49152.81</v>
+        <v>36877.57</v>
       </c>
     </row>
     <row r="204">
@@ -7558,11 +7558,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DPI70296</t>
+          <t>DPI66209</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>53.75</v>
+        <v>136.76</v>
       </c>
       <c r="E204" t="n">
         <v>980</v>
@@ -7571,13 +7571,13 @@
         <v>979</v>
       </c>
       <c r="G204" t="n">
-        <v>5.48</v>
+        <v>13.96</v>
       </c>
       <c r="H204" t="n">
         <v>421596.09</v>
       </c>
       <c r="I204" t="n">
-        <v>23122.65</v>
+        <v>58834.08</v>
       </c>
     </row>
     <row r="205">
@@ -7588,31 +7588,31 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DPI67180</t>
+          <t>DPI70109</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>101.47</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="E205" t="n">
         <v>980</v>
       </c>
       <c r="F205" t="n">
-        <v>979</v>
+        <v>824</v>
       </c>
       <c r="G205" t="n">
-        <v>10.35</v>
+        <v>6.58</v>
       </c>
       <c r="H205" t="n">
-        <v>421596.09</v>
+        <v>557988.3</v>
       </c>
       <c r="I205" t="n">
-        <v>43651.54</v>
+        <v>36701.33</v>
       </c>
     </row>
     <row r="206">
@@ -7623,31 +7623,31 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DPI64634</t>
+          <t>DPI66129</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>86.12</v>
+        <v>200.46</v>
       </c>
       <c r="E206" t="n">
         <v>980</v>
       </c>
       <c r="F206" t="n">
-        <v>979</v>
+        <v>824</v>
       </c>
       <c r="G206" t="n">
-        <v>8.789999999999999</v>
+        <v>20.46</v>
       </c>
       <c r="H206" t="n">
-        <v>421596.09</v>
+        <v>557988.3</v>
       </c>
       <c r="I206" t="n">
-        <v>37048.01</v>
+        <v>114138.12</v>
       </c>
     </row>
     <row r="207">
@@ -7658,31 +7658,31 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DPI67224</t>
+          <t>DPI64495</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>85.72</v>
+        <v>186.61</v>
       </c>
       <c r="E207" t="n">
         <v>980</v>
       </c>
       <c r="F207" t="n">
-        <v>979</v>
+        <v>824</v>
       </c>
       <c r="G207" t="n">
-        <v>8.75</v>
+        <v>19.04</v>
       </c>
       <c r="H207" t="n">
-        <v>421596.09</v>
+        <v>557988.3</v>
       </c>
       <c r="I207" t="n">
-        <v>36877.57</v>
+        <v>106249.97</v>
       </c>
     </row>
     <row r="208">
@@ -7693,31 +7693,31 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DPI66209</t>
+          <t>DFT80080</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>136.76</v>
+        <v>38.28</v>
       </c>
       <c r="E208" t="n">
         <v>980</v>
       </c>
       <c r="F208" t="n">
-        <v>979</v>
+        <v>824</v>
       </c>
       <c r="G208" t="n">
-        <v>13.96</v>
+        <v>3.91</v>
       </c>
       <c r="H208" t="n">
-        <v>421596.09</v>
+        <v>557988.3</v>
       </c>
       <c r="I208" t="n">
-        <v>58834.08</v>
+        <v>21793.39</v>
       </c>
     </row>
     <row r="209">
@@ -7733,11 +7733,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DPI70109</t>
+          <t>DPI64548</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>64.45999999999999</v>
+        <v>118.62</v>
       </c>
       <c r="E209" t="n">
         <v>980</v>
@@ -7746,13 +7746,13 @@
         <v>824</v>
       </c>
       <c r="G209" t="n">
-        <v>6.58</v>
+        <v>12.1</v>
       </c>
       <c r="H209" t="n">
         <v>557988.3</v>
       </c>
       <c r="I209" t="n">
-        <v>36701.33</v>
+        <v>67537.16</v>
       </c>
     </row>
     <row r="210">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DPI66129</t>
+          <t>DPI70107</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>200.46</v>
+        <v>57.32</v>
       </c>
       <c r="E210" t="n">
         <v>980</v>
@@ -7781,13 +7781,13 @@
         <v>824</v>
       </c>
       <c r="G210" t="n">
-        <v>20.46</v>
+        <v>5.85</v>
       </c>
       <c r="H210" t="n">
         <v>557988.3</v>
       </c>
       <c r="I210" t="n">
-        <v>114138.12</v>
+        <v>32634.24</v>
       </c>
     </row>
     <row r="211">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>DPI64495</t>
+          <t>DPI70214</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>186.61</v>
+        <v>53.89</v>
       </c>
       <c r="E211" t="n">
         <v>980</v>
@@ -7816,13 +7816,13 @@
         <v>824</v>
       </c>
       <c r="G211" t="n">
-        <v>19.04</v>
+        <v>5.5</v>
       </c>
       <c r="H211" t="n">
         <v>557988.3</v>
       </c>
       <c r="I211" t="n">
-        <v>106249.97</v>
+        <v>30685.39</v>
       </c>
     </row>
     <row r="212">
@@ -7838,11 +7838,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>DFT80080</t>
+          <t>DPI66634</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>38.28</v>
+        <v>104.69</v>
       </c>
       <c r="E212" t="n">
         <v>980</v>
@@ -7851,13 +7851,13 @@
         <v>824</v>
       </c>
       <c r="G212" t="n">
-        <v>3.91</v>
+        <v>10.68</v>
       </c>
       <c r="H212" t="n">
         <v>557988.3</v>
       </c>
       <c r="I212" t="n">
-        <v>21793.39</v>
+        <v>59608.09</v>
       </c>
     </row>
     <row r="213">
@@ -7868,31 +7868,31 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DPI64548</t>
+          <t>DPI64052</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>118.62</v>
+        <v>192.78</v>
       </c>
       <c r="E213" t="n">
         <v>980</v>
       </c>
       <c r="F213" t="n">
-        <v>824</v>
+        <v>956</v>
       </c>
       <c r="G213" t="n">
-        <v>12.1</v>
+        <v>19.67</v>
       </c>
       <c r="H213" t="n">
-        <v>557988.3</v>
+        <v>448403.88</v>
       </c>
       <c r="I213" t="n">
-        <v>67537.16</v>
+        <v>88207.48</v>
       </c>
     </row>
     <row r="214">
@@ -7903,31 +7903,31 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DPI70107</t>
+          <t>DPI67187</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>57.32</v>
+        <v>102.41</v>
       </c>
       <c r="E214" t="n">
         <v>980</v>
       </c>
       <c r="F214" t="n">
-        <v>824</v>
+        <v>956</v>
       </c>
       <c r="G214" t="n">
-        <v>5.85</v>
+        <v>10.45</v>
       </c>
       <c r="H214" t="n">
-        <v>557988.3</v>
+        <v>448403.88</v>
       </c>
       <c r="I214" t="n">
-        <v>32634.24</v>
+        <v>46860.4</v>
       </c>
     </row>
     <row r="215">
@@ -7938,31 +7938,31 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DPI70214</t>
+          <t>DPI64666</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>53.89</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="E215" t="n">
         <v>980</v>
       </c>
       <c r="F215" t="n">
-        <v>824</v>
+        <v>956</v>
       </c>
       <c r="G215" t="n">
-        <v>5.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H215" t="n">
-        <v>557988.3</v>
+        <v>448403.88</v>
       </c>
       <c r="I215" t="n">
-        <v>30685.39</v>
+        <v>42814.2</v>
       </c>
     </row>
     <row r="216">
@@ -7973,31 +7973,31 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DPI66634</t>
+          <t>DPI70190</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>104.69</v>
+        <v>60.35</v>
       </c>
       <c r="E216" t="n">
         <v>980</v>
       </c>
       <c r="F216" t="n">
-        <v>824</v>
+        <v>956</v>
       </c>
       <c r="G216" t="n">
-        <v>10.68</v>
+        <v>6.16</v>
       </c>
       <c r="H216" t="n">
-        <v>557988.3</v>
+        <v>448403.88</v>
       </c>
       <c r="I216" t="n">
-        <v>59608.09</v>
+        <v>27614.72</v>
       </c>
     </row>
     <row r="217">
@@ -8013,26 +8013,26 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DPI64052</t>
+          <t>DPI70253</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>192.78</v>
+        <v>56.09</v>
       </c>
       <c r="E217" t="n">
         <v>980</v>
       </c>
       <c r="F217" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="G217" t="n">
-        <v>19.67</v>
+        <v>5.72</v>
       </c>
       <c r="H217" t="n">
-        <v>166140.82</v>
+        <v>448403.88</v>
       </c>
       <c r="I217" t="n">
-        <v>32682.28</v>
+        <v>25662.02</v>
       </c>
     </row>
     <row r="218">
@@ -8048,26 +8048,26 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DPI66179</t>
+          <t>DPI64056</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>130.31</v>
+        <v>84.19</v>
       </c>
       <c r="E218" t="n">
         <v>980</v>
       </c>
       <c r="F218" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="G218" t="n">
-        <v>13.3</v>
+        <v>8.59</v>
       </c>
       <c r="H218" t="n">
-        <v>166140.82</v>
+        <v>448403.88</v>
       </c>
       <c r="I218" t="n">
-        <v>22090.97</v>
+        <v>38521.42</v>
       </c>
     </row>
     <row r="219">
@@ -8083,26 +8083,26 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>DPI66597</t>
+          <t>DPI67074</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>90.83</v>
+        <v>115.58</v>
       </c>
       <c r="E219" t="n">
         <v>980</v>
       </c>
       <c r="F219" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="G219" t="n">
-        <v>9.27</v>
+        <v>11.79</v>
       </c>
       <c r="H219" t="n">
-        <v>166140.82</v>
+        <v>448403.88</v>
       </c>
       <c r="I219" t="n">
-        <v>15399.35</v>
+        <v>52882.33</v>
       </c>
     </row>
     <row r="220">
@@ -8118,26 +8118,26 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>DPI63958</t>
+          <t>DPI64628</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>120.83</v>
+        <v>83.72</v>
       </c>
       <c r="E220" t="n">
         <v>980</v>
       </c>
       <c r="F220" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="G220" t="n">
-        <v>12.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H220" t="n">
-        <v>166140.82</v>
+        <v>448403.88</v>
       </c>
       <c r="I220" t="n">
-        <v>20485.32</v>
+        <v>38305.13</v>
       </c>
     </row>
     <row r="221">
@@ -8153,26 +8153,26 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>DPI66039</t>
+          <t>DPI64119</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>114.76</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="E221" t="n">
         <v>980</v>
       </c>
       <c r="F221" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="G221" t="n">
-        <v>11.71</v>
+        <v>9.33</v>
       </c>
       <c r="H221" t="n">
-        <v>166140.82</v>
+        <v>448403.88</v>
       </c>
       <c r="I221" t="n">
-        <v>19455.93</v>
+        <v>41846.93</v>
       </c>
     </row>
     <row r="222">
@@ -8188,26 +8188,26 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DPI66307</t>
+          <t>DPI66636</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>125.94</v>
+        <v>75.55</v>
       </c>
       <c r="E222" t="n">
         <v>980</v>
       </c>
       <c r="F222" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="G222" t="n">
-        <v>12.85</v>
+        <v>7.71</v>
       </c>
       <c r="H222" t="n">
-        <v>166140.82</v>
+        <v>448403.88</v>
       </c>
       <c r="I222" t="n">
-        <v>21350.79</v>
+        <v>34568.1</v>
       </c>
     </row>
     <row r="223">
@@ -8218,31 +8218,31 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DPI64638</t>
+          <t>DPI64431</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>88.97</v>
+        <v>78.73</v>
       </c>
       <c r="E223" t="n">
         <v>980</v>
       </c>
       <c r="F223" t="n">
-        <v>865</v>
+        <v>957</v>
       </c>
       <c r="G223" t="n">
-        <v>9.08</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H223" t="n">
-        <v>166140.82</v>
+        <v>272542.49</v>
       </c>
       <c r="I223" t="n">
-        <v>15083.24</v>
+        <v>21895.45</v>
       </c>
     </row>
     <row r="224">
@@ -8258,26 +8258,26 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DPI70009</t>
+          <t>DPI66449</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>60.09</v>
+        <v>191.04</v>
       </c>
       <c r="E224" t="n">
         <v>980</v>
       </c>
       <c r="F224" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G224" t="n">
-        <v>6.13</v>
+        <v>19.49</v>
       </c>
       <c r="H224" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I224" t="n">
-        <v>20309.6</v>
+        <v>53129.44</v>
       </c>
     </row>
     <row r="225">
@@ -8293,26 +8293,26 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DPI63827</t>
+          <t>DPI67072</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>130.01</v>
+        <v>126.86</v>
       </c>
       <c r="E225" t="n">
         <v>980</v>
       </c>
       <c r="F225" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G225" t="n">
-        <v>13.27</v>
+        <v>12.94</v>
       </c>
       <c r="H225" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I225" t="n">
-        <v>43937.67</v>
+        <v>35279.6</v>
       </c>
     </row>
     <row r="226">
@@ -8328,26 +8328,26 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DPI66313</t>
+          <t>DPI66153</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>124.82</v>
+        <v>97.33</v>
       </c>
       <c r="E226" t="n">
         <v>980</v>
       </c>
       <c r="F226" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G226" t="n">
-        <v>12.74</v>
+        <v>9.93</v>
       </c>
       <c r="H226" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I226" t="n">
-        <v>42186.01</v>
+        <v>27067.14</v>
       </c>
     </row>
     <row r="227">
@@ -8363,26 +8363,26 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>DPI66576</t>
+          <t>DPI66154</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>125.61</v>
+        <v>73.08</v>
       </c>
       <c r="E227" t="n">
         <v>980</v>
       </c>
       <c r="F227" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G227" t="n">
-        <v>12.82</v>
+        <v>7.46</v>
       </c>
       <c r="H227" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I227" t="n">
-        <v>42452.52</v>
+        <v>20323.86</v>
       </c>
     </row>
     <row r="228">
@@ -8398,26 +8398,26 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DPI64592</t>
+          <t>DPI66373</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>96.81999999999999</v>
+        <v>98.05</v>
       </c>
       <c r="E228" t="n">
         <v>980</v>
       </c>
       <c r="F228" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G228" t="n">
-        <v>9.880000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="H228" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I228" t="n">
-        <v>32721.98</v>
+        <v>27268.49</v>
       </c>
     </row>
     <row r="229">
@@ -8433,26 +8433,26 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DPI63919</t>
+          <t>DPI64196</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>108.37</v>
+        <v>79.7</v>
       </c>
       <c r="E229" t="n">
         <v>980</v>
       </c>
       <c r="F229" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G229" t="n">
-        <v>11.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H229" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I229" t="n">
-        <v>36626.33</v>
+        <v>22165.64</v>
       </c>
     </row>
     <row r="230">
@@ -8468,26 +8468,26 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DPI66679</t>
+          <t>DPI66221</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>131.96</v>
+        <v>121.2</v>
       </c>
       <c r="E230" t="n">
         <v>980</v>
       </c>
       <c r="F230" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G230" t="n">
-        <v>13.47</v>
+        <v>12.37</v>
       </c>
       <c r="H230" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I230" t="n">
-        <v>44599.21</v>
+        <v>33707.34</v>
       </c>
     </row>
     <row r="231">
@@ -8503,26 +8503,26 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DPI70047</t>
+          <t>DPI66597</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>76.39</v>
+        <v>90.83</v>
       </c>
       <c r="E231" t="n">
         <v>980</v>
       </c>
       <c r="F231" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="G231" t="n">
-        <v>7.8</v>
+        <v>9.27</v>
       </c>
       <c r="H231" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
       <c r="I231" t="n">
-        <v>25817.92</v>
+        <v>25261.57</v>
       </c>
     </row>
     <row r="232">
@@ -8538,26 +8538,26 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DPI64094</t>
+          <t>DPI66069</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>75.03</v>
+        <v>182.8</v>
       </c>
       <c r="E232" t="n">
         <v>980</v>
       </c>
       <c r="F232" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G232" t="n">
-        <v>7.66</v>
+        <v>18.65</v>
       </c>
       <c r="H232" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I232" t="n">
-        <v>30686.18</v>
+        <v>78206.03999999999</v>
       </c>
     </row>
     <row r="233">
@@ -8573,26 +8573,26 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DPI66128</t>
+          <t>DPI64039</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>221.49</v>
+        <v>98.41</v>
       </c>
       <c r="E233" t="n">
         <v>980</v>
       </c>
       <c r="F233" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G233" t="n">
-        <v>22.6</v>
+        <v>10.04</v>
       </c>
       <c r="H233" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I233" t="n">
-        <v>90591.28999999999</v>
+        <v>42104.05</v>
       </c>
     </row>
     <row r="234">
@@ -8608,26 +8608,26 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>DPI70096</t>
+          <t>DPI66289</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>59.61</v>
+        <v>38.55</v>
       </c>
       <c r="E234" t="n">
         <v>980</v>
       </c>
       <c r="F234" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G234" t="n">
-        <v>6.08</v>
+        <v>3.93</v>
       </c>
       <c r="H234" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I234" t="n">
-        <v>24379.72</v>
+        <v>16494.02</v>
       </c>
     </row>
     <row r="235">
@@ -8643,26 +8643,26 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DPI64037</t>
+          <t>DPI66203</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>27.36</v>
+        <v>187.41</v>
       </c>
       <c r="E235" t="n">
         <v>980</v>
       </c>
       <c r="F235" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G235" t="n">
-        <v>2.79</v>
+        <v>19.12</v>
       </c>
       <c r="H235" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I235" t="n">
-        <v>11192.53</v>
+        <v>80179.39</v>
       </c>
     </row>
     <row r="236">
@@ -8678,26 +8678,26 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DPI66172</t>
+          <t>DPI66574</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>12.83</v>
+        <v>165.71</v>
       </c>
       <c r="E236" t="n">
         <v>980</v>
       </c>
       <c r="F236" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G236" t="n">
-        <v>1.31</v>
+        <v>16.91</v>
       </c>
       <c r="H236" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I236" t="n">
-        <v>5245.57</v>
+        <v>70893.8</v>
       </c>
     </row>
     <row r="237">
@@ -8713,26 +8713,26 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>DPI64057</t>
+          <t>DPI66078</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>116.77</v>
+        <v>157.09</v>
       </c>
       <c r="E237" t="n">
         <v>980</v>
       </c>
       <c r="F237" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G237" t="n">
-        <v>11.92</v>
+        <v>16.03</v>
       </c>
       <c r="H237" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I237" t="n">
-        <v>47760.91</v>
+        <v>67207.08</v>
       </c>
     </row>
     <row r="238">
@@ -8748,26 +8748,26 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>DPI63802</t>
+          <t>DPI64433</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>120.78</v>
+        <v>82.72</v>
       </c>
       <c r="E238" t="n">
         <v>980</v>
       </c>
       <c r="F238" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G238" t="n">
-        <v>12.32</v>
+        <v>8.44</v>
       </c>
       <c r="H238" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I238" t="n">
-        <v>49400.06</v>
+        <v>35392.01</v>
       </c>
     </row>
     <row r="239">
@@ -8783,26 +8783,26 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DPI66051</t>
+          <t>DPI64480</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>99.67</v>
+        <v>56.32</v>
       </c>
       <c r="E239" t="n">
         <v>980</v>
       </c>
       <c r="F239" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="G239" t="n">
-        <v>10.17</v>
+        <v>5.75</v>
       </c>
       <c r="H239" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
       <c r="I239" t="n">
-        <v>40766.2</v>
+        <v>24094.02</v>
       </c>
     </row>
     <row r="240">
@@ -8813,31 +8813,31 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DPI64169</t>
+          <t>DPI64436</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>59.46</v>
+        <v>86.91</v>
       </c>
       <c r="E240" t="n">
         <v>980</v>
       </c>
       <c r="F240" t="n">
-        <v>925</v>
+        <v>961</v>
       </c>
       <c r="G240" t="n">
-        <v>6.07</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H240" t="n">
-        <v>400828.8</v>
+        <v>400421.92</v>
       </c>
       <c r="I240" t="n">
-        <v>24317.69</v>
+        <v>35511.67</v>
       </c>
     </row>
     <row r="241">
@@ -8848,31 +8848,31 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DPI66715</t>
+          <t>DPI64456</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>131.63</v>
+        <v>111.28</v>
       </c>
       <c r="E241" t="n">
         <v>980</v>
       </c>
       <c r="F241" t="n">
-        <v>925</v>
+        <v>961</v>
       </c>
       <c r="G241" t="n">
-        <v>13.43</v>
+        <v>11.36</v>
       </c>
       <c r="H241" t="n">
-        <v>400828.8</v>
+        <v>400421.92</v>
       </c>
       <c r="I241" t="n">
-        <v>53838.11</v>
+        <v>45470.26</v>
       </c>
     </row>
     <row r="242">
@@ -8888,26 +8888,26 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DPI66653</t>
+          <t>DPI66946</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>109.8</v>
+        <v>126.11</v>
       </c>
       <c r="E242" t="n">
         <v>980</v>
       </c>
       <c r="F242" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="G242" t="n">
-        <v>11.2</v>
+        <v>12.87</v>
       </c>
       <c r="H242" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
       <c r="I242" t="n">
-        <v>26761.31</v>
+        <v>51526.82</v>
       </c>
     </row>
     <row r="243">
@@ -8923,26 +8923,26 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>DPI66449</t>
+          <t>DPI64136</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>191.04</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="E243" t="n">
         <v>980</v>
       </c>
       <c r="F243" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="G243" t="n">
-        <v>19.49</v>
+        <v>7.21</v>
       </c>
       <c r="H243" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
       <c r="I243" t="n">
-        <v>46562.19</v>
+        <v>28879.7</v>
       </c>
     </row>
     <row r="244">
@@ -8958,26 +8958,26 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DPI67072</t>
+          <t>DPI67121</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>126.86</v>
+        <v>115.03</v>
       </c>
       <c r="E244" t="n">
         <v>980</v>
       </c>
       <c r="F244" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="G244" t="n">
-        <v>12.94</v>
+        <v>11.74</v>
       </c>
       <c r="H244" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
       <c r="I244" t="n">
-        <v>30918.75</v>
+        <v>47000.66</v>
       </c>
     </row>
     <row r="245">
@@ -8993,26 +8993,26 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DPI66153</t>
+          <t>DPI66039</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>97.33</v>
+        <v>114.76</v>
       </c>
       <c r="E245" t="n">
         <v>980</v>
       </c>
       <c r="F245" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="G245" t="n">
-        <v>9.93</v>
+        <v>11.71</v>
       </c>
       <c r="H245" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
       <c r="I245" t="n">
-        <v>23721.42</v>
+        <v>46891.43</v>
       </c>
     </row>
     <row r="246">
@@ -9028,26 +9028,26 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DPI70081</t>
+          <t>DPI66307</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>54.11</v>
+        <v>125.94</v>
       </c>
       <c r="E246" t="n">
         <v>980</v>
       </c>
       <c r="F246" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="G246" t="n">
-        <v>5.52</v>
+        <v>12.85</v>
       </c>
       <c r="H246" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
       <c r="I246" t="n">
-        <v>13188.62</v>
+        <v>51458.3</v>
       </c>
     </row>
     <row r="247">
@@ -9063,26 +9063,26 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DPI66154</t>
+          <t>DPI64638</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>73.08</v>
+        <v>88.97</v>
       </c>
       <c r="E247" t="n">
         <v>980</v>
       </c>
       <c r="F247" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="G247" t="n">
-        <v>7.46</v>
+        <v>9.08</v>
       </c>
       <c r="H247" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
       <c r="I247" t="n">
-        <v>17811.66</v>
+        <v>36352.65</v>
       </c>
     </row>
     <row r="248">
@@ -9098,26 +9098,26 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DPI66373</t>
+          <t>DPI63958</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>98.05</v>
+        <v>120.83</v>
       </c>
       <c r="E248" t="n">
         <v>980</v>
       </c>
       <c r="F248" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="G248" t="n">
-        <v>10.01</v>
+        <v>12.33</v>
       </c>
       <c r="H248" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
       <c r="I248" t="n">
-        <v>23897.88</v>
+        <v>49372.39</v>
       </c>
     </row>
     <row r="249">
@@ -9128,31 +9128,31 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DPI66221</t>
+          <t>DPI66179</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>121.2</v>
+        <v>130.31</v>
       </c>
       <c r="E249" t="n">
         <v>980</v>
       </c>
       <c r="F249" t="n">
-        <v>871</v>
+        <v>962</v>
       </c>
       <c r="G249" t="n">
-        <v>12.37</v>
+        <v>13.3</v>
       </c>
       <c r="H249" t="n">
-        <v>238853.93</v>
+        <v>300038.08</v>
       </c>
       <c r="I249" t="n">
-        <v>29540.83</v>
+        <v>39894.66</v>
       </c>
     </row>
     <row r="250">
@@ -9168,26 +9168,26 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>DPI64480</t>
+          <t>DPI64218</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>56.32</v>
+        <v>52.55</v>
       </c>
       <c r="E250" t="n">
         <v>980</v>
       </c>
       <c r="F250" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G250" t="n">
-        <v>5.75</v>
+        <v>5.36</v>
       </c>
       <c r="H250" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I250" t="n">
-        <v>22175.3</v>
+        <v>16089.84</v>
       </c>
     </row>
     <row r="251">
@@ -9203,26 +9203,26 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>DPI66078</t>
+          <t>DPI64301</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>157.09</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="E251" t="n">
         <v>980</v>
       </c>
       <c r="F251" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G251" t="n">
-        <v>16.03</v>
+        <v>10.15</v>
       </c>
       <c r="H251" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I251" t="n">
-        <v>61855.06</v>
+        <v>30464.86</v>
       </c>
     </row>
     <row r="252">
@@ -9238,26 +9238,26 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>DPI64433</t>
+          <t>DPI70255</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>82.72</v>
+        <v>63.7</v>
       </c>
       <c r="E252" t="n">
         <v>980</v>
       </c>
       <c r="F252" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G252" t="n">
-        <v>8.44</v>
+        <v>6.5</v>
       </c>
       <c r="H252" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I252" t="n">
-        <v>32573.58</v>
+        <v>19501.08</v>
       </c>
     </row>
     <row r="253">
@@ -9273,26 +9273,26 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DPI67187</t>
+          <t>DPI66645</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>102.41</v>
+        <v>127.76</v>
       </c>
       <c r="E253" t="n">
         <v>980</v>
       </c>
       <c r="F253" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G253" t="n">
-        <v>10.45</v>
+        <v>13.04</v>
       </c>
       <c r="H253" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I253" t="n">
-        <v>40326.63</v>
+        <v>39115.33</v>
       </c>
     </row>
     <row r="254">
@@ -9308,26 +9308,26 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DPI70105</t>
+          <t>DPI64244</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>75.19</v>
+        <v>126.9</v>
       </c>
       <c r="E254" t="n">
         <v>980</v>
       </c>
       <c r="F254" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G254" t="n">
-        <v>7.67</v>
+        <v>12.95</v>
       </c>
       <c r="H254" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I254" t="n">
-        <v>29608.19</v>
+        <v>38851.66</v>
       </c>
     </row>
     <row r="255">
@@ -9343,26 +9343,26 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>DPI64436</t>
+          <t>DPI66128</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>86.91</v>
+        <v>221.49</v>
       </c>
       <c r="E255" t="n">
         <v>980</v>
       </c>
       <c r="F255" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G255" t="n">
-        <v>8.869999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="H255" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I255" t="n">
-        <v>34222.25</v>
+        <v>67811.59</v>
       </c>
     </row>
     <row r="256">
@@ -9378,26 +9378,26 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>DPI64456</t>
+          <t>DPI64094</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>111.28</v>
+        <v>75.03</v>
       </c>
       <c r="E256" t="n">
         <v>980</v>
       </c>
       <c r="F256" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G256" t="n">
-        <v>11.36</v>
+        <v>7.66</v>
       </c>
       <c r="H256" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I256" t="n">
-        <v>43819.24</v>
+        <v>22969.96</v>
       </c>
     </row>
     <row r="257">
@@ -9413,26 +9413,26 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DPI66946</t>
+          <t>DPI70142</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>126.11</v>
+        <v>63.66</v>
       </c>
       <c r="E257" t="n">
         <v>980</v>
       </c>
       <c r="F257" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G257" t="n">
-        <v>12.87</v>
+        <v>6.5</v>
       </c>
       <c r="H257" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
       <c r="I257" t="n">
-        <v>49655.88</v>
+        <v>19490.78</v>
       </c>
     </row>
     <row r="258">
@@ -9443,31 +9443,31 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DPI66574</t>
+          <t>DPI70009</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>165.71</v>
+        <v>60.09</v>
       </c>
       <c r="E258" t="n">
         <v>980</v>
       </c>
       <c r="F258" t="n">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="G258" t="n">
-        <v>16.91</v>
+        <v>6.13</v>
       </c>
       <c r="H258" t="n">
-        <v>385882.65</v>
+        <v>464235.26</v>
       </c>
       <c r="I258" t="n">
-        <v>65248.19</v>
+        <v>28466.76</v>
       </c>
     </row>
     <row r="259">
@@ -9483,26 +9483,26 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DPI67121</t>
+          <t>DPI63827</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>115.03</v>
+        <v>130.01</v>
       </c>
       <c r="E259" t="n">
         <v>980</v>
       </c>
       <c r="F259" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G259" t="n">
-        <v>11.74</v>
+        <v>13.27</v>
       </c>
       <c r="H259" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I259" t="n">
-        <v>20180.62</v>
+        <v>61584.83</v>
       </c>
     </row>
     <row r="260">
@@ -9518,26 +9518,26 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DPI64450</t>
+          <t>DPI66313</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>49.06</v>
+        <v>124.82</v>
       </c>
       <c r="E260" t="n">
         <v>980</v>
       </c>
       <c r="F260" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G260" t="n">
-        <v>5.01</v>
+        <v>12.74</v>
       </c>
       <c r="H260" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I260" t="n">
-        <v>8607.27</v>
+        <v>59129.63</v>
       </c>
     </row>
     <row r="261">
@@ -9553,26 +9553,26 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>DPI64686</t>
+          <t>DPI66576</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>97.63</v>
+        <v>125.61</v>
       </c>
       <c r="E261" t="n">
         <v>980</v>
       </c>
       <c r="F261" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G261" t="n">
-        <v>9.960000000000001</v>
+        <v>12.82</v>
       </c>
       <c r="H261" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I261" t="n">
-        <v>17127.9</v>
+        <v>59503.18</v>
       </c>
     </row>
     <row r="262">
@@ -9588,26 +9588,26 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>DPI66203</t>
+          <t>DPI64592</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>187.41</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="E262" t="n">
         <v>980</v>
       </c>
       <c r="F262" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G262" t="n">
-        <v>19.12</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H262" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I262" t="n">
-        <v>32878.82</v>
+        <v>45864.46</v>
       </c>
     </row>
     <row r="263">
@@ -9623,26 +9623,26 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DPI64301</t>
+          <t>DPI63919</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>99.51000000000001</v>
+        <v>108.37</v>
       </c>
       <c r="E263" t="n">
         <v>980</v>
       </c>
       <c r="F263" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G263" t="n">
-        <v>10.15</v>
+        <v>11.06</v>
       </c>
       <c r="H263" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I263" t="n">
-        <v>17457.07</v>
+        <v>51336.95</v>
       </c>
     </row>
     <row r="264">
@@ -9658,26 +9658,26 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DFT80044</t>
+          <t>DPI66679</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>26.45</v>
+        <v>131.96</v>
       </c>
       <c r="E264" t="n">
         <v>980</v>
       </c>
       <c r="F264" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G264" t="n">
-        <v>2.7</v>
+        <v>13.47</v>
       </c>
       <c r="H264" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I264" t="n">
-        <v>4639.82</v>
+        <v>62512.07</v>
       </c>
     </row>
     <row r="265">
@@ -9693,26 +9693,26 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DPI66590</t>
+          <t>DPI70047</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>142.23</v>
+        <v>76.39</v>
       </c>
       <c r="E265" t="n">
         <v>980</v>
       </c>
       <c r="F265" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G265" t="n">
-        <v>14.51</v>
+        <v>7.8</v>
       </c>
       <c r="H265" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I265" t="n">
-        <v>24953.03</v>
+        <v>36187.45</v>
       </c>
     </row>
     <row r="266">
@@ -9728,26 +9728,26 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DPI66339</t>
+          <t>DPI66923</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>131.28</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="E266" t="n">
         <v>980</v>
       </c>
       <c r="F266" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G266" t="n">
-        <v>13.4</v>
+        <v>7</v>
       </c>
       <c r="H266" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I266" t="n">
-        <v>23032.24</v>
+        <v>32481.03</v>
       </c>
     </row>
     <row r="267">
@@ -9763,26 +9763,26 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>DPI66387</t>
+          <t>DFT80078</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>108.78</v>
+        <v>42.46</v>
       </c>
       <c r="E267" t="n">
         <v>980</v>
       </c>
       <c r="F267" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G267" t="n">
-        <v>11.1</v>
+        <v>4.33</v>
       </c>
       <c r="H267" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
       <c r="I267" t="n">
-        <v>19084.36</v>
+        <v>20114.06</v>
       </c>
     </row>
     <row r="268">

--- a/store_wise_monthly_costs.xlsx
+++ b/store_wise_monthly_costs.xlsx
@@ -11249,10 +11249,10 @@
         <v>7.12</v>
       </c>
       <c r="H309" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I309" t="n">
-        <v>97084.92999999999</v>
+        <v>33731.98</v>
       </c>
     </row>
     <row r="310">
@@ -11284,10 +11284,10 @@
         <v>7.79</v>
       </c>
       <c r="H310" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I310" t="n">
-        <v>106270.32</v>
+        <v>36923.43</v>
       </c>
     </row>
     <row r="311">
@@ -11319,10 +11319,10 @@
         <v>5.84</v>
       </c>
       <c r="H311" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I311" t="n">
-        <v>79713.84</v>
+        <v>27696.43</v>
       </c>
     </row>
     <row r="312">
@@ -11354,10 +11354,10 @@
         <v>5.71</v>
       </c>
       <c r="H312" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I312" t="n">
-        <v>77915.84</v>
+        <v>27071.71</v>
       </c>
     </row>
     <row r="313">
@@ -11389,10 +11389,10 @@
         <v>5.28</v>
       </c>
       <c r="H313" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I313" t="n">
-        <v>72029.97</v>
+        <v>25026.68</v>
       </c>
     </row>
     <row r="314">
@@ -11424,10 +11424,10 @@
         <v>10.88</v>
       </c>
       <c r="H314" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I314" t="n">
-        <v>148391.91</v>
+        <v>51558.5</v>
       </c>
     </row>
     <row r="315">
@@ -11459,10 +11459,10 @@
         <v>10.18</v>
       </c>
       <c r="H315" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I315" t="n">
-        <v>138827.91</v>
+        <v>48235.5</v>
       </c>
     </row>
     <row r="316">
@@ -11494,10 +11494,10 @@
         <v>7.83</v>
       </c>
       <c r="H316" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I316" t="n">
-        <v>106824.99</v>
+        <v>37116.15</v>
       </c>
     </row>
     <row r="317">
@@ -11529,10 +11529,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="H317" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I317" t="n">
-        <v>126884.16</v>
+        <v>44085.67</v>
       </c>
     </row>
     <row r="318">
@@ -11564,10 +11564,10 @@
         <v>2.99</v>
       </c>
       <c r="H318" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I318" t="n">
-        <v>40801.92</v>
+        <v>14176.55</v>
       </c>
     </row>
     <row r="319">
@@ -11599,10 +11599,10 @@
         <v>13.44</v>
       </c>
       <c r="H319" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I319" t="n">
-        <v>183322.19</v>
+        <v>63694.96</v>
       </c>
     </row>
     <row r="320">
@@ -11634,10 +11634,10 @@
         <v>7.09</v>
       </c>
       <c r="H320" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I320" t="n">
-        <v>96750.69</v>
+        <v>33615.85</v>
       </c>
     </row>
     <row r="321">
@@ -11669,10 +11669,10 @@
         <v>6</v>
       </c>
       <c r="H321" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
       <c r="I321" t="n">
-        <v>81878.85000000001</v>
+        <v>28448.66</v>
       </c>
     </row>
     <row r="322">
@@ -11704,10 +11704,10 @@
         <v>10.65</v>
       </c>
       <c r="H322" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I322" t="n">
-        <v>126058.42</v>
+        <v>31233.99</v>
       </c>
     </row>
     <row r="323">
@@ -11739,10 +11739,10 @@
         <v>9.130000000000001</v>
       </c>
       <c r="H323" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I323" t="n">
-        <v>107975.57</v>
+        <v>26753.53</v>
       </c>
     </row>
     <row r="324">
@@ -11774,10 +11774,10 @@
         <v>5.63</v>
       </c>
       <c r="H324" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I324" t="n">
-        <v>66555.53</v>
+        <v>16490.72</v>
       </c>
     </row>
     <row r="325">
@@ -11809,10 +11809,10 @@
         <v>13.13</v>
       </c>
       <c r="H325" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I325" t="n">
-        <v>155348.33</v>
+        <v>38491.26</v>
       </c>
     </row>
     <row r="326">
@@ -11844,10 +11844,10 @@
         <v>2.68</v>
       </c>
       <c r="H326" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I326" t="n">
-        <v>31747.4</v>
+        <v>7866.18</v>
       </c>
     </row>
     <row r="327">
@@ -11879,10 +11879,10 @@
         <v>13.82</v>
       </c>
       <c r="H327" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I327" t="n">
-        <v>163484.49</v>
+        <v>40507.19</v>
       </c>
     </row>
     <row r="328">
@@ -11914,10 +11914,10 @@
         <v>14.1</v>
       </c>
       <c r="H328" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I328" t="n">
-        <v>166794.03</v>
+        <v>41327.21</v>
       </c>
     </row>
     <row r="329">
@@ -11949,10 +11949,10 @@
         <v>9.99</v>
       </c>
       <c r="H329" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I329" t="n">
-        <v>118150.69</v>
+        <v>29274.66</v>
       </c>
     </row>
     <row r="330">
@@ -11984,10 +11984,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H330" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I330" t="n">
-        <v>104164.94</v>
+        <v>25809.36</v>
       </c>
     </row>
     <row r="331">
@@ -12019,10 +12019,10 @@
         <v>3.42</v>
       </c>
       <c r="H331" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I331" t="n">
-        <v>40520</v>
+        <v>10039.8</v>
       </c>
     </row>
     <row r="332">
@@ -12054,10 +12054,10 @@
         <v>6.08</v>
       </c>
       <c r="H332" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
       <c r="I332" t="n">
-        <v>71920.21000000001</v>
+        <v>17819.95</v>
       </c>
     </row>
     <row r="333">
@@ -12089,10 +12089,10 @@
         <v>9.94</v>
       </c>
       <c r="H333" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I333" t="n">
-        <v>139081.9</v>
+        <v>50654.13</v>
       </c>
     </row>
     <row r="334">
@@ -12124,10 +12124,10 @@
         <v>9.15</v>
       </c>
       <c r="H334" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I334" t="n">
-        <v>128026.28</v>
+        <v>46627.63</v>
       </c>
     </row>
     <row r="335">
@@ -12159,10 +12159,10 @@
         <v>6.81</v>
       </c>
       <c r="H335" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I335" t="n">
-        <v>95357.33</v>
+        <v>34729.48</v>
       </c>
     </row>
     <row r="336">
@@ -12194,10 +12194,10 @@
         <v>8.359999999999999</v>
       </c>
       <c r="H336" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I336" t="n">
-        <v>117063.42</v>
+        <v>42634.92</v>
       </c>
     </row>
     <row r="337">
@@ -12229,10 +12229,10 @@
         <v>5.09</v>
       </c>
       <c r="H337" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I337" t="n">
-        <v>71203.62</v>
+        <v>25932.61</v>
       </c>
     </row>
     <row r="338">
@@ -12264,10 +12264,10 @@
         <v>9.050000000000001</v>
       </c>
       <c r="H338" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I338" t="n">
-        <v>126746.76</v>
+        <v>46161.63</v>
       </c>
     </row>
     <row r="339">
@@ -12299,10 +12299,10 @@
         <v>14.07</v>
       </c>
       <c r="H339" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I339" t="n">
-        <v>196903.51</v>
+        <v>71712.97</v>
       </c>
     </row>
     <row r="340">
@@ -12334,10 +12334,10 @@
         <v>15.14</v>
       </c>
       <c r="H340" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I340" t="n">
-        <v>211916.56</v>
+        <v>77180.77</v>
       </c>
     </row>
     <row r="341">
@@ -12369,10 +12369,10 @@
         <v>7.19</v>
       </c>
       <c r="H341" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I341" t="n">
-        <v>100616.37</v>
+        <v>36644.85</v>
       </c>
     </row>
     <row r="342">
@@ -12404,10 +12404,10 @@
         <v>12.32</v>
       </c>
       <c r="H342" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
       <c r="I342" t="n">
-        <v>172397.59</v>
+        <v>62787.82</v>
       </c>
     </row>
     <row r="343">
@@ -12439,10 +12439,10 @@
         <v>18.29</v>
       </c>
       <c r="H343" t="n">
-        <v>901483.97</v>
+        <v>126583.97</v>
       </c>
       <c r="I343" t="n">
-        <v>164872.19</v>
+        <v>23150.91</v>
       </c>
     </row>
     <row r="344">
@@ -12474,10 +12474,10 @@
         <v>21.97</v>
       </c>
       <c r="H344" t="n">
-        <v>901483.97</v>
+        <v>126583.97</v>
       </c>
       <c r="I344" t="n">
-        <v>198070.4</v>
+        <v>27812.52</v>
       </c>
     </row>
     <row r="345">
@@ -12509,10 +12509,10 @@
         <v>12.73</v>
       </c>
       <c r="H345" t="n">
-        <v>901483.97</v>
+        <v>126583.97</v>
       </c>
       <c r="I345" t="n">
-        <v>114780.33</v>
+        <v>16117.15</v>
       </c>
     </row>
     <row r="346">
@@ -12544,10 +12544,10 @@
         <v>22.45</v>
       </c>
       <c r="H346" t="n">
-        <v>901483.97</v>
+        <v>126583.97</v>
       </c>
       <c r="I346" t="n">
-        <v>202342.66</v>
+        <v>28412.42</v>
       </c>
     </row>
     <row r="347">
@@ -12579,10 +12579,10 @@
         <v>17.29</v>
       </c>
       <c r="H347" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I347" t="n">
-        <v>194064.32</v>
+        <v>40188.67</v>
       </c>
     </row>
     <row r="348">
@@ -12614,10 +12614,10 @@
         <v>7.66</v>
       </c>
       <c r="H348" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I348" t="n">
-        <v>85943.5</v>
+        <v>17797.99</v>
       </c>
     </row>
     <row r="349">
@@ -12649,10 +12649,10 @@
         <v>6.37</v>
       </c>
       <c r="H349" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I349" t="n">
-        <v>71466.99000000001</v>
+        <v>14800.06</v>
       </c>
     </row>
     <row r="350">
@@ -12684,10 +12684,10 @@
         <v>4.17</v>
       </c>
       <c r="H350" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I350" t="n">
-        <v>46862.94</v>
+        <v>9704.82</v>
       </c>
     </row>
     <row r="351">
@@ -12719,10 +12719,10 @@
         <v>14.05</v>
       </c>
       <c r="H351" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I351" t="n">
-        <v>157750.87</v>
+        <v>32668.54</v>
       </c>
     </row>
     <row r="352">
@@ -12754,10 +12754,10 @@
         <v>17.81</v>
       </c>
       <c r="H352" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I352" t="n">
-        <v>199916.71</v>
+        <v>41400.63</v>
       </c>
     </row>
     <row r="353">
@@ -12789,10 +12789,10 @@
         <v>11.51</v>
       </c>
       <c r="H353" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I353" t="n">
-        <v>129204.05</v>
+        <v>26756.79</v>
       </c>
     </row>
     <row r="354">
@@ -12824,10 +12824,10 @@
         <v>15.17</v>
       </c>
       <c r="H354" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I354" t="n">
-        <v>170323.99</v>
+        <v>35272.3</v>
       </c>
     </row>
     <row r="355">
@@ -12859,10 +12859,10 @@
         <v>5.22</v>
       </c>
       <c r="H355" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
       <c r="I355" t="n">
-        <v>58542.61</v>
+        <v>12123.55</v>
       </c>
     </row>
     <row r="356">
@@ -12894,10 +12894,10 @@
         <v>12.07</v>
       </c>
       <c r="H356" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
       <c r="I356" t="n">
-        <v>145355.05</v>
+        <v>37924.15</v>
       </c>
     </row>
     <row r="357">
@@ -12929,10 +12929,10 @@
         <v>18.22</v>
       </c>
       <c r="H357" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
       <c r="I357" t="n">
-        <v>219375.56</v>
+        <v>57236.62</v>
       </c>
     </row>
     <row r="358">
@@ -12964,10 +12964,10 @@
         <v>12.75</v>
       </c>
       <c r="H358" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
       <c r="I358" t="n">
-        <v>153548.25</v>
+        <v>40061.81</v>
       </c>
     </row>
     <row r="359">
@@ -12999,10 +12999,10 @@
         <v>8.27</v>
       </c>
       <c r="H359" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
       <c r="I359" t="n">
-        <v>99620.41</v>
+        <v>25991.66</v>
       </c>
     </row>
     <row r="360">
@@ -13034,10 +13034,10 @@
         <v>8.65</v>
       </c>
       <c r="H360" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
       <c r="I360" t="n">
-        <v>104177.97</v>
+        <v>27180.76</v>
       </c>
     </row>
     <row r="361">
@@ -13069,10 +13069,10 @@
         <v>16.54</v>
       </c>
       <c r="H361" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
       <c r="I361" t="n">
-        <v>199204.84</v>
+        <v>51973.94</v>
       </c>
     </row>
     <row r="362">
@@ -13104,10 +13104,10 @@
         <v>11.56</v>
       </c>
       <c r="H362" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
       <c r="I362" t="n">
-        <v>139234.36</v>
+        <v>36327.22</v>
       </c>
     </row>
     <row r="363">
@@ -13139,10 +13139,10 @@
         <v>4.34</v>
       </c>
       <c r="H363" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I363" t="n">
-        <v>49653.15</v>
+        <v>11002.79</v>
       </c>
     </row>
     <row r="364">
@@ -13174,10 +13174,10 @@
         <v>9.92</v>
       </c>
       <c r="H364" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I364" t="n">
-        <v>113375</v>
+        <v>25123.11</v>
       </c>
     </row>
     <row r="365">
@@ -13209,10 +13209,10 @@
         <v>11.05</v>
       </c>
       <c r="H365" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I365" t="n">
-        <v>126384.33</v>
+        <v>28005.89</v>
       </c>
     </row>
     <row r="366">
@@ -13244,10 +13244,10 @@
         <v>14.11</v>
       </c>
       <c r="H366" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I366" t="n">
-        <v>161372.13</v>
+        <v>35758.94</v>
       </c>
     </row>
     <row r="367">
@@ -13279,10 +13279,10 @@
         <v>10.87</v>
       </c>
       <c r="H367" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I367" t="n">
-        <v>124259.65</v>
+        <v>27535.07</v>
       </c>
     </row>
     <row r="368">
@@ -13314,10 +13314,10 @@
         <v>5.29</v>
       </c>
       <c r="H368" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I368" t="n">
-        <v>60525.71</v>
+        <v>13412.07</v>
       </c>
     </row>
     <row r="369">
@@ -13349,10 +13349,10 @@
         <v>8.18</v>
       </c>
       <c r="H369" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I369" t="n">
-        <v>93482.32000000001</v>
+        <v>20715.03</v>
       </c>
     </row>
     <row r="370">
@@ -13384,10 +13384,10 @@
         <v>15.7</v>
       </c>
       <c r="H370" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I370" t="n">
-        <v>179503.23</v>
+        <v>39776.67</v>
       </c>
     </row>
     <row r="371">
@@ -13419,10 +13419,10 @@
         <v>3.87</v>
       </c>
       <c r="H371" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I371" t="n">
-        <v>44253.05</v>
+        <v>9806.17</v>
       </c>
     </row>
     <row r="372">
@@ -13454,10 +13454,10 @@
         <v>9.98</v>
       </c>
       <c r="H372" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
       <c r="I372" t="n">
-        <v>114072.89</v>
+        <v>25277.76</v>
       </c>
     </row>
     <row r="373">
@@ -13489,10 +13489,10 @@
         <v>8.15</v>
       </c>
       <c r="H373" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I373" t="n">
-        <v>88136.14</v>
+        <v>15584.79</v>
       </c>
     </row>
     <row r="374">
@@ -13524,10 +13524,10 @@
         <v>12.48</v>
       </c>
       <c r="H374" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I374" t="n">
-        <v>134902.81</v>
+        <v>23854.36</v>
       </c>
     </row>
     <row r="375">
@@ -13559,10 +13559,10 @@
         <v>10.09</v>
       </c>
       <c r="H375" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I375" t="n">
-        <v>109099.58</v>
+        <v>19291.67</v>
       </c>
     </row>
     <row r="376">
@@ -13594,10 +13594,10 @@
         <v>5.49</v>
       </c>
       <c r="H376" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I376" t="n">
-        <v>59340.49</v>
+        <v>10492.96</v>
       </c>
     </row>
     <row r="377">
@@ -13629,10 +13629,10 @@
         <v>7.27</v>
       </c>
       <c r="H377" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I377" t="n">
-        <v>78579.46000000001</v>
+        <v>13894.91</v>
       </c>
     </row>
     <row r="378">
@@ -13664,10 +13664,10 @@
         <v>8.869999999999999</v>
       </c>
       <c r="H378" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I378" t="n">
-        <v>95893.27</v>
+        <v>16956.45</v>
       </c>
     </row>
     <row r="379">
@@ -13699,10 +13699,10 @@
         <v>13.41</v>
       </c>
       <c r="H379" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I379" t="n">
-        <v>145025.01</v>
+        <v>25644.23</v>
       </c>
     </row>
     <row r="380">
@@ -13734,10 +13734,10 @@
         <v>11.87</v>
       </c>
       <c r="H380" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I380" t="n">
-        <v>128316.7</v>
+        <v>22689.76</v>
       </c>
     </row>
     <row r="381">
@@ -13769,10 +13769,10 @@
         <v>8.949999999999999</v>
       </c>
       <c r="H381" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I381" t="n">
-        <v>96756.12</v>
+        <v>17109.02</v>
       </c>
     </row>
     <row r="382">
@@ -13804,10 +13804,10 @@
         <v>10.76</v>
       </c>
       <c r="H382" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
       <c r="I382" t="n">
-        <v>116387.29</v>
+        <v>20580.33</v>
       </c>
     </row>
     <row r="383">
@@ -13839,10 +13839,10 @@
         <v>13.94</v>
       </c>
       <c r="H383" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I383" t="n">
-        <v>155091.52</v>
+        <v>31065.99</v>
       </c>
     </row>
     <row r="384">
@@ -13874,10 +13874,10 @@
         <v>8.06</v>
       </c>
       <c r="H384" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I384" t="n">
-        <v>89657.28</v>
+        <v>17959.02</v>
       </c>
     </row>
     <row r="385">
@@ -13909,10 +13909,10 @@
         <v>6.32</v>
       </c>
       <c r="H385" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I385" t="n">
-        <v>70344.02</v>
+        <v>14090.43</v>
       </c>
     </row>
     <row r="386">
@@ -13944,10 +13944,10 @@
         <v>16.07</v>
       </c>
       <c r="H386" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I386" t="n">
-        <v>178861.64</v>
+        <v>35827.32</v>
       </c>
     </row>
     <row r="387">
@@ -13979,10 +13979,10 @@
         <v>7.17</v>
       </c>
       <c r="H387" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I387" t="n">
-        <v>79792.14999999999</v>
+        <v>15982.96</v>
       </c>
     </row>
     <row r="388">
@@ -14014,10 +14014,10 @@
         <v>11.66</v>
       </c>
       <c r="H388" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I388" t="n">
-        <v>129813.03</v>
+        <v>26002.52</v>
       </c>
     </row>
     <row r="389">
@@ -14049,10 +14049,10 @@
         <v>14.05</v>
       </c>
       <c r="H389" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I389" t="n">
-        <v>156320.61</v>
+        <v>31312.19</v>
       </c>
     </row>
     <row r="390">
@@ -14084,10 +14084,10 @@
         <v>11.2</v>
       </c>
       <c r="H390" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
       <c r="I390" t="n">
-        <v>124668.57</v>
+        <v>24972.04</v>
       </c>
     </row>
     <row r="391">
@@ -14119,10 +14119,10 @@
         <v>7.36</v>
       </c>
       <c r="H391" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I391" t="n">
-        <v>79717.56</v>
+        <v>14230.28</v>
       </c>
     </row>
     <row r="392">
@@ -14154,10 +14154,10 @@
         <v>5.23</v>
       </c>
       <c r="H392" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I392" t="n">
-        <v>56641.9</v>
+        <v>10111.08</v>
       </c>
     </row>
     <row r="393">
@@ -14189,10 +14189,10 @@
         <v>12.97</v>
       </c>
       <c r="H393" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I393" t="n">
-        <v>140514.02</v>
+        <v>25082.99</v>
       </c>
     </row>
     <row r="394">
@@ -14224,10 +14224,10 @@
         <v>13.87</v>
       </c>
       <c r="H394" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I394" t="n">
-        <v>150307.4</v>
+        <v>26831.19</v>
       </c>
     </row>
     <row r="395">
@@ -14259,10 +14259,10 @@
         <v>15.55</v>
       </c>
       <c r="H395" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I395" t="n">
-        <v>168454.88</v>
+        <v>30070.68</v>
       </c>
     </row>
     <row r="396">
@@ -14294,10 +14294,10 @@
         <v>10.94</v>
       </c>
       <c r="H396" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I396" t="n">
-        <v>118520.37</v>
+        <v>21156.93</v>
       </c>
     </row>
     <row r="397">
@@ -14329,10 +14329,10 @@
         <v>16.41</v>
       </c>
       <c r="H397" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I397" t="n">
-        <v>177764.75</v>
+        <v>31732.57</v>
       </c>
     </row>
     <row r="398">
@@ -14364,10 +14364,10 @@
         <v>11.66</v>
       </c>
       <c r="H398" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I398" t="n">
-        <v>126305.81</v>
+        <v>22546.7</v>
       </c>
     </row>
     <row r="399">
@@ -14399,10 +14399,10 @@
         <v>0.88</v>
       </c>
       <c r="H399" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I399" t="n">
-        <v>9496.98</v>
+        <v>1695.29</v>
       </c>
     </row>
     <row r="400">
@@ -14434,10 +14434,10 @@
         <v>5.01</v>
       </c>
       <c r="H400" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
       <c r="I400" t="n">
-        <v>54286.53</v>
+        <v>9690.620000000001</v>
       </c>
     </row>
     <row r="401">

--- a/store_wise_monthly_costs.xlsx
+++ b/store_wise_monthly_costs.xlsx
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>DPI67178</t>
+          <t>DPI66742</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>83.31</v>
+        <v>200.32</v>
       </c>
       <c r="E178" t="n">
         <v>980</v>
@@ -6661,13 +6661,13 @@
         <v>965</v>
       </c>
       <c r="G178" t="n">
-        <v>8.5</v>
+        <v>20.44</v>
       </c>
       <c r="H178" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I178" t="n">
-        <v>37306.54</v>
+        <v>89681.62</v>
       </c>
     </row>
     <row r="179">
@@ -6683,11 +6683,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>DPI64297</t>
+          <t>DPI64724</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>126.1</v>
+        <v>84.75</v>
       </c>
       <c r="E179" t="n">
         <v>980</v>
@@ -6696,13 +6696,13 @@
         <v>965</v>
       </c>
       <c r="G179" t="n">
-        <v>12.87</v>
+        <v>8.65</v>
       </c>
       <c r="H179" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I179" t="n">
-        <v>56468.7</v>
+        <v>37940.16</v>
       </c>
     </row>
     <row r="180">
@@ -6734,10 +6734,10 @@
         <v>13.44</v>
       </c>
       <c r="H180" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I180" t="n">
-        <v>58985.83</v>
+        <v>58968.53</v>
       </c>
     </row>
     <row r="181">
@@ -6753,11 +6753,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DPI64724</t>
+          <t>DPI64297</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>84.75</v>
+        <v>126.1</v>
       </c>
       <c r="E181" t="n">
         <v>980</v>
@@ -6766,13 +6766,13 @@
         <v>965</v>
       </c>
       <c r="G181" t="n">
-        <v>8.65</v>
+        <v>12.87</v>
       </c>
       <c r="H181" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I181" t="n">
-        <v>37951.29</v>
+        <v>56452.14</v>
       </c>
     </row>
     <row r="182">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>DPI66742</t>
+          <t>DPI67178</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>200.32</v>
+        <v>83.31</v>
       </c>
       <c r="E182" t="n">
         <v>980</v>
@@ -6801,13 +6801,13 @@
         <v>965</v>
       </c>
       <c r="G182" t="n">
-        <v>20.44</v>
+        <v>8.5</v>
       </c>
       <c r="H182" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I182" t="n">
-        <v>89707.92999999999</v>
+        <v>37295.6</v>
       </c>
     </row>
     <row r="183">
@@ -6839,10 +6839,10 @@
         <v>14.21</v>
       </c>
       <c r="H183" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I183" t="n">
-        <v>62382.07</v>
+        <v>62363.77</v>
       </c>
     </row>
     <row r="184">
@@ -6874,10 +6874,10 @@
         <v>7.93</v>
       </c>
       <c r="H184" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I184" t="n">
-        <v>34788.32</v>
+        <v>34778.11</v>
       </c>
     </row>
     <row r="185">
@@ -6909,10 +6909,10 @@
         <v>7.67</v>
       </c>
       <c r="H185" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I185" t="n">
-        <v>33673.03</v>
+        <v>33663.16</v>
       </c>
     </row>
     <row r="186">
@@ -6944,10 +6944,10 @@
         <v>4.77</v>
       </c>
       <c r="H186" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
       <c r="I186" t="n">
-        <v>20926.67</v>
+        <v>20920.53</v>
       </c>
     </row>
     <row r="187">
@@ -8223,11 +8223,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DPI64431</t>
+          <t>DPI66597</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>78.73</v>
+        <v>90.83</v>
       </c>
       <c r="E223" t="n">
         <v>980</v>
@@ -8236,13 +8236,13 @@
         <v>957</v>
       </c>
       <c r="G223" t="n">
-        <v>8.029999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="H223" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I223" t="n">
-        <v>21895.45</v>
+        <v>25425.38</v>
       </c>
     </row>
     <row r="224">
@@ -8258,11 +8258,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DPI66449</t>
+          <t>DPI66373</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>191.04</v>
+        <v>98.05</v>
       </c>
       <c r="E224" t="n">
         <v>980</v>
@@ -8271,13 +8271,13 @@
         <v>957</v>
       </c>
       <c r="G224" t="n">
-        <v>19.49</v>
+        <v>10.01</v>
       </c>
       <c r="H224" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I224" t="n">
-        <v>53129.44</v>
+        <v>27445.31</v>
       </c>
     </row>
     <row r="225">
@@ -8293,11 +8293,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DPI67072</t>
+          <t>DPI66154</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>126.86</v>
+        <v>73.08</v>
       </c>
       <c r="E225" t="n">
         <v>980</v>
@@ -8306,13 +8306,13 @@
         <v>957</v>
       </c>
       <c r="G225" t="n">
-        <v>12.94</v>
+        <v>7.46</v>
       </c>
       <c r="H225" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I225" t="n">
-        <v>35279.6</v>
+        <v>20455.65</v>
       </c>
     </row>
     <row r="226">
@@ -8344,10 +8344,10 @@
         <v>9.93</v>
       </c>
       <c r="H226" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I226" t="n">
-        <v>27067.14</v>
+        <v>27242.66</v>
       </c>
     </row>
     <row r="227">
@@ -8363,11 +8363,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>DPI66154</t>
+          <t>DPI67072</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>73.08</v>
+        <v>126.86</v>
       </c>
       <c r="E227" t="n">
         <v>980</v>
@@ -8376,13 +8376,13 @@
         <v>957</v>
       </c>
       <c r="G227" t="n">
-        <v>7.46</v>
+        <v>12.94</v>
       </c>
       <c r="H227" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I227" t="n">
-        <v>20323.86</v>
+        <v>35508.37</v>
       </c>
     </row>
     <row r="228">
@@ -8398,11 +8398,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DPI66373</t>
+          <t>DPI66449</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>98.05</v>
+        <v>191.04</v>
       </c>
       <c r="E228" t="n">
         <v>980</v>
@@ -8411,13 +8411,13 @@
         <v>957</v>
       </c>
       <c r="G228" t="n">
-        <v>10.01</v>
+        <v>19.49</v>
       </c>
       <c r="H228" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I228" t="n">
-        <v>27268.49</v>
+        <v>53473.95</v>
       </c>
     </row>
     <row r="229">
@@ -8433,11 +8433,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DPI64196</t>
+          <t>DPI64431</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>79.7</v>
+        <v>78.73</v>
       </c>
       <c r="E229" t="n">
         <v>980</v>
@@ -8446,13 +8446,13 @@
         <v>957</v>
       </c>
       <c r="G229" t="n">
-        <v>8.130000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H229" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I229" t="n">
-        <v>22165.64</v>
+        <v>22037.43</v>
       </c>
     </row>
     <row r="230">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DPI66221</t>
+          <t>DPI64196</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>121.2</v>
+        <v>79.7</v>
       </c>
       <c r="E230" t="n">
         <v>980</v>
@@ -8481,13 +8481,13 @@
         <v>957</v>
       </c>
       <c r="G230" t="n">
-        <v>12.37</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H230" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I230" t="n">
-        <v>33707.34</v>
+        <v>22309.37</v>
       </c>
     </row>
     <row r="231">
@@ -8503,11 +8503,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DPI66597</t>
+          <t>DPI66221</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>90.83</v>
+        <v>121.2</v>
       </c>
       <c r="E231" t="n">
         <v>980</v>
@@ -8516,13 +8516,13 @@
         <v>957</v>
       </c>
       <c r="G231" t="n">
-        <v>9.27</v>
+        <v>12.37</v>
       </c>
       <c r="H231" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
       <c r="I231" t="n">
-        <v>25261.57</v>
+        <v>33925.91</v>
       </c>
     </row>
     <row r="232">
@@ -8818,11 +8818,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DPI64436</t>
+          <t>DPI64638</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>86.91</v>
+        <v>88.97</v>
       </c>
       <c r="E240" t="n">
         <v>980</v>
@@ -8831,13 +8831,13 @@
         <v>961</v>
       </c>
       <c r="G240" t="n">
-        <v>8.869999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="H240" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I240" t="n">
-        <v>35511.67</v>
+        <v>36378.33</v>
       </c>
     </row>
     <row r="241">
@@ -8853,11 +8853,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DPI64456</t>
+          <t>DPI66307</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>111.28</v>
+        <v>125.94</v>
       </c>
       <c r="E241" t="n">
         <v>980</v>
@@ -8866,13 +8866,13 @@
         <v>961</v>
       </c>
       <c r="G241" t="n">
-        <v>11.36</v>
+        <v>12.85</v>
       </c>
       <c r="H241" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I241" t="n">
-        <v>45470.26</v>
+        <v>51494.65</v>
       </c>
     </row>
     <row r="242">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DPI66946</t>
+          <t>DPI66039</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>126.11</v>
+        <v>114.76</v>
       </c>
       <c r="E242" t="n">
         <v>980</v>
@@ -8901,13 +8901,13 @@
         <v>961</v>
       </c>
       <c r="G242" t="n">
-        <v>12.87</v>
+        <v>11.71</v>
       </c>
       <c r="H242" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I242" t="n">
-        <v>51526.82</v>
+        <v>46924.55</v>
       </c>
     </row>
     <row r="243">
@@ -8923,11 +8923,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>DPI64136</t>
+          <t>DPI63958</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>70.68000000000001</v>
+        <v>120.83</v>
       </c>
       <c r="E243" t="n">
         <v>980</v>
@@ -8936,13 +8936,13 @@
         <v>961</v>
       </c>
       <c r="G243" t="n">
-        <v>7.21</v>
+        <v>12.33</v>
       </c>
       <c r="H243" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I243" t="n">
-        <v>28879.7</v>
+        <v>49407.27</v>
       </c>
     </row>
     <row r="244">
@@ -8974,10 +8974,10 @@
         <v>11.74</v>
       </c>
       <c r="H244" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I244" t="n">
-        <v>47000.66</v>
+        <v>47033.86</v>
       </c>
     </row>
     <row r="245">
@@ -8993,11 +8993,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DPI66039</t>
+          <t>DPI64136</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>114.76</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="E245" t="n">
         <v>980</v>
@@ -9006,13 +9006,13 @@
         <v>961</v>
       </c>
       <c r="G245" t="n">
-        <v>11.71</v>
+        <v>7.21</v>
       </c>
       <c r="H245" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I245" t="n">
-        <v>46891.43</v>
+        <v>28900.1</v>
       </c>
     </row>
     <row r="246">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DPI66307</t>
+          <t>DPI66946</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>125.94</v>
+        <v>126.11</v>
       </c>
       <c r="E246" t="n">
         <v>980</v>
@@ -9041,13 +9041,13 @@
         <v>961</v>
       </c>
       <c r="G246" t="n">
-        <v>12.85</v>
+        <v>12.87</v>
       </c>
       <c r="H246" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I246" t="n">
-        <v>51458.3</v>
+        <v>51563.22</v>
       </c>
     </row>
     <row r="247">
@@ -9063,11 +9063,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DPI64638</t>
+          <t>DPI64456</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>88.97</v>
+        <v>111.28</v>
       </c>
       <c r="E247" t="n">
         <v>980</v>
@@ -9076,13 +9076,13 @@
         <v>961</v>
       </c>
       <c r="G247" t="n">
-        <v>9.08</v>
+        <v>11.36</v>
       </c>
       <c r="H247" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I247" t="n">
-        <v>36352.65</v>
+        <v>45502.38</v>
       </c>
     </row>
     <row r="248">
@@ -9098,11 +9098,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DPI63958</t>
+          <t>DPI64436</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>120.83</v>
+        <v>86.91</v>
       </c>
       <c r="E248" t="n">
         <v>980</v>
@@ -9111,13 +9111,13 @@
         <v>961</v>
       </c>
       <c r="G248" t="n">
-        <v>12.33</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H248" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
       <c r="I248" t="n">
-        <v>49372.39</v>
+        <v>35536.76</v>
       </c>
     </row>
     <row r="249">
@@ -14469,10 +14469,10 @@
         <v>7.87</v>
       </c>
       <c r="H401" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I401" t="n">
-        <v>107000.44</v>
+        <v>36954.74</v>
       </c>
     </row>
     <row r="402">
@@ -14504,10 +14504,10 @@
         <v>17.88</v>
       </c>
       <c r="H402" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I402" t="n">
-        <v>243071.96</v>
+        <v>83949.75999999999</v>
       </c>
     </row>
     <row r="403">
@@ -14539,10 +14539,10 @@
         <v>9.75</v>
       </c>
       <c r="H403" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I403" t="n">
-        <v>132550.97</v>
+        <v>45779.13</v>
       </c>
     </row>
     <row r="404">
@@ -14574,10 +14574,10 @@
         <v>9.31</v>
       </c>
       <c r="H404" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I404" t="n">
-        <v>126594.88</v>
+        <v>43722.07</v>
       </c>
     </row>
     <row r="405">
@@ -14609,10 +14609,10 @@
         <v>4.47</v>
       </c>
       <c r="H405" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I405" t="n">
-        <v>60741.25</v>
+        <v>20978.2</v>
       </c>
     </row>
     <row r="406">
@@ -14644,10 +14644,10 @@
         <v>17.71</v>
       </c>
       <c r="H406" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I406" t="n">
-        <v>240825.28</v>
+        <v>83173.82000000001</v>
       </c>
     </row>
     <row r="407">
@@ -14679,10 +14679,10 @@
         <v>12.59</v>
       </c>
       <c r="H407" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I407" t="n">
-        <v>171147.8</v>
+        <v>59109.31</v>
       </c>
     </row>
     <row r="408">
@@ -14714,10 +14714,10 @@
         <v>8.81</v>
       </c>
       <c r="H408" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I408" t="n">
-        <v>119841.02</v>
+        <v>41389.49</v>
       </c>
     </row>
     <row r="409">
@@ -14749,10 +14749,10 @@
         <v>3.41</v>
       </c>
       <c r="H409" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I409" t="n">
-        <v>46401.95</v>
+        <v>16025.84</v>
       </c>
     </row>
     <row r="410">
@@ -14784,10 +14784,10 @@
         <v>4.56</v>
       </c>
       <c r="H410" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I410" t="n">
-        <v>62001.77</v>
+        <v>21413.55</v>
       </c>
     </row>
     <row r="411">
@@ -14819,10 +14819,10 @@
         <v>3.16</v>
       </c>
       <c r="H411" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
       <c r="I411" t="n">
-        <v>42979.66</v>
+        <v>14843.88</v>
       </c>
     </row>
     <row r="412">
@@ -14854,10 +14854,10 @@
         <v>16.82</v>
       </c>
       <c r="H412" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I412" t="n">
-        <v>197890.86</v>
+        <v>48209.16</v>
       </c>
     </row>
     <row r="413">
@@ -14889,10 +14889,10 @@
         <v>10.78</v>
       </c>
       <c r="H413" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I413" t="n">
-        <v>126900.15</v>
+        <v>30914.77</v>
       </c>
     </row>
     <row r="414">
@@ -14924,10 +14924,10 @@
         <v>12.18</v>
       </c>
       <c r="H414" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I414" t="n">
-        <v>143355.4</v>
+        <v>34923.51</v>
       </c>
     </row>
     <row r="415">
@@ -14959,10 +14959,10 @@
         <v>10.78</v>
       </c>
       <c r="H415" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I415" t="n">
-        <v>126795.13</v>
+        <v>30889.18</v>
       </c>
     </row>
     <row r="416">
@@ -14994,10 +14994,10 @@
         <v>13.63</v>
       </c>
       <c r="H416" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I416" t="n">
-        <v>160432.92</v>
+        <v>39083.85</v>
       </c>
     </row>
     <row r="417">
@@ -15029,10 +15029,10 @@
         <v>10.78</v>
       </c>
       <c r="H417" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I417" t="n">
-        <v>126811.62</v>
+        <v>30893.2</v>
       </c>
     </row>
     <row r="418">
@@ -15064,10 +15064,10 @@
         <v>17.84</v>
       </c>
       <c r="H418" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I418" t="n">
-        <v>209898.82</v>
+        <v>51134.48</v>
       </c>
     </row>
     <row r="419">
@@ -15099,10 +15099,10 @@
         <v>7.08</v>
       </c>
       <c r="H419" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
       <c r="I419" t="n">
-        <v>83268.33</v>
+        <v>20285.41</v>
       </c>
     </row>
     <row r="420">
@@ -15134,10 +15134,10 @@
         <v>14.05</v>
       </c>
       <c r="H420" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I420" t="n">
-        <v>167834.86</v>
+        <v>42799.78</v>
       </c>
     </row>
     <row r="421">
@@ -15169,10 +15169,10 @@
         <v>14.16</v>
       </c>
       <c r="H421" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I421" t="n">
-        <v>169126.93</v>
+        <v>43129.27</v>
       </c>
     </row>
     <row r="422">
@@ -15204,10 +15204,10 @@
         <v>13.24</v>
       </c>
       <c r="H422" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I422" t="n">
-        <v>158143.67</v>
+        <v>40328.42</v>
       </c>
     </row>
     <row r="423">
@@ -15239,10 +15239,10 @@
         <v>9.91</v>
       </c>
       <c r="H423" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I423" t="n">
-        <v>118384.85</v>
+        <v>30189.47</v>
       </c>
     </row>
     <row r="424">
@@ -15274,10 +15274,10 @@
         <v>4.02</v>
       </c>
       <c r="H424" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I424" t="n">
-        <v>48037.92</v>
+        <v>12250.21</v>
       </c>
     </row>
     <row r="425">
@@ -15309,10 +15309,10 @@
         <v>10.14</v>
       </c>
       <c r="H425" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I425" t="n">
-        <v>121145.84</v>
+        <v>30893.55</v>
       </c>
     </row>
     <row r="426">
@@ -15344,10 +15344,10 @@
         <v>14.72</v>
       </c>
       <c r="H426" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I426" t="n">
-        <v>175868.54</v>
+        <v>44848.46</v>
       </c>
     </row>
     <row r="427">
@@ -15379,10 +15379,10 @@
         <v>13.33</v>
       </c>
       <c r="H427" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I427" t="n">
-        <v>159202.7</v>
+        <v>40598.48</v>
       </c>
     </row>
     <row r="428">
@@ -15414,10 +15414,10 @@
         <v>5.24</v>
       </c>
       <c r="H428" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
       <c r="I428" t="n">
-        <v>62572.46</v>
+        <v>15956.68</v>
       </c>
     </row>
     <row r="429">
@@ -15449,10 +15449,10 @@
         <v>12.64</v>
       </c>
       <c r="H429" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I429" t="n">
-        <v>152726.67</v>
+        <v>40225.9</v>
       </c>
     </row>
     <row r="430">
@@ -15484,10 +15484,10 @@
         <v>7.11</v>
       </c>
       <c r="H430" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I430" t="n">
-        <v>85890.72</v>
+        <v>22622.32</v>
       </c>
     </row>
     <row r="431">
@@ -15519,10 +15519,10 @@
         <v>9.83</v>
       </c>
       <c r="H431" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I431" t="n">
-        <v>118804.81</v>
+        <v>31291.39</v>
       </c>
     </row>
     <row r="432">
@@ -15554,10 +15554,10 @@
         <v>9.58</v>
       </c>
       <c r="H432" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I432" t="n">
-        <v>115779.21</v>
+        <v>30494.49</v>
       </c>
     </row>
     <row r="433">
@@ -15589,10 +15589,10 @@
         <v>10.54</v>
       </c>
       <c r="H433" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I433" t="n">
-        <v>127353.57</v>
+        <v>33543.01</v>
       </c>
     </row>
     <row r="434">
@@ -15624,10 +15624,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H434" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I434" t="n">
-        <v>105174.1</v>
+        <v>27701.27</v>
       </c>
     </row>
     <row r="435">
@@ -15659,10 +15659,10 @@
         <v>15.18</v>
       </c>
       <c r="H435" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I435" t="n">
-        <v>183383.69</v>
+        <v>48300.49</v>
       </c>
     </row>
     <row r="436">
@@ -15694,10 +15694,10 @@
         <v>9.48</v>
       </c>
       <c r="H436" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I436" t="n">
-        <v>114564.53</v>
+        <v>30174.57</v>
       </c>
     </row>
     <row r="437">
@@ -15729,10 +15729,10 @@
         <v>13.8</v>
       </c>
       <c r="H437" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
       <c r="I437" t="n">
-        <v>166703.54</v>
+        <v>43907.19</v>
       </c>
     </row>
     <row r="438">
@@ -15764,10 +15764,10 @@
         <v>17.23</v>
       </c>
       <c r="H438" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I438" t="n">
-        <v>204878.74</v>
+        <v>51510.89</v>
       </c>
     </row>
     <row r="439">
@@ -15799,10 +15799,10 @@
         <v>2.33</v>
       </c>
       <c r="H439" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I439" t="n">
-        <v>27648.32</v>
+        <v>6951.38</v>
       </c>
     </row>
     <row r="440">
@@ -15834,10 +15834,10 @@
         <v>14.56</v>
       </c>
       <c r="H440" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I440" t="n">
-        <v>173131.94</v>
+        <v>43529.07</v>
       </c>
     </row>
     <row r="441">
@@ -15869,10 +15869,10 @@
         <v>9.94</v>
       </c>
       <c r="H441" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I441" t="n">
-        <v>118133.19</v>
+        <v>29701.21</v>
       </c>
     </row>
     <row r="442">
@@ -15904,10 +15904,10 @@
         <v>12.83</v>
       </c>
       <c r="H442" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I442" t="n">
-        <v>152541.43</v>
+        <v>38352.18</v>
       </c>
     </row>
     <row r="443">
@@ -15939,10 +15939,10 @@
         <v>11.21</v>
       </c>
       <c r="H443" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I443" t="n">
-        <v>133326.22</v>
+        <v>33521.06</v>
       </c>
     </row>
     <row r="444">
@@ -15974,10 +15974,10 @@
         <v>9.210000000000001</v>
       </c>
       <c r="H444" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I444" t="n">
-        <v>109502.89</v>
+        <v>27531.37</v>
       </c>
     </row>
     <row r="445">
@@ -16009,10 +16009,10 @@
         <v>11.77</v>
       </c>
       <c r="H445" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I445" t="n">
-        <v>139949.88</v>
+        <v>35186.39</v>
       </c>
     </row>
     <row r="446">
@@ -16044,10 +16044,10 @@
         <v>6.26</v>
       </c>
       <c r="H446" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I446" t="n">
-        <v>74417.38</v>
+        <v>18710.12</v>
       </c>
     </row>
     <row r="447">
@@ -16079,10 +16079,10 @@
         <v>3.95</v>
       </c>
       <c r="H447" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
       <c r="I447" t="n">
-        <v>46925.62</v>
+        <v>11798.1</v>
       </c>
     </row>
     <row r="448">
@@ -16114,10 +16114,10 @@
         <v>9.41</v>
       </c>
       <c r="H448" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I448" t="n">
-        <v>134521.01</v>
+        <v>50751.48</v>
       </c>
     </row>
     <row r="449">
@@ -16149,10 +16149,10 @@
         <v>7.12</v>
       </c>
       <c r="H449" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I449" t="n">
-        <v>101706.43</v>
+        <v>38371.34</v>
       </c>
     </row>
     <row r="450">
@@ -16184,10 +16184,10 @@
         <v>11.41</v>
       </c>
       <c r="H450" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I450" t="n">
-        <v>163025.91</v>
+        <v>61505.68</v>
       </c>
     </row>
     <row r="451">
@@ -16219,10 +16219,10 @@
         <v>5.41</v>
       </c>
       <c r="H451" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I451" t="n">
-        <v>77306.64999999999</v>
+        <v>29165.9</v>
       </c>
     </row>
     <row r="452">
@@ -16254,10 +16254,10 @@
         <v>10.26</v>
       </c>
       <c r="H452" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I452" t="n">
-        <v>146597.34</v>
+        <v>55307.59</v>
       </c>
     </row>
     <row r="453">
@@ -16289,10 +16289,10 @@
         <v>4.44</v>
       </c>
       <c r="H453" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I453" t="n">
-        <v>63479.22</v>
+        <v>23949.16</v>
       </c>
     </row>
     <row r="454">
@@ -16324,10 +16324,10 @@
         <v>8.23</v>
       </c>
       <c r="H454" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I454" t="n">
-        <v>117675.91</v>
+        <v>44396.24</v>
       </c>
     </row>
     <row r="455">
@@ -16359,10 +16359,10 @@
         <v>7.04</v>
       </c>
       <c r="H455" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I455" t="n">
-        <v>100598.82</v>
+        <v>37953.47</v>
       </c>
     </row>
     <row r="456">
@@ -16394,10 +16394,10 @@
         <v>5.29</v>
       </c>
       <c r="H456" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I456" t="n">
-        <v>75536.19</v>
+        <v>28497.95</v>
       </c>
     </row>
     <row r="457">
@@ -16429,10 +16429,10 @@
         <v>7.26</v>
       </c>
       <c r="H457" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I457" t="n">
-        <v>103824.89</v>
+        <v>39170.59</v>
       </c>
     </row>
     <row r="458">
@@ -16464,10 +16464,10 @@
         <v>5.77</v>
       </c>
       <c r="H458" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I458" t="n">
-        <v>82486.36</v>
+        <v>31120.08</v>
       </c>
     </row>
     <row r="459">
@@ -16499,10 +16499,10 @@
         <v>6.73</v>
       </c>
       <c r="H459" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I459" t="n">
-        <v>96240.39999999999</v>
+        <v>36309.14</v>
       </c>
     </row>
     <row r="460">
@@ -16534,10 +16534,10 @@
         <v>7.84</v>
       </c>
       <c r="H460" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
       <c r="I460" t="n">
-        <v>111994.48</v>
+        <v>42252.77</v>
       </c>
     </row>
     <row r="461">
@@ -16569,10 +16569,10 @@
         <v>10.16</v>
       </c>
       <c r="H461" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I461" t="n">
-        <v>116509.13</v>
+        <v>26114.75</v>
       </c>
     </row>
     <row r="462">
@@ -16604,10 +16604,10 @@
         <v>27.86</v>
       </c>
       <c r="H462" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I462" t="n">
-        <v>319641.14</v>
+        <v>71645.42999999999</v>
       </c>
     </row>
     <row r="463">
@@ -16639,10 +16639,10 @@
         <v>10.95</v>
       </c>
       <c r="H463" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I463" t="n">
-        <v>125577.67</v>
+        <v>28147.4</v>
       </c>
     </row>
     <row r="464">
@@ -16674,10 +16674,10 @@
         <v>6.67</v>
       </c>
       <c r="H464" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I464" t="n">
-        <v>76551.61</v>
+        <v>17158.53</v>
       </c>
     </row>
     <row r="465">
@@ -16709,10 +16709,10 @@
         <v>10.53</v>
       </c>
       <c r="H465" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I465" t="n">
-        <v>120828.79</v>
+        <v>27082.97</v>
       </c>
     </row>
     <row r="466">
@@ -16744,10 +16744,10 @@
         <v>11.03</v>
       </c>
       <c r="H466" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I466" t="n">
-        <v>126504.97</v>
+        <v>28355.25</v>
       </c>
     </row>
     <row r="467">
@@ -16779,10 +16779,10 @@
         <v>13.58</v>
       </c>
       <c r="H467" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I467" t="n">
-        <v>155778.71</v>
+        <v>34916.76</v>
       </c>
     </row>
     <row r="468">
@@ -16814,10 +16814,10 @@
         <v>9.27</v>
       </c>
       <c r="H468" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
       <c r="I468" t="n">
-        <v>106392.84</v>
+        <v>23847.25</v>
       </c>
     </row>
     <row r="469">
@@ -16849,10 +16849,10 @@
         <v>10.73</v>
       </c>
       <c r="H469" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I469" t="n">
-        <v>138497.76</v>
+        <v>43013.27</v>
       </c>
     </row>
     <row r="470">
@@ -16884,10 +16884,10 @@
         <v>15.78</v>
       </c>
       <c r="H470" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I470" t="n">
-        <v>203694.74</v>
+        <v>63261.5</v>
       </c>
     </row>
     <row r="471">
@@ -16919,10 +16919,10 @@
         <v>7.42</v>
       </c>
       <c r="H471" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I471" t="n">
-        <v>95744.8</v>
+        <v>29735.48</v>
       </c>
     </row>
     <row r="472">
@@ -16954,10 +16954,10 @@
         <v>9.859999999999999</v>
       </c>
       <c r="H472" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I472" t="n">
-        <v>127316.9</v>
+        <v>39540.83</v>
       </c>
     </row>
     <row r="473">
@@ -16989,10 +16989,10 @@
         <v>11.85</v>
       </c>
       <c r="H473" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I473" t="n">
-        <v>152992</v>
+        <v>47514.75</v>
       </c>
     </row>
     <row r="474">
@@ -17024,10 +17024,10 @@
         <v>10.23</v>
       </c>
       <c r="H474" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I474" t="n">
-        <v>132022.03</v>
+        <v>41002.1</v>
       </c>
     </row>
     <row r="475">
@@ -17059,10 +17059,10 @@
         <v>13.95</v>
       </c>
       <c r="H475" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I475" t="n">
-        <v>180081.53</v>
+        <v>55927.95</v>
       </c>
     </row>
     <row r="476">
@@ -17094,10 +17094,10 @@
         <v>15.08</v>
       </c>
       <c r="H476" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
       <c r="I476" t="n">
-        <v>194629.81</v>
+        <v>60446.21</v>
       </c>
     </row>
     <row r="477">
@@ -17129,10 +17129,10 @@
         <v>16.26</v>
       </c>
       <c r="H477" t="n">
-        <v>865631.98</v>
+        <v>90731.98</v>
       </c>
       <c r="I477" t="n">
-        <v>140744.08</v>
+        <v>14752.22</v>
       </c>
     </row>
     <row r="478">
@@ -17164,10 +17164,10 @@
         <v>16.81</v>
       </c>
       <c r="H478" t="n">
-        <v>865631.98</v>
+        <v>90731.98</v>
       </c>
       <c r="I478" t="n">
-        <v>145473.32</v>
+        <v>15247.91</v>
       </c>
     </row>
     <row r="479">
@@ -17199,10 +17199,10 @@
         <v>32.36</v>
       </c>
       <c r="H479" t="n">
-        <v>865631.98</v>
+        <v>90731.98</v>
       </c>
       <c r="I479" t="n">
-        <v>280091.18</v>
+        <v>29358</v>
       </c>
     </row>
     <row r="480">
@@ -17234,10 +17234,10 @@
         <v>15.99</v>
       </c>
       <c r="H480" t="n">
-        <v>865631.98</v>
+        <v>90731.98</v>
       </c>
       <c r="I480" t="n">
-        <v>138439.81</v>
+        <v>14510.69</v>
       </c>
     </row>
     <row r="481">
@@ -17269,10 +17269,10 @@
         <v>5.53</v>
       </c>
       <c r="H481" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
       <c r="I481" t="n">
-        <v>74478.24000000001</v>
+        <v>25267.58</v>
       </c>
     </row>
     <row r="482">
@@ -17304,10 +17304,10 @@
         <v>11.42</v>
       </c>
       <c r="H482" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
       <c r="I482" t="n">
-        <v>153864.44</v>
+        <v>52200.24</v>
       </c>
     </row>
     <row r="483">
@@ -17339,10 +17339,10 @@
         <v>12.83</v>
       </c>
       <c r="H483" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
       <c r="I483" t="n">
-        <v>172793.16</v>
+        <v>58622.02</v>
       </c>
     </row>
     <row r="484">
@@ -17374,10 +17374,10 @@
         <v>11.33</v>
       </c>
       <c r="H484" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
       <c r="I484" t="n">
-        <v>152579.38</v>
+        <v>51764.27</v>
       </c>
     </row>
     <row r="485">
@@ -17409,10 +17409,10 @@
         <v>6.72</v>
       </c>
       <c r="H485" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
       <c r="I485" t="n">
-        <v>90492.22</v>
+        <v>30700.5</v>
       </c>
     </row>
     <row r="486">
@@ -17444,10 +17444,10 @@
         <v>17.36</v>
       </c>
       <c r="H486" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
       <c r="I486" t="n">
-        <v>233861.04</v>
+        <v>79339.99000000001</v>
       </c>
     </row>
     <row r="487">
@@ -17479,10 +17479,10 @@
         <v>11.16</v>
       </c>
       <c r="H487" t="n">
-        <v>1347019.53</v>
+        <v>456991.53</v>
       </c>
       <c r="I487" t="n">
-        <v>150334.46</v>
+        <v>51002.66</v>
       </c>
     </row>
     <row r="488">
@@ -17514,10 +17514,10 @@
         <v>11.36</v>
       </c>
       <c r="H488" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I488" t="n">
-        <v>115415.17</v>
+        <v>14331.51</v>
       </c>
     </row>
     <row r="489">
@@ -17549,10 +17549,10 @@
         <v>12.16</v>
       </c>
       <c r="H489" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I489" t="n">
-        <v>123553.02</v>
+        <v>15342.01</v>
       </c>
     </row>
     <row r="490">
@@ -17584,10 +17584,10 @@
         <v>19.09</v>
       </c>
       <c r="H490" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I490" t="n">
-        <v>194001.28</v>
+        <v>24089.82</v>
       </c>
     </row>
     <row r="491">
@@ -17619,10 +17619,10 @@
         <v>8.33</v>
       </c>
       <c r="H491" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I491" t="n">
-        <v>84642.88</v>
+        <v>10510.4</v>
       </c>
     </row>
     <row r="492">
@@ -17654,10 +17654,10 @@
         <v>8.460000000000001</v>
       </c>
       <c r="H492" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I492" t="n">
-        <v>85928.22</v>
+        <v>10670.01</v>
       </c>
     </row>
     <row r="493">
@@ -17689,10 +17689,10 @@
         <v>17.24</v>
       </c>
       <c r="H493" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I493" t="n">
-        <v>175195.82</v>
+        <v>21754.68</v>
       </c>
     </row>
     <row r="494">
@@ -17724,10 +17724,10 @@
         <v>15.22</v>
       </c>
       <c r="H494" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I494" t="n">
-        <v>154634.28</v>
+        <v>19201.48</v>
       </c>
     </row>
     <row r="495">
@@ -17759,10 +17759,10 @@
         <v>7.88</v>
       </c>
       <c r="H495" t="n">
-        <v>1016214.99</v>
+        <v>126186.99</v>
       </c>
       <c r="I495" t="n">
-        <v>80087.74000000001</v>
+        <v>9944.780000000001</v>
       </c>
     </row>
     <row r="496">
@@ -17794,10 +17794,10 @@
         <v>13.12</v>
       </c>
       <c r="H496" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I496" t="n">
-        <v>147451.92</v>
+        <v>30661.08</v>
       </c>
     </row>
     <row r="497">
@@ -17829,10 +17829,10 @@
         <v>4.78</v>
       </c>
       <c r="H497" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I497" t="n">
-        <v>53660.97</v>
+        <v>11158.23</v>
       </c>
     </row>
     <row r="498">
@@ -17864,10 +17864,10 @@
         <v>13.84</v>
       </c>
       <c r="H498" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I498" t="n">
-        <v>155525.38</v>
+        <v>32339.87</v>
       </c>
     </row>
     <row r="499">
@@ -17899,10 +17899,10 @@
         <v>5.43</v>
       </c>
       <c r="H499" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I499" t="n">
-        <v>61024.37</v>
+        <v>12689.38</v>
       </c>
     </row>
     <row r="500">
@@ -17934,10 +17934,10 @@
         <v>7.28</v>
       </c>
       <c r="H500" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I500" t="n">
-        <v>81815.31</v>
+        <v>17012.63</v>
       </c>
     </row>
     <row r="501">
@@ -17969,10 +17969,10 @@
         <v>9.73</v>
       </c>
       <c r="H501" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I501" t="n">
-        <v>109361.02</v>
+        <v>22740.47</v>
       </c>
     </row>
     <row r="502">
@@ -18004,10 +18004,10 @@
         <v>10.48</v>
       </c>
       <c r="H502" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I502" t="n">
-        <v>117796.91</v>
+        <v>24494.63</v>
       </c>
     </row>
     <row r="503">
@@ -18039,10 +18039,10 @@
         <v>12.07</v>
       </c>
       <c r="H503" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I503" t="n">
-        <v>135652.56</v>
+        <v>28207.52</v>
       </c>
     </row>
     <row r="504">
@@ -18074,10 +18074,10 @@
         <v>6.41</v>
       </c>
       <c r="H504" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I504" t="n">
-        <v>71985.27</v>
+        <v>14968.58</v>
       </c>
     </row>
     <row r="505">
@@ -18109,10 +18109,10 @@
         <v>15.05</v>
       </c>
       <c r="H505" t="n">
-        <v>1123686.87</v>
+        <v>233658.87</v>
       </c>
       <c r="I505" t="n">
-        <v>169112.54</v>
+        <v>35165.17</v>
       </c>
     </row>
   </sheetData>
